--- a/Book.xlsx
+++ b/Book.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HUAWEI\Documents\falah-library-search\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{413A03BB-6037-400E-802D-98F05189FCA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24A7F7EF-FD51-461A-B734-F9909F71D3CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1934" uniqueCount="1073">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2106" uniqueCount="1073">
   <si>
     <t>ID</t>
   </si>
@@ -4142,7 +4142,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="26">
+  <fills count="27">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4293,6 +4293,12 @@
         <bgColor rgb="FFEAF2E3"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="9">
     <border>
@@ -4422,9 +4428,6 @@
     <xf numFmtId="21" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -4850,6 +4853,9 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5798,11 +5804,11 @@
     <col min="10" max="10" width="27.109375" customWidth="1"/>
     <col min="11" max="11" width="41.88671875" customWidth="1"/>
     <col min="12" max="12" width="82.5546875" customWidth="1"/>
-    <col min="13" max="13" width="28.77734375" customWidth="1"/>
+    <col min="13" max="13" width="86.6640625" customWidth="1"/>
     <col min="14" max="14" width="71.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="99" thickBot="1">
+    <row r="1" spans="1:14" ht="74.400000000000006" thickBot="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5846,7 +5852,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="409.6">
+    <row r="2" spans="1:14" ht="180">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -5886,7 +5892,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="162.6" thickBot="1">
+    <row r="3" spans="1:14" ht="180.6" thickBot="1">
       <c r="A3" s="6">
         <v>2</v>
       </c>
@@ -5894,7 +5900,9 @@
         <v>76</v>
       </c>
       <c r="C3" s="8"/>
-      <c r="D3" s="9"/>
+      <c r="D3" s="9" t="s">
+        <v>71</v>
+      </c>
       <c r="E3" s="7" t="s">
         <v>22</v>
       </c>
@@ -5930,7 +5938,9 @@
         <v>81</v>
       </c>
       <c r="C4" s="8"/>
-      <c r="D4" s="9"/>
+      <c r="D4" s="9" t="s">
+        <v>71</v>
+      </c>
       <c r="E4" s="7" t="s">
         <v>27</v>
       </c>
@@ -5966,7 +5976,9 @@
         <v>85</v>
       </c>
       <c r="C5" s="8"/>
-      <c r="D5" s="9"/>
+      <c r="D5" s="9" t="s">
+        <v>71</v>
+      </c>
       <c r="E5" s="7" t="s">
         <v>31</v>
       </c>
@@ -6002,7 +6014,9 @@
         <v>89</v>
       </c>
       <c r="C6" s="8"/>
-      <c r="D6" s="9"/>
+      <c r="D6" s="9" t="s">
+        <v>71</v>
+      </c>
       <c r="E6" s="7" t="s">
         <v>35</v>
       </c>
@@ -6038,7 +6052,9 @@
         <v>93</v>
       </c>
       <c r="C7" s="8"/>
-      <c r="D7" s="9"/>
+      <c r="D7" s="9" t="s">
+        <v>71</v>
+      </c>
       <c r="E7" s="7" t="s">
         <v>39</v>
       </c>
@@ -6074,7 +6090,9 @@
         <v>99</v>
       </c>
       <c r="C8" s="8"/>
-      <c r="D8" s="9"/>
+      <c r="D8" s="9" t="s">
+        <v>71</v>
+      </c>
       <c r="E8" s="7" t="s">
         <v>43</v>
       </c>
@@ -6150,7 +6168,9 @@
         <v>112</v>
       </c>
       <c r="C10" s="8"/>
-      <c r="D10" s="9"/>
+      <c r="D10" s="9" t="s">
+        <v>105</v>
+      </c>
       <c r="E10" s="7" t="s">
         <v>113</v>
       </c>
@@ -6186,7 +6206,9 @@
         <v>119</v>
       </c>
       <c r="C11" s="8"/>
-      <c r="D11" s="9"/>
+      <c r="D11" s="9" t="s">
+        <v>105</v>
+      </c>
       <c r="E11" s="7" t="s">
         <v>120</v>
       </c>
@@ -6222,7 +6244,9 @@
         <v>124</v>
       </c>
       <c r="C12" s="8"/>
-      <c r="D12" s="9"/>
+      <c r="D12" s="9" t="s">
+        <v>105</v>
+      </c>
       <c r="E12" s="7" t="s">
         <v>27</v>
       </c>
@@ -6258,7 +6282,9 @@
         <v>128</v>
       </c>
       <c r="C13" s="8"/>
-      <c r="D13" s="9"/>
+      <c r="D13" s="9" t="s">
+        <v>105</v>
+      </c>
       <c r="E13" s="7" t="s">
         <v>31</v>
       </c>
@@ -6294,7 +6320,9 @@
         <v>132</v>
       </c>
       <c r="C14" s="8"/>
-      <c r="D14" s="9"/>
+      <c r="D14" s="9" t="s">
+        <v>105</v>
+      </c>
       <c r="E14" s="7" t="s">
         <v>35</v>
       </c>
@@ -6330,7 +6358,9 @@
         <v>136</v>
       </c>
       <c r="C15" s="8"/>
-      <c r="D15" s="9"/>
+      <c r="D15" s="9" t="s">
+        <v>105</v>
+      </c>
       <c r="E15" s="7" t="s">
         <v>39</v>
       </c>
@@ -6390,11 +6420,11 @@
       <c r="K16" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="L16" s="11" t="s">
+      <c r="L16" s="154" t="s">
         <v>145</v>
       </c>
       <c r="M16" s="9"/>
-      <c r="N16" s="11" t="s">
+      <c r="N16" s="154" t="s">
         <v>146</v>
       </c>
     </row>
@@ -6406,7 +6436,9 @@
         <v>147</v>
       </c>
       <c r="C17" s="8"/>
-      <c r="D17" s="9"/>
+      <c r="D17" s="9" t="s">
+        <v>142</v>
+      </c>
       <c r="E17" s="7" t="s">
         <v>22</v>
       </c>
@@ -6442,7 +6474,9 @@
         <v>151</v>
       </c>
       <c r="C18" s="8"/>
-      <c r="D18" s="9"/>
+      <c r="D18" s="9" t="s">
+        <v>142</v>
+      </c>
       <c r="E18" s="7" t="s">
         <v>27</v>
       </c>
@@ -6478,7 +6512,9 @@
         <v>155</v>
       </c>
       <c r="C19" s="8"/>
-      <c r="D19" s="9"/>
+      <c r="D19" s="9" t="s">
+        <v>142</v>
+      </c>
       <c r="E19" s="7" t="s">
         <v>31</v>
       </c>
@@ -6506,7 +6542,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="144">
+    <row r="20" spans="1:14" ht="180">
       <c r="A20" s="5">
         <v>19</v>
       </c>
@@ -6554,7 +6590,9 @@
         <v>166</v>
       </c>
       <c r="C21" s="8"/>
-      <c r="D21" s="9"/>
+      <c r="D21" s="9" t="s">
+        <v>161</v>
+      </c>
       <c r="E21" s="7" t="s">
         <v>22</v>
       </c>
@@ -6590,7 +6628,9 @@
         <v>170</v>
       </c>
       <c r="C22" s="8"/>
-      <c r="D22" s="9"/>
+      <c r="D22" s="9" t="s">
+        <v>161</v>
+      </c>
       <c r="E22" s="7" t="s">
         <v>27</v>
       </c>
@@ -6618,7 +6658,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="180.6" thickBot="1">
+    <row r="23" spans="1:14" ht="198.6" thickBot="1">
       <c r="A23" s="6">
         <v>22</v>
       </c>
@@ -6626,7 +6666,9 @@
         <v>174</v>
       </c>
       <c r="C23" s="8"/>
-      <c r="D23" s="9"/>
+      <c r="D23" s="9" t="s">
+        <v>161</v>
+      </c>
       <c r="E23" s="7" t="s">
         <v>31</v>
       </c>
@@ -6662,7 +6704,9 @@
         <v>178</v>
       </c>
       <c r="C24" s="8"/>
-      <c r="D24" s="9"/>
+      <c r="D24" s="9" t="s">
+        <v>161</v>
+      </c>
       <c r="E24" s="7" t="s">
         <v>35</v>
       </c>
@@ -6698,7 +6742,9 @@
         <v>182</v>
       </c>
       <c r="C25" s="8"/>
-      <c r="D25" s="9"/>
+      <c r="D25" s="9" t="s">
+        <v>161</v>
+      </c>
       <c r="E25" s="7" t="s">
         <v>39</v>
       </c>
@@ -6734,7 +6780,9 @@
         <v>187</v>
       </c>
       <c r="C26" s="8"/>
-      <c r="D26" s="9"/>
+      <c r="D26" s="9" t="s">
+        <v>161</v>
+      </c>
       <c r="E26" s="7" t="s">
         <v>43</v>
       </c>
@@ -6762,7 +6810,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="180.6" thickBot="1">
+    <row r="27" spans="1:14" ht="198.6" thickBot="1">
       <c r="A27" s="6">
         <v>26</v>
       </c>
@@ -6770,7 +6818,9 @@
         <v>192</v>
       </c>
       <c r="C27" s="8"/>
-      <c r="D27" s="9"/>
+      <c r="D27" s="9" t="s">
+        <v>161</v>
+      </c>
       <c r="E27" s="7" t="s">
         <v>48</v>
       </c>
@@ -6846,7 +6896,9 @@
         <v>202</v>
       </c>
       <c r="C29" s="8"/>
-      <c r="D29" s="9"/>
+      <c r="D29" s="9" t="s">
+        <v>198</v>
+      </c>
       <c r="E29" s="7" t="s">
         <v>22</v>
       </c>
@@ -6882,7 +6934,9 @@
         <v>206</v>
       </c>
       <c r="C30" s="8"/>
-      <c r="D30" s="9"/>
+      <c r="D30" s="9" t="s">
+        <v>198</v>
+      </c>
       <c r="E30" s="7" t="s">
         <v>27</v>
       </c>
@@ -6918,7 +6972,9 @@
         <v>210</v>
       </c>
       <c r="C31" s="8"/>
-      <c r="D31" s="9"/>
+      <c r="D31" s="9" t="s">
+        <v>198</v>
+      </c>
       <c r="E31" s="7" t="s">
         <v>31</v>
       </c>
@@ -6954,7 +7010,9 @@
         <v>214</v>
       </c>
       <c r="C32" s="8"/>
-      <c r="D32" s="9"/>
+      <c r="D32" s="9" t="s">
+        <v>198</v>
+      </c>
       <c r="E32" s="7" t="s">
         <v>35</v>
       </c>
@@ -6982,7 +7040,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="33" spans="1:14" ht="180.6" thickBot="1">
+    <row r="33" spans="1:14" ht="198.6" thickBot="1">
       <c r="A33" s="6">
         <v>32</v>
       </c>
@@ -6990,7 +7048,9 @@
         <v>218</v>
       </c>
       <c r="C33" s="8"/>
-      <c r="D33" s="9"/>
+      <c r="D33" s="9" t="s">
+        <v>198</v>
+      </c>
       <c r="E33" s="7" t="s">
         <v>39</v>
       </c>
@@ -7026,7 +7086,9 @@
         <v>222</v>
       </c>
       <c r="C34" s="8"/>
-      <c r="D34" s="9"/>
+      <c r="D34" s="9" t="s">
+        <v>198</v>
+      </c>
       <c r="E34" s="7" t="s">
         <v>43</v>
       </c>
@@ -7062,7 +7124,9 @@
         <v>226</v>
       </c>
       <c r="C35" s="8"/>
-      <c r="D35" s="9"/>
+      <c r="D35" s="9" t="s">
+        <v>198</v>
+      </c>
       <c r="E35" s="7" t="s">
         <v>48</v>
       </c>
@@ -7098,7 +7162,9 @@
         <v>230</v>
       </c>
       <c r="C36" s="8"/>
-      <c r="D36" s="9"/>
+      <c r="D36" s="9" t="s">
+        <v>198</v>
+      </c>
       <c r="E36" s="7" t="s">
         <v>52</v>
       </c>
@@ -7134,7 +7200,9 @@
         <v>234</v>
       </c>
       <c r="C37" s="8"/>
-      <c r="D37" s="9"/>
+      <c r="D37" s="9" t="s">
+        <v>198</v>
+      </c>
       <c r="E37" s="7" t="s">
         <v>56</v>
       </c>
@@ -7210,7 +7278,9 @@
         <v>249</v>
       </c>
       <c r="C39" s="8"/>
-      <c r="D39" s="9"/>
+      <c r="D39" s="9" t="s">
+        <v>242</v>
+      </c>
       <c r="E39" s="7" t="s">
         <v>22</v>
       </c>
@@ -7246,7 +7316,9 @@
         <v>256</v>
       </c>
       <c r="C40" s="8"/>
-      <c r="D40" s="9"/>
+      <c r="D40" s="9" t="s">
+        <v>242</v>
+      </c>
       <c r="E40" s="7" t="s">
         <v>27</v>
       </c>
@@ -7280,7 +7352,9 @@
         <v>261</v>
       </c>
       <c r="C41" s="8"/>
-      <c r="D41" s="9"/>
+      <c r="D41" s="9" t="s">
+        <v>242</v>
+      </c>
       <c r="E41" s="7" t="s">
         <v>31</v>
       </c>
@@ -7308,7 +7382,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="42" spans="1:14" ht="180">
+    <row r="42" spans="1:14" ht="198">
       <c r="A42" s="5">
         <v>41</v>
       </c>
@@ -7316,7 +7390,9 @@
         <v>265</v>
       </c>
       <c r="C42" s="8"/>
-      <c r="D42" s="9"/>
+      <c r="D42" s="9" t="s">
+        <v>242</v>
+      </c>
       <c r="E42" s="7" t="s">
         <v>35</v>
       </c>
@@ -7352,7 +7428,9 @@
         <v>270</v>
       </c>
       <c r="C43" s="8"/>
-      <c r="D43" s="9"/>
+      <c r="D43" s="9" t="s">
+        <v>242</v>
+      </c>
       <c r="E43" s="7" t="s">
         <v>39</v>
       </c>
@@ -7428,7 +7506,9 @@
         <v>281</v>
       </c>
       <c r="C45" s="8"/>
-      <c r="D45" s="9"/>
+      <c r="D45" s="9" t="s">
+        <v>276</v>
+      </c>
       <c r="E45" s="7" t="s">
         <v>22</v>
       </c>
@@ -7464,7 +7544,9 @@
         <v>285</v>
       </c>
       <c r="C46" s="8"/>
-      <c r="D46" s="9"/>
+      <c r="D46" s="9" t="s">
+        <v>276</v>
+      </c>
       <c r="E46" s="7" t="s">
         <v>27</v>
       </c>
@@ -7500,7 +7582,9 @@
         <v>289</v>
       </c>
       <c r="C47" s="8"/>
-      <c r="D47" s="9"/>
+      <c r="D47" s="9" t="s">
+        <v>276</v>
+      </c>
       <c r="E47" s="7" t="s">
         <v>31</v>
       </c>
@@ -7576,7 +7660,9 @@
         <v>299</v>
       </c>
       <c r="C49" s="8"/>
-      <c r="D49" s="9"/>
+      <c r="D49" s="9" t="s">
+        <v>295</v>
+      </c>
       <c r="E49" s="7" t="s">
         <v>113</v>
       </c>
@@ -7612,7 +7698,9 @@
         <v>305</v>
       </c>
       <c r="C50" s="8"/>
-      <c r="D50" s="9"/>
+      <c r="D50" s="9" t="s">
+        <v>295</v>
+      </c>
       <c r="E50" s="7" t="s">
         <v>120</v>
       </c>
@@ -7648,7 +7736,9 @@
         <v>310</v>
       </c>
       <c r="C51" s="8"/>
-      <c r="D51" s="9"/>
+      <c r="D51" s="9" t="s">
+        <v>295</v>
+      </c>
       <c r="E51" s="7" t="s">
         <v>27</v>
       </c>
@@ -7684,7 +7774,9 @@
         <v>314</v>
       </c>
       <c r="C52" s="8"/>
-      <c r="D52" s="9"/>
+      <c r="D52" s="9" t="s">
+        <v>295</v>
+      </c>
       <c r="E52" s="7" t="s">
         <v>31</v>
       </c>
@@ -7720,7 +7812,9 @@
         <v>318</v>
       </c>
       <c r="C53" s="8"/>
-      <c r="D53" s="9"/>
+      <c r="D53" s="9" t="s">
+        <v>295</v>
+      </c>
       <c r="E53" s="7" t="s">
         <v>35</v>
       </c>
@@ -7756,7 +7850,9 @@
         <v>322</v>
       </c>
       <c r="C54" s="8"/>
-      <c r="D54" s="9"/>
+      <c r="D54" s="9" t="s">
+        <v>295</v>
+      </c>
       <c r="E54" s="7" t="s">
         <v>39</v>
       </c>
@@ -7792,7 +7888,9 @@
         <v>326</v>
       </c>
       <c r="C55" s="8"/>
-      <c r="D55" s="9"/>
+      <c r="D55" s="9" t="s">
+        <v>295</v>
+      </c>
       <c r="E55" s="7" t="s">
         <v>43</v>
       </c>
@@ -7820,1387 +7918,1441 @@
         <v>329</v>
       </c>
     </row>
-    <row r="56" spans="1:14" ht="348.6">
+    <row r="56" spans="1:14" ht="162">
       <c r="A56" s="5">
         <v>55</v>
       </c>
-      <c r="B56" s="12" t="s">
+      <c r="B56" s="11" t="s">
         <v>330</v>
       </c>
-      <c r="C56" s="13" t="s">
+      <c r="C56" s="12" t="s">
         <v>331</v>
       </c>
-      <c r="D56" s="14" t="s">
+      <c r="D56" s="13" t="s">
         <v>332</v>
       </c>
-      <c r="E56" s="15" t="s">
+      <c r="E56" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="F56" s="16" t="s">
+      <c r="F56" s="15" t="s">
         <v>333</v>
       </c>
-      <c r="G56" s="17">
+      <c r="G56" s="16">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="H56" s="14" t="s">
+      <c r="H56" s="13" t="s">
         <v>301</v>
       </c>
-      <c r="I56" s="14" t="s">
+      <c r="I56" s="13" t="s">
         <v>334</v>
       </c>
-      <c r="J56" s="14" t="s">
+      <c r="J56" s="13" t="s">
         <v>335</v>
       </c>
-      <c r="K56" s="14" t="s">
+      <c r="K56" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="L56" s="14" t="s">
+      <c r="L56" s="13" t="s">
         <v>336</v>
       </c>
-      <c r="M56" s="18" t="s">
+      <c r="M56" s="17" t="s">
         <v>337</v>
       </c>
-      <c r="N56" s="14" t="s">
+      <c r="N56" s="13" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="57" spans="1:14" ht="331.8" thickBot="1">
+    <row r="57" spans="1:14" ht="180.6" thickBot="1">
       <c r="A57" s="6">
         <v>56</v>
       </c>
-      <c r="B57" s="12" t="s">
+      <c r="B57" s="11" t="s">
         <v>339</v>
       </c>
-      <c r="C57" s="19"/>
-      <c r="D57" s="20"/>
-      <c r="E57" s="15" t="s">
+      <c r="C57" s="18"/>
+      <c r="D57" s="13" t="s">
+        <v>332</v>
+      </c>
+      <c r="E57" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="F57" s="21" t="s">
+      <c r="F57" s="20" t="s">
         <v>340</v>
       </c>
-      <c r="G57" s="22">
+      <c r="G57" s="21">
         <v>3.8194444444444448E-2</v>
       </c>
-      <c r="H57" s="20" t="s">
+      <c r="H57" s="19" t="s">
         <v>244</v>
       </c>
-      <c r="I57" s="20" t="s">
+      <c r="I57" s="19" t="s">
         <v>341</v>
       </c>
-      <c r="J57" s="14" t="s">
+      <c r="J57" s="13" t="s">
         <v>335</v>
       </c>
-      <c r="K57" s="20" t="s">
+      <c r="K57" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="L57" s="20" t="s">
+      <c r="L57" s="19" t="s">
         <v>342</v>
       </c>
-      <c r="M57" s="23" t="s">
+      <c r="M57" s="22" t="s">
         <v>343</v>
       </c>
-      <c r="N57" s="20" t="s">
+      <c r="N57" s="19" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="58" spans="1:14" ht="348.6">
+    <row r="58" spans="1:14" ht="198">
       <c r="A58" s="5">
         <v>57</v>
       </c>
-      <c r="B58" s="12" t="s">
+      <c r="B58" s="11" t="s">
         <v>345</v>
       </c>
-      <c r="C58" s="19"/>
-      <c r="D58" s="20"/>
-      <c r="E58" s="15" t="s">
+      <c r="C58" s="18"/>
+      <c r="D58" s="13" t="s">
+        <v>332</v>
+      </c>
+      <c r="E58" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="F58" s="21" t="s">
+      <c r="F58" s="20" t="s">
         <v>346</v>
       </c>
-      <c r="G58" s="22">
+      <c r="G58" s="21">
         <v>2.0833333333333332E-2</v>
       </c>
-      <c r="H58" s="20" t="s">
+      <c r="H58" s="19" t="s">
         <v>347</v>
       </c>
-      <c r="I58" s="20" t="s">
+      <c r="I58" s="19" t="s">
         <v>348</v>
       </c>
-      <c r="J58" s="14" t="s">
+      <c r="J58" s="13" t="s">
         <v>335</v>
       </c>
-      <c r="K58" s="20" t="s">
+      <c r="K58" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="L58" s="20" t="s">
+      <c r="L58" s="19" t="s">
         <v>349</v>
       </c>
-      <c r="M58" s="23" t="s">
+      <c r="M58" s="22" t="s">
         <v>350</v>
       </c>
-      <c r="N58" s="20" t="s">
+      <c r="N58" s="19" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="59" spans="1:14" ht="244.8" thickBot="1">
+    <row r="59" spans="1:14" ht="162.6" thickBot="1">
       <c r="A59" s="6">
         <v>58</v>
       </c>
-      <c r="B59" s="12" t="s">
+      <c r="B59" s="11" t="s">
         <v>352</v>
       </c>
-      <c r="C59" s="19"/>
-      <c r="D59" s="20"/>
-      <c r="E59" s="15" t="s">
+      <c r="C59" s="18"/>
+      <c r="D59" s="13" t="s">
+        <v>332</v>
+      </c>
+      <c r="E59" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="F59" s="21" t="s">
+      <c r="F59" s="20" t="s">
         <v>353</v>
       </c>
-      <c r="G59" s="22">
+      <c r="G59" s="21">
         <v>1.9444444444444445E-2</v>
       </c>
-      <c r="H59" s="20" t="s">
+      <c r="H59" s="19" t="s">
         <v>347</v>
       </c>
-      <c r="I59" s="20" t="s">
+      <c r="I59" s="19" t="s">
         <v>354</v>
       </c>
-      <c r="J59" s="14" t="s">
+      <c r="J59" s="13" t="s">
         <v>335</v>
       </c>
-      <c r="K59" s="20" t="s">
+      <c r="K59" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="L59" s="20" t="s">
+      <c r="L59" s="19" t="s">
         <v>355</v>
       </c>
-      <c r="M59" s="23" t="s">
+      <c r="M59" s="22" t="s">
         <v>356</v>
       </c>
-      <c r="N59" s="20" t="s">
+      <c r="N59" s="19" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="60" spans="1:14" ht="261.60000000000002">
+    <row r="60" spans="1:14" ht="180">
       <c r="A60" s="5">
         <v>59</v>
       </c>
-      <c r="B60" s="12" t="s">
+      <c r="B60" s="11" t="s">
         <v>358</v>
       </c>
-      <c r="C60" s="19"/>
-      <c r="D60" s="20"/>
-      <c r="E60" s="15" t="s">
+      <c r="C60" s="18"/>
+      <c r="D60" s="13" t="s">
+        <v>332</v>
+      </c>
+      <c r="E60" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="F60" s="21" t="s">
+      <c r="F60" s="20" t="s">
         <v>359</v>
       </c>
-      <c r="G60" s="22">
+      <c r="G60" s="21">
         <v>2.9861111111111113E-2</v>
       </c>
-      <c r="H60" s="20" t="s">
+      <c r="H60" s="19" t="s">
         <v>347</v>
       </c>
-      <c r="I60" s="20" t="s">
+      <c r="I60" s="19" t="s">
         <v>360</v>
       </c>
-      <c r="J60" s="20" t="s">
+      <c r="J60" s="19" t="s">
         <v>361</v>
       </c>
-      <c r="K60" s="20" t="s">
+      <c r="K60" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="L60" s="20" t="s">
+      <c r="L60" s="19" t="s">
         <v>362</v>
       </c>
-      <c r="M60" s="23" t="s">
+      <c r="M60" s="22" t="s">
         <v>363</v>
       </c>
-      <c r="N60" s="20" t="s">
+      <c r="N60" s="19" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="61" spans="1:14" ht="331.8" thickBot="1">
+    <row r="61" spans="1:14" ht="180.6" thickBot="1">
       <c r="A61" s="6">
         <v>60</v>
       </c>
-      <c r="B61" s="12" t="s">
+      <c r="B61" s="11" t="s">
         <v>365</v>
       </c>
-      <c r="C61" s="19"/>
-      <c r="D61" s="20"/>
-      <c r="E61" s="15" t="s">
+      <c r="C61" s="18"/>
+      <c r="D61" s="13" t="s">
+        <v>332</v>
+      </c>
+      <c r="E61" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="F61" s="21" t="s">
+      <c r="F61" s="20" t="s">
         <v>366</v>
       </c>
-      <c r="G61" s="22">
+      <c r="G61" s="21">
         <v>3.5416666666666666E-2</v>
       </c>
-      <c r="H61" s="20" t="s">
+      <c r="H61" s="19" t="s">
         <v>347</v>
       </c>
-      <c r="I61" s="20" t="s">
+      <c r="I61" s="19" t="s">
         <v>367</v>
       </c>
-      <c r="J61" s="20" t="s">
+      <c r="J61" s="19" t="s">
         <v>368</v>
       </c>
-      <c r="K61" s="20" t="s">
+      <c r="K61" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="L61" s="20" t="s">
+      <c r="L61" s="19" t="s">
         <v>369</v>
       </c>
-      <c r="M61" s="23" t="s">
+      <c r="M61" s="22" t="s">
         <v>370</v>
       </c>
-      <c r="N61" s="20" t="s">
+      <c r="N61" s="19" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="62" spans="1:14" ht="348.6">
+    <row r="62" spans="1:14" ht="198">
       <c r="A62" s="5">
         <v>61</v>
       </c>
-      <c r="B62" s="12" t="s">
+      <c r="B62" s="11" t="s">
         <v>372</v>
       </c>
-      <c r="C62" s="19"/>
-      <c r="D62" s="20"/>
-      <c r="E62" s="15" t="s">
+      <c r="C62" s="18"/>
+      <c r="D62" s="13" t="s">
+        <v>332</v>
+      </c>
+      <c r="E62" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="F62" s="21" t="s">
+      <c r="F62" s="20" t="s">
         <v>373</v>
       </c>
-      <c r="G62" s="22">
+      <c r="G62" s="21">
         <v>2.0833333333333332E-2</v>
       </c>
-      <c r="H62" s="20" t="s">
+      <c r="H62" s="19" t="s">
         <v>374</v>
       </c>
-      <c r="I62" s="20" t="s">
+      <c r="I62" s="19" t="s">
         <v>375</v>
       </c>
-      <c r="J62" s="20" t="s">
+      <c r="J62" s="19" t="s">
         <v>376</v>
       </c>
-      <c r="K62" s="20" t="s">
+      <c r="K62" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="L62" s="20" t="s">
+      <c r="L62" s="19" t="s">
         <v>377</v>
       </c>
-      <c r="M62" s="23" t="s">
+      <c r="M62" s="22" t="s">
         <v>378</v>
       </c>
-      <c r="N62" s="20" t="s">
+      <c r="N62" s="19" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="63" spans="1:14" ht="409.6" thickBot="1">
+    <row r="63" spans="1:14" ht="297" thickBot="1">
       <c r="A63" s="6">
         <v>62</v>
       </c>
-      <c r="B63" s="24" t="s">
+      <c r="B63" s="23" t="s">
         <v>380</v>
       </c>
-      <c r="C63" s="25" t="s">
+      <c r="C63" s="24" t="s">
         <v>381</v>
       </c>
-      <c r="D63" s="26" t="s">
+      <c r="D63" s="25" t="s">
         <v>382</v>
       </c>
-      <c r="E63" s="27" t="s">
+      <c r="E63" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="F63" s="28" t="s">
+      <c r="F63" s="27" t="s">
         <v>383</v>
       </c>
-      <c r="G63" s="29">
+      <c r="G63" s="28">
         <v>2.0625000000000001E-2</v>
       </c>
-      <c r="H63" s="28" t="s">
+      <c r="H63" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="I63" s="28" t="s">
+      <c r="I63" s="27" t="s">
         <v>115</v>
       </c>
-      <c r="J63" s="28" t="s">
+      <c r="J63" s="27" t="s">
         <v>384</v>
       </c>
-      <c r="K63" s="28" t="s">
+      <c r="K63" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="L63" s="28" t="s">
+      <c r="L63" s="27" t="s">
         <v>385</v>
       </c>
-      <c r="M63" s="30" t="s">
+      <c r="M63" s="29" t="s">
         <v>386</v>
       </c>
-      <c r="N63" s="28" t="s">
+      <c r="N63" s="27" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="64" spans="1:14" ht="409.6">
+    <row r="64" spans="1:14" ht="313.8">
       <c r="A64" s="5">
         <v>63</v>
       </c>
-      <c r="B64" s="24" t="s">
+      <c r="B64" s="23" t="s">
         <v>388</v>
       </c>
-      <c r="C64" s="25"/>
-      <c r="D64" s="28"/>
-      <c r="E64" s="27" t="s">
+      <c r="C64" s="24"/>
+      <c r="D64" s="25" t="s">
+        <v>382</v>
+      </c>
+      <c r="E64" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="F64" s="28" t="s">
+      <c r="F64" s="27" t="s">
         <v>389</v>
       </c>
-      <c r="G64" s="29">
+      <c r="G64" s="28">
         <v>1.6921296296296295E-2</v>
       </c>
-      <c r="H64" s="28" t="s">
+      <c r="H64" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="I64" s="28" t="s">
+      <c r="I64" s="27" t="s">
         <v>115</v>
       </c>
-      <c r="J64" s="28" t="s">
+      <c r="J64" s="27" t="s">
         <v>384</v>
       </c>
-      <c r="K64" s="28" t="s">
+      <c r="K64" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="L64" s="28" t="s">
+      <c r="L64" s="27" t="s">
         <v>390</v>
       </c>
-      <c r="M64" s="30" t="s">
+      <c r="M64" s="29" t="s">
         <v>391</v>
       </c>
-      <c r="N64" s="28" t="s">
+      <c r="N64" s="27" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="65" spans="1:14" ht="409.6" thickBot="1">
+    <row r="65" spans="1:14" ht="349.2" thickBot="1">
       <c r="A65" s="6">
         <v>64</v>
       </c>
-      <c r="B65" s="24" t="s">
+      <c r="B65" s="23" t="s">
         <v>393</v>
       </c>
-      <c r="C65" s="25"/>
-      <c r="D65" s="28"/>
-      <c r="E65" s="27" t="s">
+      <c r="C65" s="24"/>
+      <c r="D65" s="25" t="s">
+        <v>382</v>
+      </c>
+      <c r="E65" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="F65" s="28" t="s">
+      <c r="F65" s="27" t="s">
         <v>394</v>
       </c>
-      <c r="G65" s="29">
+      <c r="G65" s="28">
         <v>1.7592592592592592E-3</v>
       </c>
-      <c r="H65" s="28" t="s">
+      <c r="H65" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="I65" s="28" t="s">
+      <c r="I65" s="27" t="s">
         <v>395</v>
       </c>
-      <c r="J65" s="28" t="s">
+      <c r="J65" s="27" t="s">
         <v>384</v>
       </c>
-      <c r="K65" s="28" t="s">
+      <c r="K65" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="L65" s="28" t="s">
+      <c r="L65" s="27" t="s">
         <v>396</v>
       </c>
-      <c r="M65" s="30" t="s">
+      <c r="M65" s="29" t="s">
         <v>397</v>
       </c>
-      <c r="N65" s="28" t="s">
+      <c r="N65" s="27" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="66" spans="1:14" ht="409.6">
+    <row r="66" spans="1:14" ht="348.6">
       <c r="A66" s="5">
         <v>65</v>
       </c>
-      <c r="B66" s="24" t="s">
+      <c r="B66" s="23" t="s">
         <v>399</v>
       </c>
-      <c r="C66" s="25"/>
-      <c r="D66" s="28"/>
-      <c r="E66" s="27" t="s">
+      <c r="C66" s="24"/>
+      <c r="D66" s="25" t="s">
+        <v>382</v>
+      </c>
+      <c r="E66" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="F66" s="28" t="s">
+      <c r="F66" s="27" t="s">
         <v>400</v>
       </c>
-      <c r="G66" s="29">
+      <c r="G66" s="28">
         <v>1.3888888888888888E-2</v>
       </c>
-      <c r="H66" s="28" t="s">
+      <c r="H66" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="I66" s="28" t="s">
+      <c r="I66" s="27" t="s">
         <v>395</v>
       </c>
-      <c r="J66" s="28" t="s">
+      <c r="J66" s="27" t="s">
         <v>384</v>
       </c>
-      <c r="K66" s="28" t="s">
+      <c r="K66" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="L66" s="28" t="s">
+      <c r="L66" s="27" t="s">
         <v>401</v>
       </c>
-      <c r="M66" s="30" t="s">
+      <c r="M66" s="29" t="s">
         <v>402</v>
       </c>
-      <c r="N66" s="28" t="s">
+      <c r="N66" s="27" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="67" spans="1:14" ht="409.6" thickBot="1">
+    <row r="67" spans="1:14" ht="297" thickBot="1">
       <c r="A67" s="6">
         <v>66</v>
       </c>
-      <c r="B67" s="24" t="s">
+      <c r="B67" s="23" t="s">
         <v>404</v>
       </c>
-      <c r="C67" s="25"/>
-      <c r="D67" s="28"/>
-      <c r="E67" s="27" t="s">
+      <c r="C67" s="24"/>
+      <c r="D67" s="25" t="s">
+        <v>382</v>
+      </c>
+      <c r="E67" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="F67" s="28" t="s">
+      <c r="F67" s="27" t="s">
         <v>405</v>
       </c>
-      <c r="G67" s="29">
+      <c r="G67" s="28">
         <v>1.9050925925925926E-2</v>
       </c>
-      <c r="H67" s="28" t="s">
+      <c r="H67" s="27" t="s">
         <v>244</v>
       </c>
-      <c r="I67" s="28" t="s">
+      <c r="I67" s="27" t="s">
         <v>341</v>
       </c>
-      <c r="J67" s="28" t="s">
+      <c r="J67" s="27" t="s">
         <v>384</v>
       </c>
-      <c r="K67" s="28" t="s">
+      <c r="K67" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="L67" s="28" t="s">
+      <c r="L67" s="27" t="s">
         <v>406</v>
       </c>
-      <c r="M67" s="30" t="s">
+      <c r="M67" s="29" t="s">
         <v>407</v>
       </c>
-      <c r="N67" s="28" t="s">
+      <c r="N67" s="27" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="68" spans="1:14" ht="409.6">
+    <row r="68" spans="1:14" ht="296.39999999999998">
       <c r="A68" s="5">
         <v>67</v>
       </c>
-      <c r="B68" s="24" t="s">
+      <c r="B68" s="23" t="s">
         <v>409</v>
       </c>
-      <c r="C68" s="25"/>
-      <c r="D68" s="28"/>
-      <c r="E68" s="27" t="s">
+      <c r="C68" s="24"/>
+      <c r="D68" s="25" t="s">
+        <v>382</v>
+      </c>
+      <c r="E68" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="F68" s="28" t="s">
+      <c r="F68" s="27" t="s">
         <v>410</v>
       </c>
-      <c r="G68" s="29">
+      <c r="G68" s="28">
         <v>1.7893518518518517E-2</v>
       </c>
-      <c r="H68" s="28" t="s">
+      <c r="H68" s="27" t="s">
         <v>107</v>
       </c>
-      <c r="I68" s="28" t="s">
+      <c r="I68" s="27" t="s">
         <v>108</v>
       </c>
-      <c r="J68" s="28" t="s">
+      <c r="J68" s="27" t="s">
         <v>384</v>
       </c>
-      <c r="K68" s="28" t="s">
+      <c r="K68" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="L68" s="28" t="s">
+      <c r="L68" s="27" t="s">
         <v>411</v>
       </c>
-      <c r="M68" s="30" t="s">
+      <c r="M68" s="29" t="s">
         <v>412</v>
       </c>
-      <c r="N68" s="28" t="s">
+      <c r="N68" s="27" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="69" spans="1:14" ht="409.6" thickBot="1">
+    <row r="69" spans="1:14" ht="314.39999999999998" thickBot="1">
       <c r="A69" s="6">
         <v>68</v>
       </c>
-      <c r="B69" s="24" t="s">
+      <c r="B69" s="23" t="s">
         <v>414</v>
       </c>
-      <c r="C69" s="25"/>
-      <c r="D69" s="28"/>
-      <c r="E69" s="27" t="s">
+      <c r="C69" s="24"/>
+      <c r="D69" s="25" t="s">
+        <v>382</v>
+      </c>
+      <c r="E69" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="F69" s="28" t="s">
+      <c r="F69" s="27" t="s">
         <v>415</v>
       </c>
-      <c r="G69" s="29">
+      <c r="G69" s="28">
         <v>1.7083333333333332E-2</v>
       </c>
-      <c r="H69" s="28" t="s">
+      <c r="H69" s="27" t="s">
         <v>107</v>
       </c>
-      <c r="I69" s="28" t="s">
+      <c r="I69" s="27" t="s">
         <v>108</v>
       </c>
-      <c r="J69" s="28" t="s">
+      <c r="J69" s="27" t="s">
         <v>384</v>
       </c>
-      <c r="K69" s="28" t="s">
+      <c r="K69" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="L69" s="28" t="s">
+      <c r="L69" s="27" t="s">
         <v>416</v>
       </c>
-      <c r="M69" s="30" t="s">
+      <c r="M69" s="29" t="s">
         <v>417</v>
       </c>
-      <c r="N69" s="28" t="s">
+      <c r="N69" s="27" t="s">
         <v>418</v>
       </c>
     </row>
-    <row r="70" spans="1:14" ht="409.6">
+    <row r="70" spans="1:14" ht="313.8">
       <c r="A70" s="5">
         <v>69</v>
       </c>
-      <c r="B70" s="24" t="s">
+      <c r="B70" s="23" t="s">
         <v>419</v>
       </c>
-      <c r="C70" s="25"/>
-      <c r="D70" s="28"/>
-      <c r="E70" s="27" t="s">
+      <c r="C70" s="24"/>
+      <c r="D70" s="25" t="s">
+        <v>382</v>
+      </c>
+      <c r="E70" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="F70" s="28" t="s">
+      <c r="F70" s="27" t="s">
         <v>420</v>
       </c>
-      <c r="G70" s="29">
+      <c r="G70" s="28">
         <v>1.6238425925925927E-2</v>
       </c>
-      <c r="H70" s="28" t="s">
+      <c r="H70" s="27" t="s">
         <v>107</v>
       </c>
-      <c r="I70" s="28" t="s">
+      <c r="I70" s="27" t="s">
         <v>108</v>
       </c>
-      <c r="J70" s="28" t="s">
+      <c r="J70" s="27" t="s">
         <v>384</v>
       </c>
-      <c r="K70" s="28" t="s">
+      <c r="K70" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="L70" s="28" t="s">
+      <c r="L70" s="27" t="s">
         <v>421</v>
       </c>
-      <c r="M70" s="30" t="s">
+      <c r="M70" s="29" t="s">
         <v>422</v>
       </c>
-      <c r="N70" s="28" t="s">
+      <c r="N70" s="27" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="71" spans="1:14" ht="409.6" thickBot="1">
+    <row r="71" spans="1:14" ht="279.60000000000002" thickBot="1">
       <c r="A71" s="6">
         <v>70</v>
       </c>
-      <c r="B71" s="24" t="s">
+      <c r="B71" s="23" t="s">
         <v>424</v>
       </c>
-      <c r="C71" s="25"/>
-      <c r="D71" s="28"/>
-      <c r="E71" s="27" t="s">
+      <c r="C71" s="24"/>
+      <c r="D71" s="25" t="s">
+        <v>382</v>
+      </c>
+      <c r="E71" s="26" t="s">
         <v>52</v>
       </c>
-      <c r="F71" s="28" t="s">
+      <c r="F71" s="27" t="s">
         <v>425</v>
       </c>
-      <c r="G71" s="29">
+      <c r="G71" s="28">
         <v>1.3368055555555555E-2</v>
       </c>
-      <c r="H71" s="28" t="s">
+      <c r="H71" s="27" t="s">
         <v>107</v>
       </c>
-      <c r="I71" s="28" t="s">
+      <c r="I71" s="27" t="s">
         <v>189</v>
       </c>
-      <c r="J71" s="28" t="s">
+      <c r="J71" s="27" t="s">
         <v>384</v>
       </c>
-      <c r="K71" s="28" t="s">
+      <c r="K71" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="L71" s="28" t="s">
+      <c r="L71" s="27" t="s">
         <v>426</v>
       </c>
-      <c r="M71" s="30" t="s">
+      <c r="M71" s="29" t="s">
         <v>427</v>
       </c>
-      <c r="N71" s="28" t="s">
+      <c r="N71" s="27" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="72" spans="1:14" ht="409.6">
+    <row r="72" spans="1:14" ht="244.2">
       <c r="A72" s="5">
         <v>71</v>
       </c>
-      <c r="B72" s="31" t="s">
+      <c r="B72" s="30" t="s">
         <v>429</v>
       </c>
-      <c r="C72" s="32" t="s">
+      <c r="C72" s="31" t="s">
         <v>430</v>
       </c>
-      <c r="D72" s="33" t="s">
+      <c r="D72" s="32" t="s">
         <v>431</v>
       </c>
-      <c r="E72" s="34" t="s">
+      <c r="E72" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="F72" s="33" t="s">
+      <c r="F72" s="32" t="s">
         <v>431</v>
       </c>
-      <c r="G72" s="35">
+      <c r="G72" s="34">
         <v>1.7280092592592593E-2</v>
       </c>
-      <c r="H72" s="33" t="s">
+      <c r="H72" s="32" t="s">
         <v>244</v>
       </c>
-      <c r="I72" s="33" t="s">
+      <c r="I72" s="32" t="s">
         <v>341</v>
       </c>
-      <c r="J72" s="33" t="s">
+      <c r="J72" s="32" t="s">
         <v>432</v>
       </c>
-      <c r="K72" s="33" t="s">
+      <c r="K72" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="L72" s="33" t="s">
+      <c r="L72" s="32" t="s">
         <v>433</v>
       </c>
-      <c r="M72" s="36" t="s">
+      <c r="M72" s="35" t="s">
         <v>434</v>
       </c>
-      <c r="N72" s="33" t="s">
+      <c r="N72" s="32" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="73" spans="1:14" ht="409.6" thickBot="1">
+    <row r="73" spans="1:14" ht="244.8" thickBot="1">
       <c r="A73" s="6">
         <v>72</v>
       </c>
-      <c r="B73" s="31" t="s">
+      <c r="B73" s="30" t="s">
         <v>436</v>
       </c>
-      <c r="C73" s="32"/>
-      <c r="D73" s="33"/>
-      <c r="E73" s="34" t="s">
+      <c r="C73" s="31"/>
+      <c r="D73" s="32" t="s">
+        <v>431</v>
+      </c>
+      <c r="E73" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="F73" s="33" t="s">
+      <c r="F73" s="32" t="s">
         <v>437</v>
       </c>
-      <c r="G73" s="35">
+      <c r="G73" s="34">
         <v>2.6585648148148146E-2</v>
       </c>
-      <c r="H73" s="33" t="s">
+      <c r="H73" s="32" t="s">
         <v>244</v>
       </c>
-      <c r="I73" s="33" t="s">
+      <c r="I73" s="32" t="s">
         <v>341</v>
       </c>
-      <c r="J73" s="33" t="s">
+      <c r="J73" s="32" t="s">
         <v>432</v>
       </c>
-      <c r="K73" s="33" t="s">
+      <c r="K73" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="L73" s="33" t="s">
+      <c r="L73" s="32" t="s">
         <v>438</v>
       </c>
-      <c r="M73" s="36" t="s">
+      <c r="M73" s="35" t="s">
         <v>439</v>
       </c>
-      <c r="N73" s="33" t="s">
+      <c r="N73" s="32" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="74" spans="1:14" ht="383.4">
+    <row r="74" spans="1:14" ht="216">
       <c r="A74" s="5">
         <v>73</v>
       </c>
-      <c r="B74" s="37" t="s">
+      <c r="B74" s="36" t="s">
         <v>441</v>
       </c>
-      <c r="C74" s="38" t="s">
+      <c r="C74" s="37" t="s">
         <v>442</v>
       </c>
-      <c r="D74" s="39" t="s">
+      <c r="D74" s="38" t="s">
         <v>443</v>
       </c>
-      <c r="E74" s="40" t="s">
+      <c r="E74" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="F74" s="39" t="s">
+      <c r="F74" s="38" t="s">
         <v>444</v>
       </c>
-      <c r="G74" s="41">
+      <c r="G74" s="40">
         <v>9.5138888888888894E-3</v>
       </c>
-      <c r="H74" s="39" t="s">
+      <c r="H74" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="I74" s="39" t="s">
+      <c r="I74" s="38" t="s">
         <v>58</v>
       </c>
-      <c r="J74" s="39" t="s">
+      <c r="J74" s="38" t="s">
         <v>432</v>
       </c>
-      <c r="K74" s="39" t="s">
+      <c r="K74" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="L74" s="39" t="s">
+      <c r="L74" s="38" t="s">
         <v>445</v>
       </c>
-      <c r="M74" s="42" t="s">
+      <c r="M74" s="41" t="s">
         <v>446</v>
       </c>
-      <c r="N74" s="39" t="s">
+      <c r="N74" s="38" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="75" spans="1:14" ht="409.6" thickBot="1">
+    <row r="75" spans="1:14" ht="234.6" thickBot="1">
       <c r="A75" s="6">
         <v>74</v>
       </c>
-      <c r="B75" s="37" t="s">
+      <c r="B75" s="36" t="s">
         <v>448</v>
       </c>
-      <c r="C75" s="38"/>
-      <c r="D75" s="39"/>
-      <c r="E75" s="40" t="s">
+      <c r="C75" s="37"/>
+      <c r="D75" s="38" t="s">
+        <v>443</v>
+      </c>
+      <c r="E75" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="F75" s="39" t="s">
+      <c r="F75" s="38" t="s">
         <v>449</v>
       </c>
-      <c r="G75" s="41">
+      <c r="G75" s="40">
         <v>1.2141203703703704E-2</v>
       </c>
-      <c r="H75" s="39" t="s">
+      <c r="H75" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="I75" s="39" t="s">
+      <c r="I75" s="38" t="s">
         <v>58</v>
       </c>
-      <c r="J75" s="39" t="s">
+      <c r="J75" s="38" t="s">
         <v>432</v>
       </c>
-      <c r="K75" s="39" t="s">
+      <c r="K75" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="L75" s="39" t="s">
+      <c r="L75" s="38" t="s">
         <v>450</v>
       </c>
-      <c r="M75" s="42" t="s">
+      <c r="M75" s="41" t="s">
         <v>451</v>
       </c>
-      <c r="N75" s="39" t="s">
+      <c r="N75" s="38" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="76" spans="1:14" ht="409.6">
+    <row r="76" spans="1:14" ht="192">
       <c r="A76" s="5">
         <v>75</v>
       </c>
-      <c r="B76" s="43" t="s">
+      <c r="B76" s="42" t="s">
         <v>453</v>
       </c>
-      <c r="C76" s="44" t="s">
+      <c r="C76" s="43" t="s">
         <v>454</v>
       </c>
-      <c r="D76" s="45" t="s">
+      <c r="D76" s="44" t="s">
         <v>455</v>
       </c>
-      <c r="E76" s="46" t="s">
+      <c r="E76" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="F76" s="45" t="s">
+      <c r="F76" s="44" t="s">
         <v>456</v>
       </c>
-      <c r="G76" s="47"/>
-      <c r="H76" s="45" t="s">
+      <c r="G76" s="46"/>
+      <c r="H76" s="44" t="s">
         <v>107</v>
       </c>
-      <c r="I76" s="45" t="s">
+      <c r="I76" s="44" t="s">
         <v>108</v>
       </c>
-      <c r="J76" s="45" t="s">
+      <c r="J76" s="44" t="s">
         <v>457</v>
       </c>
-      <c r="K76" s="45" t="s">
+      <c r="K76" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="L76" s="45" t="s">
+      <c r="L76" s="44" t="s">
         <v>458</v>
       </c>
-      <c r="M76" s="48" t="s">
+      <c r="M76" s="47" t="s">
         <v>459</v>
       </c>
-      <c r="N76" s="45" t="s">
+      <c r="N76" s="44" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="77" spans="1:14" ht="409.6" thickBot="1">
+    <row r="77" spans="1:14" ht="180.6" thickBot="1">
       <c r="A77" s="6">
         <v>76</v>
       </c>
-      <c r="B77" s="43" t="s">
+      <c r="B77" s="42" t="s">
         <v>461</v>
       </c>
-      <c r="C77" s="44"/>
-      <c r="D77" s="45"/>
-      <c r="E77" s="46" t="s">
+      <c r="C77" s="43"/>
+      <c r="D77" s="44" t="s">
+        <v>455</v>
+      </c>
+      <c r="E77" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="F77" s="45" t="s">
+      <c r="F77" s="44" t="s">
         <v>462</v>
       </c>
-      <c r="G77" s="47">
+      <c r="G77" s="46">
         <v>1.1851851851851851E-2</v>
       </c>
-      <c r="H77" s="45" t="s">
+      <c r="H77" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="I77" s="45" t="s">
+      <c r="I77" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="J77" s="45" t="s">
+      <c r="J77" s="44" t="s">
         <v>457</v>
       </c>
-      <c r="K77" s="45" t="s">
+      <c r="K77" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="L77" s="45" t="s">
+      <c r="L77" s="44" t="s">
         <v>463</v>
       </c>
-      <c r="M77" s="48" t="s">
+      <c r="M77" s="47" t="s">
         <v>464</v>
       </c>
-      <c r="N77" s="45" t="s">
+      <c r="N77" s="44" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="78" spans="1:14" ht="409.6">
+    <row r="78" spans="1:14" ht="198">
       <c r="A78" s="5">
         <v>77</v>
       </c>
-      <c r="B78" s="43" t="s">
+      <c r="B78" s="42" t="s">
         <v>466</v>
       </c>
-      <c r="C78" s="44"/>
-      <c r="D78" s="45"/>
-      <c r="E78" s="46" t="s">
+      <c r="C78" s="43"/>
+      <c r="D78" s="44" t="s">
+        <v>455</v>
+      </c>
+      <c r="E78" s="45" t="s">
         <v>27</v>
       </c>
-      <c r="F78" s="45" t="s">
+      <c r="F78" s="44" t="s">
         <v>467</v>
       </c>
-      <c r="G78" s="47">
+      <c r="G78" s="46">
         <v>1.4282407407407407E-2</v>
       </c>
-      <c r="H78" s="45" t="s">
+      <c r="H78" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="I78" s="45" t="s">
+      <c r="I78" s="44" t="s">
         <v>115</v>
       </c>
-      <c r="J78" s="45" t="s">
+      <c r="J78" s="44" t="s">
         <v>457</v>
       </c>
-      <c r="K78" s="45" t="s">
+      <c r="K78" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="L78" s="45" t="s">
+      <c r="L78" s="44" t="s">
         <v>468</v>
       </c>
-      <c r="M78" s="48" t="s">
+      <c r="M78" s="47" t="s">
         <v>469</v>
       </c>
-      <c r="N78" s="45" t="s">
+      <c r="N78" s="44" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="79" spans="1:14" ht="297" thickBot="1">
+    <row r="79" spans="1:14" ht="162.6" thickBot="1">
       <c r="A79" s="6">
         <v>78</v>
       </c>
-      <c r="B79" s="49" t="s">
+      <c r="B79" s="48" t="s">
         <v>471</v>
       </c>
-      <c r="C79" s="50" t="s">
+      <c r="C79" s="49" t="s">
         <v>472</v>
       </c>
-      <c r="D79" s="51" t="s">
+      <c r="D79" s="50" t="s">
         <v>473</v>
       </c>
-      <c r="E79" s="52" t="s">
+      <c r="E79" s="51" t="s">
         <v>15</v>
       </c>
-      <c r="F79" s="53" t="s">
+      <c r="F79" s="52" t="s">
         <v>474</v>
       </c>
-      <c r="G79" s="54">
+      <c r="G79" s="53">
         <v>3.0520833333333334E-2</v>
       </c>
-      <c r="H79" s="53" t="s">
+      <c r="H79" s="52" t="s">
         <v>95</v>
       </c>
-      <c r="I79" s="53" t="s">
+      <c r="I79" s="52" t="s">
         <v>184</v>
       </c>
-      <c r="J79" s="53" t="s">
+      <c r="J79" s="52" t="s">
         <v>432</v>
       </c>
-      <c r="K79" s="53" t="s">
+      <c r="K79" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="L79" s="53" t="s">
+      <c r="L79" s="52" t="s">
         <v>475</v>
       </c>
-      <c r="M79" s="55" t="s">
+      <c r="M79" s="54" t="s">
         <v>476</v>
       </c>
-      <c r="N79" s="53" t="s">
+      <c r="N79" s="52" t="s">
         <v>477</v>
       </c>
     </row>
-    <row r="80" spans="1:14" ht="279">
+    <row r="80" spans="1:14" ht="162">
       <c r="A80" s="5">
         <v>79</v>
       </c>
-      <c r="B80" s="49" t="s">
+      <c r="B80" s="48" t="s">
         <v>478</v>
       </c>
-      <c r="C80" s="50"/>
-      <c r="D80" s="53"/>
-      <c r="E80" s="52" t="s">
+      <c r="C80" s="49"/>
+      <c r="D80" s="50" t="s">
+        <v>473</v>
+      </c>
+      <c r="E80" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="F80" s="53" t="s">
+      <c r="F80" s="52" t="s">
         <v>479</v>
       </c>
-      <c r="G80" s="54">
+      <c r="G80" s="53">
         <v>1.6030092592592592E-2</v>
       </c>
-      <c r="H80" s="53" t="s">
+      <c r="H80" s="52" t="s">
         <v>95</v>
       </c>
-      <c r="I80" s="53" t="s">
+      <c r="I80" s="52" t="s">
         <v>184</v>
       </c>
-      <c r="J80" s="53" t="s">
+      <c r="J80" s="52" t="s">
         <v>432</v>
       </c>
-      <c r="K80" s="53" t="s">
+      <c r="K80" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="L80" s="53" t="s">
+      <c r="L80" s="52" t="s">
         <v>480</v>
       </c>
-      <c r="M80" s="55" t="s">
+      <c r="M80" s="54" t="s">
         <v>481</v>
       </c>
-      <c r="N80" s="53" t="s">
+      <c r="N80" s="52" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="81" spans="1:14" ht="401.4" thickBot="1">
+    <row r="81" spans="1:14" ht="180.6" thickBot="1">
       <c r="A81" s="6">
         <v>80</v>
       </c>
-      <c r="B81" s="49" t="s">
+      <c r="B81" s="48" t="s">
         <v>483</v>
       </c>
-      <c r="C81" s="50"/>
-      <c r="D81" s="53"/>
-      <c r="E81" s="52" t="s">
+      <c r="C81" s="49"/>
+      <c r="D81" s="50" t="s">
+        <v>473</v>
+      </c>
+      <c r="E81" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="F81" s="53" t="s">
+      <c r="F81" s="52" t="s">
         <v>484</v>
       </c>
-      <c r="G81" s="54"/>
-      <c r="H81" s="53" t="s">
+      <c r="G81" s="53"/>
+      <c r="H81" s="52" t="s">
         <v>95</v>
       </c>
-      <c r="I81" s="53" t="s">
+      <c r="I81" s="52" t="s">
         <v>184</v>
       </c>
-      <c r="J81" s="53" t="s">
+      <c r="J81" s="52" t="s">
         <v>432</v>
       </c>
-      <c r="K81" s="53" t="s">
+      <c r="K81" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="L81" s="53" t="s">
+      <c r="L81" s="52" t="s">
         <v>485</v>
       </c>
-      <c r="M81" s="55" t="s">
+      <c r="M81" s="54" t="s">
         <v>486</v>
       </c>
-      <c r="N81" s="53" t="s">
+      <c r="N81" s="52" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="82" spans="1:14" ht="400.8">
+    <row r="82" spans="1:14" ht="180">
       <c r="A82" s="5">
         <v>81</v>
       </c>
-      <c r="B82" s="49" t="s">
+      <c r="B82" s="48" t="s">
         <v>488</v>
       </c>
-      <c r="C82" s="50"/>
-      <c r="D82" s="53"/>
-      <c r="E82" s="52" t="s">
+      <c r="C82" s="49"/>
+      <c r="D82" s="50" t="s">
+        <v>473</v>
+      </c>
+      <c r="E82" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="F82" s="53" t="s">
+      <c r="F82" s="52" t="s">
         <v>489</v>
       </c>
-      <c r="G82" s="54">
+      <c r="G82" s="53">
         <v>1.3668981481481482E-2</v>
       </c>
-      <c r="H82" s="53" t="s">
+      <c r="H82" s="52" t="s">
         <v>95</v>
       </c>
-      <c r="I82" s="53" t="s">
+      <c r="I82" s="52" t="s">
         <v>184</v>
       </c>
-      <c r="J82" s="53" t="s">
+      <c r="J82" s="52" t="s">
         <v>432</v>
       </c>
-      <c r="K82" s="53" t="s">
+      <c r="K82" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="L82" s="53" t="s">
+      <c r="L82" s="52" t="s">
         <v>490</v>
       </c>
-      <c r="M82" s="55" t="s">
+      <c r="M82" s="54" t="s">
         <v>491</v>
       </c>
-      <c r="N82" s="53" t="s">
+      <c r="N82" s="52" t="s">
         <v>492</v>
       </c>
     </row>
-    <row r="83" spans="1:14" ht="409.6" thickBot="1">
+    <row r="83" spans="1:14" ht="198.6" thickBot="1">
       <c r="A83" s="6">
         <v>82</v>
       </c>
-      <c r="B83" s="49" t="s">
+      <c r="B83" s="48" t="s">
         <v>493</v>
       </c>
-      <c r="C83" s="50"/>
-      <c r="D83" s="53"/>
-      <c r="E83" s="52" t="s">
+      <c r="C83" s="49"/>
+      <c r="D83" s="50" t="s">
+        <v>473</v>
+      </c>
+      <c r="E83" s="51" t="s">
         <v>35</v>
       </c>
-      <c r="F83" s="53" t="s">
+      <c r="F83" s="52" t="s">
         <v>494</v>
       </c>
-      <c r="G83" s="54">
+      <c r="G83" s="53">
         <v>8.2060185185185187E-3</v>
       </c>
-      <c r="H83" s="53" t="s">
+      <c r="H83" s="52" t="s">
         <v>95</v>
       </c>
-      <c r="I83" s="53" t="s">
+      <c r="I83" s="52" t="s">
         <v>96</v>
       </c>
-      <c r="J83" s="53" t="s">
+      <c r="J83" s="52" t="s">
         <v>432</v>
       </c>
-      <c r="K83" s="53" t="s">
+      <c r="K83" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="L83" s="53" t="s">
+      <c r="L83" s="52" t="s">
         <v>495</v>
       </c>
-      <c r="M83" s="55" t="s">
+      <c r="M83" s="54" t="s">
         <v>496</v>
       </c>
-      <c r="N83" s="53" t="s">
+      <c r="N83" s="52" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="84" spans="1:14" ht="244.2">
+    <row r="84" spans="1:14" ht="198">
       <c r="A84" s="5">
         <v>83</v>
       </c>
-      <c r="B84" s="56" t="s">
+      <c r="B84" s="55" t="s">
         <v>498</v>
       </c>
-      <c r="C84" s="57" t="s">
+      <c r="C84" s="56" t="s">
         <v>499</v>
       </c>
-      <c r="D84" s="58" t="s">
+      <c r="D84" s="57" t="s">
         <v>500</v>
       </c>
-      <c r="E84" s="59" t="s">
+      <c r="E84" s="58" t="s">
         <v>15</v>
       </c>
-      <c r="F84" s="58" t="s">
+      <c r="F84" s="57" t="s">
         <v>501</v>
       </c>
-      <c r="G84" s="60">
+      <c r="G84" s="59">
         <v>2.1006944444444446E-2</v>
       </c>
-      <c r="H84" s="58" t="s">
+      <c r="H84" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="I84" s="61" t="s">
+      <c r="I84" s="60" t="s">
         <v>502</v>
       </c>
-      <c r="J84" s="61" t="s">
+      <c r="J84" s="60" t="s">
         <v>432</v>
       </c>
-      <c r="K84" s="58" t="s">
+      <c r="K84" s="57" t="s">
         <v>19</v>
       </c>
-      <c r="L84" s="58" t="s">
+      <c r="L84" s="57" t="s">
         <v>503</v>
       </c>
-      <c r="M84" s="62" t="s">
+      <c r="M84" s="61" t="s">
         <v>504</v>
       </c>
-      <c r="N84" s="58" t="s">
+      <c r="N84" s="57" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="85" spans="1:14" ht="349.2" thickBot="1">
+    <row r="85" spans="1:14" ht="180.6" thickBot="1">
       <c r="A85" s="6">
         <v>84</v>
       </c>
-      <c r="B85" s="56" t="s">
+      <c r="B85" s="55" t="s">
         <v>506</v>
       </c>
-      <c r="C85" s="57"/>
-      <c r="D85" s="58"/>
-      <c r="E85" s="59" t="s">
+      <c r="C85" s="56"/>
+      <c r="D85" s="57" t="s">
+        <v>500</v>
+      </c>
+      <c r="E85" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="F85" s="58" t="s">
+      <c r="F85" s="57" t="s">
         <v>507</v>
       </c>
-      <c r="G85" s="60">
+      <c r="G85" s="59">
         <v>2.8229166666666666E-2</v>
       </c>
-      <c r="H85" s="58" t="s">
+      <c r="H85" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="I85" s="61" t="s">
+      <c r="I85" s="60" t="s">
         <v>502</v>
       </c>
-      <c r="J85" s="61" t="s">
+      <c r="J85" s="60" t="s">
         <v>432</v>
       </c>
-      <c r="K85" s="58" t="s">
+      <c r="K85" s="57" t="s">
         <v>19</v>
       </c>
-      <c r="L85" s="58" t="s">
+      <c r="L85" s="57" t="s">
         <v>508</v>
       </c>
-      <c r="M85" s="62" t="s">
+      <c r="M85" s="61" t="s">
         <v>509</v>
       </c>
-      <c r="N85" s="58" t="s">
+      <c r="N85" s="57" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="86" spans="1:14" ht="383.4">
+    <row r="86" spans="1:14" ht="198">
       <c r="A86" s="5">
         <v>85</v>
       </c>
-      <c r="B86" s="56" t="s">
+      <c r="B86" s="55" t="s">
         <v>511</v>
       </c>
-      <c r="C86" s="57"/>
-      <c r="D86" s="58"/>
-      <c r="E86" s="59" t="s">
+      <c r="C86" s="56"/>
+      <c r="D86" s="57" t="s">
+        <v>500</v>
+      </c>
+      <c r="E86" s="58" t="s">
         <v>27</v>
       </c>
-      <c r="F86" s="58" t="s">
+      <c r="F86" s="57" t="s">
         <v>512</v>
       </c>
-      <c r="G86" s="60">
+      <c r="G86" s="59">
         <v>1.9108796296296297E-2</v>
       </c>
-      <c r="H86" s="58" t="s">
+      <c r="H86" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="I86" s="61" t="s">
+      <c r="I86" s="60" t="s">
         <v>502</v>
       </c>
-      <c r="J86" s="61" t="s">
+      <c r="J86" s="60" t="s">
         <v>432</v>
       </c>
-      <c r="K86" s="58" t="s">
+      <c r="K86" s="57" t="s">
         <v>19</v>
       </c>
-      <c r="L86" s="58" t="s">
+      <c r="L86" s="57" t="s">
         <v>513</v>
       </c>
-      <c r="M86" s="62" t="s">
+      <c r="M86" s="61" t="s">
         <v>514</v>
       </c>
-      <c r="N86" s="58" t="s">
+      <c r="N86" s="57" t="s">
         <v>515</v>
       </c>
     </row>
-    <row r="87" spans="1:14" ht="210" thickBot="1">
+    <row r="87" spans="1:14" ht="180.6" thickBot="1">
       <c r="A87" s="6">
         <v>86</v>
       </c>
-      <c r="B87" s="56" t="s">
+      <c r="B87" s="55" t="s">
         <v>516</v>
       </c>
-      <c r="C87" s="57"/>
-      <c r="D87" s="58"/>
-      <c r="E87" s="59" t="s">
+      <c r="C87" s="56"/>
+      <c r="D87" s="57" t="s">
+        <v>500</v>
+      </c>
+      <c r="E87" s="58" t="s">
         <v>31</v>
       </c>
-      <c r="F87" s="58" t="s">
+      <c r="F87" s="57" t="s">
         <v>517</v>
       </c>
-      <c r="G87" s="60">
+      <c r="G87" s="59">
         <v>2.0810185185185185E-2</v>
       </c>
-      <c r="H87" s="58" t="s">
+      <c r="H87" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="I87" s="61" t="s">
+      <c r="I87" s="60" t="s">
         <v>502</v>
       </c>
-      <c r="J87" s="61" t="s">
+      <c r="J87" s="60" t="s">
         <v>432</v>
       </c>
-      <c r="K87" s="58" t="s">
+      <c r="K87" s="57" t="s">
         <v>19</v>
       </c>
-      <c r="L87" s="58" t="s">
+      <c r="L87" s="57" t="s">
         <v>518</v>
       </c>
-      <c r="M87" s="62" t="s">
+      <c r="M87" s="61" t="s">
         <v>519</v>
       </c>
-      <c r="N87" s="58" t="s">
+      <c r="N87" s="57" t="s">
         <v>520</v>
       </c>
     </row>
-    <row r="88" spans="1:14" ht="383.4">
+    <row r="88" spans="1:14" ht="198">
       <c r="A88" s="5">
         <v>87</v>
       </c>
-      <c r="B88" s="56" t="s">
+      <c r="B88" s="55" t="s">
         <v>521</v>
       </c>
-      <c r="C88" s="57"/>
-      <c r="D88" s="58"/>
-      <c r="E88" s="59" t="s">
+      <c r="C88" s="56"/>
+      <c r="D88" s="57" t="s">
+        <v>500</v>
+      </c>
+      <c r="E88" s="58" t="s">
         <v>35</v>
       </c>
-      <c r="F88" s="58" t="s">
+      <c r="F88" s="57" t="s">
         <v>522</v>
       </c>
-      <c r="G88" s="63" t="s">
+      <c r="G88" s="62" t="s">
         <v>523</v>
       </c>
-      <c r="H88" s="58" t="s">
+      <c r="H88" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="I88" s="61" t="s">
+      <c r="I88" s="60" t="s">
         <v>502</v>
       </c>
-      <c r="J88" s="61" t="s">
+      <c r="J88" s="60" t="s">
         <v>432</v>
       </c>
-      <c r="K88" s="58" t="s">
+      <c r="K88" s="57" t="s">
         <v>19</v>
       </c>
-      <c r="L88" s="58" t="s">
+      <c r="L88" s="57" t="s">
         <v>524</v>
       </c>
-      <c r="M88" s="62" t="s">
+      <c r="M88" s="61" t="s">
         <v>525</v>
       </c>
-      <c r="N88" s="58" t="s">
+      <c r="N88" s="57" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="89" spans="1:14" ht="331.8" thickBot="1">
+    <row r="89" spans="1:14" ht="216.6" thickBot="1">
       <c r="A89" s="6">
         <v>88</v>
       </c>
-      <c r="B89" s="56" t="s">
+      <c r="B89" s="55" t="s">
         <v>527</v>
       </c>
-      <c r="C89" s="57"/>
-      <c r="D89" s="58"/>
-      <c r="E89" s="59" t="s">
+      <c r="C89" s="56"/>
+      <c r="D89" s="57" t="s">
+        <v>500</v>
+      </c>
+      <c r="E89" s="58" t="s">
         <v>39</v>
       </c>
-      <c r="F89" s="58" t="s">
+      <c r="F89" s="57" t="s">
         <v>528</v>
       </c>
-      <c r="G89" s="60">
+      <c r="G89" s="59">
         <v>9.3634259259259261E-3</v>
       </c>
-      <c r="H89" s="58" t="s">
+      <c r="H89" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="I89" s="61" t="s">
+      <c r="I89" s="60" t="s">
         <v>502</v>
       </c>
-      <c r="J89" s="61" t="s">
+      <c r="J89" s="60" t="s">
         <v>432</v>
       </c>
-      <c r="K89" s="58" t="s">
+      <c r="K89" s="57" t="s">
         <v>19</v>
       </c>
-      <c r="L89" s="58" t="s">
+      <c r="L89" s="57" t="s">
         <v>529</v>
       </c>
-      <c r="M89" s="62" t="s">
+      <c r="M89" s="61" t="s">
         <v>530</v>
       </c>
-      <c r="N89" s="58" t="s">
+      <c r="N89" s="57" t="s">
         <v>531</v>
       </c>
     </row>
@@ -9208,43 +9360,43 @@
       <c r="A90" s="5">
         <v>89</v>
       </c>
-      <c r="B90" s="64" t="s">
+      <c r="B90" s="63" t="s">
         <v>532</v>
       </c>
-      <c r="C90" s="65" t="s">
+      <c r="C90" s="64" t="s">
         <v>533</v>
       </c>
-      <c r="D90" s="66" t="s">
+      <c r="D90" s="65" t="s">
         <v>534</v>
       </c>
-      <c r="E90" s="67" t="s">
+      <c r="E90" s="66" t="s">
         <v>15</v>
       </c>
-      <c r="F90" s="68" t="s">
+      <c r="F90" s="67" t="s">
         <v>535</v>
       </c>
-      <c r="G90" s="69">
+      <c r="G90" s="68">
         <v>1.2037037037037037E-2</v>
       </c>
-      <c r="H90" s="70" t="s">
+      <c r="H90" s="69" t="s">
         <v>536</v>
       </c>
-      <c r="I90" s="70" t="s">
+      <c r="I90" s="69" t="s">
         <v>252</v>
       </c>
-      <c r="J90" s="70" t="s">
+      <c r="J90" s="69" t="s">
         <v>537</v>
       </c>
-      <c r="K90" s="70" t="s">
+      <c r="K90" s="69" t="s">
         <v>538</v>
       </c>
-      <c r="L90" s="70" t="s">
+      <c r="L90" s="69" t="s">
         <v>539</v>
       </c>
-      <c r="M90" s="71" t="s">
+      <c r="M90" s="70" t="s">
         <v>540</v>
       </c>
-      <c r="N90" s="70" t="s">
+      <c r="N90" s="69" t="s">
         <v>541</v>
       </c>
     </row>
@@ -9252,39 +9404,41 @@
       <c r="A91" s="6">
         <v>90</v>
       </c>
-      <c r="B91" s="64" t="s">
+      <c r="B91" s="63" t="s">
         <v>542</v>
       </c>
-      <c r="C91" s="65"/>
-      <c r="D91" s="70"/>
-      <c r="E91" s="67" t="s">
+      <c r="C91" s="64"/>
+      <c r="D91" s="65" t="s">
+        <v>534</v>
+      </c>
+      <c r="E91" s="66" t="s">
         <v>22</v>
       </c>
-      <c r="F91" s="68" t="s">
+      <c r="F91" s="67" t="s">
         <v>543</v>
       </c>
-      <c r="G91" s="69">
+      <c r="G91" s="68">
         <v>1.2581018518518519E-2</v>
       </c>
-      <c r="H91" s="70" t="s">
+      <c r="H91" s="69" t="s">
         <v>536</v>
       </c>
-      <c r="I91" s="70" t="s">
+      <c r="I91" s="69" t="s">
         <v>252</v>
       </c>
-      <c r="J91" s="70" t="s">
+      <c r="J91" s="69" t="s">
         <v>537</v>
       </c>
-      <c r="K91" s="70" t="s">
+      <c r="K91" s="69" t="s">
         <v>538</v>
       </c>
-      <c r="L91" s="70" t="s">
+      <c r="L91" s="69" t="s">
         <v>544</v>
       </c>
-      <c r="M91" s="71" t="s">
+      <c r="M91" s="70" t="s">
         <v>545</v>
       </c>
-      <c r="N91" s="70" t="s">
+      <c r="N91" s="69" t="s">
         <v>546</v>
       </c>
     </row>
@@ -9292,79 +9446,83 @@
       <c r="A92" s="5">
         <v>91</v>
       </c>
-      <c r="B92" s="64" t="s">
+      <c r="B92" s="63" t="s">
         <v>547</v>
       </c>
-      <c r="C92" s="65"/>
-      <c r="D92" s="70"/>
-      <c r="E92" s="67" t="s">
+      <c r="C92" s="64"/>
+      <c r="D92" s="65" t="s">
+        <v>534</v>
+      </c>
+      <c r="E92" s="66" t="s">
         <v>27</v>
       </c>
-      <c r="F92" s="68" t="s">
+      <c r="F92" s="67" t="s">
         <v>548</v>
       </c>
-      <c r="G92" s="69">
+      <c r="G92" s="68">
         <v>1.7534722222222222E-2</v>
       </c>
-      <c r="H92" s="70" t="s">
+      <c r="H92" s="69" t="s">
         <v>536</v>
       </c>
-      <c r="I92" s="70" t="s">
+      <c r="I92" s="69" t="s">
         <v>252</v>
       </c>
-      <c r="J92" s="70" t="s">
+      <c r="J92" s="69" t="s">
         <v>537</v>
       </c>
-      <c r="K92" s="70" t="s">
+      <c r="K92" s="69" t="s">
         <v>538</v>
       </c>
-      <c r="L92" s="70" t="s">
+      <c r="L92" s="69" t="s">
         <v>549</v>
       </c>
-      <c r="M92" s="71" t="s">
+      <c r="M92" s="70" t="s">
         <v>550</v>
       </c>
-      <c r="N92" s="70" t="s">
+      <c r="N92" s="69" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="93" spans="1:14" ht="144.6" thickBot="1">
+    <row r="93" spans="1:14" ht="162.6" thickBot="1">
       <c r="A93" s="6">
         <v>92</v>
       </c>
-      <c r="B93" s="64" t="s">
+      <c r="B93" s="63" t="s">
         <v>552</v>
       </c>
-      <c r="C93" s="65"/>
-      <c r="D93" s="70"/>
-      <c r="E93" s="67" t="s">
+      <c r="C93" s="64"/>
+      <c r="D93" s="65" t="s">
+        <v>534</v>
+      </c>
+      <c r="E93" s="66" t="s">
         <v>31</v>
       </c>
-      <c r="F93" s="68" t="s">
+      <c r="F93" s="67" t="s">
         <v>553</v>
       </c>
-      <c r="G93" s="69">
+      <c r="G93" s="68">
         <v>2.101851851851852E-2</v>
       </c>
-      <c r="H93" s="70" t="s">
+      <c r="H93" s="69" t="s">
         <v>536</v>
       </c>
-      <c r="I93" s="70" t="s">
+      <c r="I93" s="69" t="s">
         <v>252</v>
       </c>
-      <c r="J93" s="70" t="s">
+      <c r="J93" s="69" t="s">
         <v>537</v>
       </c>
-      <c r="K93" s="70" t="s">
+      <c r="K93" s="69" t="s">
         <v>538</v>
       </c>
-      <c r="L93" s="70" t="s">
+      <c r="L93" s="69" t="s">
         <v>554</v>
       </c>
-      <c r="M93" s="71" t="s">
+      <c r="M93" s="70" t="s">
         <v>555</v>
       </c>
-      <c r="N93" s="70" t="s">
+      <c r="N93" s="69" t="s">
         <v>556</v>
       </c>
     </row>
@@ -9372,43 +9530,43 @@
       <c r="A94" s="5">
         <v>93</v>
       </c>
-      <c r="B94" s="72" t="s">
+      <c r="B94" s="71" t="s">
         <v>557</v>
       </c>
-      <c r="C94" s="73" t="s">
+      <c r="C94" s="72" t="s">
         <v>558</v>
       </c>
-      <c r="D94" s="74" t="s">
+      <c r="D94" s="73" t="s">
         <v>559</v>
       </c>
-      <c r="E94" s="75" t="s">
+      <c r="E94" s="74" t="s">
         <v>15</v>
       </c>
-      <c r="F94" s="76" t="s">
+      <c r="F94" s="75" t="s">
         <v>560</v>
       </c>
-      <c r="G94" s="77">
+      <c r="G94" s="76">
         <v>1.3472222222222222E-2</v>
       </c>
-      <c r="H94" s="74" t="s">
+      <c r="H94" s="73" t="s">
         <v>536</v>
       </c>
-      <c r="I94" s="74" t="s">
+      <c r="I94" s="73" t="s">
         <v>252</v>
       </c>
-      <c r="J94" s="74" t="s">
+      <c r="J94" s="73" t="s">
         <v>561</v>
       </c>
-      <c r="K94" s="74" t="s">
+      <c r="K94" s="73" t="s">
         <v>538</v>
       </c>
-      <c r="L94" s="74" t="s">
+      <c r="L94" s="73" t="s">
         <v>562</v>
       </c>
-      <c r="M94" s="78" t="s">
+      <c r="M94" s="77" t="s">
         <v>563</v>
       </c>
-      <c r="N94" s="74" t="s">
+      <c r="N94" s="73" t="s">
         <v>564</v>
       </c>
     </row>
@@ -9416,39 +9574,41 @@
       <c r="A95" s="6">
         <v>94</v>
       </c>
-      <c r="B95" s="72" t="s">
+      <c r="B95" s="71" t="s">
         <v>565</v>
       </c>
-      <c r="C95" s="73"/>
-      <c r="D95" s="74"/>
-      <c r="E95" s="75" t="s">
+      <c r="C95" s="72"/>
+      <c r="D95" s="73" t="s">
+        <v>559</v>
+      </c>
+      <c r="E95" s="74" t="s">
         <v>22</v>
       </c>
-      <c r="F95" s="76" t="s">
+      <c r="F95" s="75" t="s">
         <v>566</v>
       </c>
-      <c r="G95" s="77">
+      <c r="G95" s="76">
         <v>1.0092592592592592E-2</v>
       </c>
-      <c r="H95" s="74" t="s">
+      <c r="H95" s="73" t="s">
         <v>536</v>
       </c>
-      <c r="I95" s="74" t="s">
+      <c r="I95" s="73" t="s">
         <v>252</v>
       </c>
-      <c r="J95" s="74" t="s">
+      <c r="J95" s="73" t="s">
         <v>561</v>
       </c>
-      <c r="K95" s="74" t="s">
+      <c r="K95" s="73" t="s">
         <v>538</v>
       </c>
-      <c r="L95" s="74" t="s">
+      <c r="L95" s="73" t="s">
         <v>567</v>
       </c>
-      <c r="M95" s="78" t="s">
+      <c r="M95" s="77" t="s">
         <v>568</v>
       </c>
-      <c r="N95" s="74" t="s">
+      <c r="N95" s="73" t="s">
         <v>569</v>
       </c>
     </row>
@@ -9456,39 +9616,41 @@
       <c r="A96" s="5">
         <v>95</v>
       </c>
-      <c r="B96" s="72" t="s">
+      <c r="B96" s="71" t="s">
         <v>570</v>
       </c>
-      <c r="C96" s="73"/>
-      <c r="D96" s="74"/>
-      <c r="E96" s="75" t="s">
+      <c r="C96" s="72"/>
+      <c r="D96" s="73" t="s">
+        <v>559</v>
+      </c>
+      <c r="E96" s="74" t="s">
         <v>27</v>
       </c>
-      <c r="F96" s="76" t="s">
+      <c r="F96" s="75" t="s">
         <v>571</v>
       </c>
-      <c r="G96" s="77">
+      <c r="G96" s="76">
         <v>7.8240740740740736E-3</v>
       </c>
-      <c r="H96" s="74" t="s">
+      <c r="H96" s="73" t="s">
         <v>536</v>
       </c>
-      <c r="I96" s="74" t="s">
+      <c r="I96" s="73" t="s">
         <v>252</v>
       </c>
-      <c r="J96" s="74" t="s">
+      <c r="J96" s="73" t="s">
         <v>572</v>
       </c>
-      <c r="K96" s="74" t="s">
+      <c r="K96" s="73" t="s">
         <v>538</v>
       </c>
-      <c r="L96" s="74" t="s">
+      <c r="L96" s="73" t="s">
         <v>573</v>
       </c>
-      <c r="M96" s="78" t="s">
+      <c r="M96" s="77" t="s">
         <v>574</v>
       </c>
-      <c r="N96" s="74" t="s">
+      <c r="N96" s="73" t="s">
         <v>575</v>
       </c>
     </row>
@@ -9496,39 +9658,41 @@
       <c r="A97" s="6">
         <v>96</v>
       </c>
-      <c r="B97" s="72" t="s">
+      <c r="B97" s="71" t="s">
         <v>576</v>
       </c>
-      <c r="C97" s="73"/>
-      <c r="D97" s="74"/>
-      <c r="E97" s="75" t="s">
+      <c r="C97" s="72"/>
+      <c r="D97" s="73" t="s">
+        <v>559</v>
+      </c>
+      <c r="E97" s="74" t="s">
         <v>31</v>
       </c>
-      <c r="F97" s="76" t="s">
+      <c r="F97" s="75" t="s">
         <v>577</v>
       </c>
-      <c r="G97" s="77">
+      <c r="G97" s="76">
         <v>7.8240740740740736E-3</v>
       </c>
-      <c r="H97" s="74" t="s">
+      <c r="H97" s="73" t="s">
         <v>536</v>
       </c>
-      <c r="I97" s="74" t="s">
+      <c r="I97" s="73" t="s">
         <v>252</v>
       </c>
-      <c r="J97" s="74" t="s">
+      <c r="J97" s="73" t="s">
         <v>578</v>
       </c>
-      <c r="K97" s="74" t="s">
+      <c r="K97" s="73" t="s">
         <v>538</v>
       </c>
-      <c r="L97" s="74" t="s">
+      <c r="L97" s="73" t="s">
         <v>579</v>
       </c>
-      <c r="M97" s="78" t="s">
+      <c r="M97" s="77" t="s">
         <v>580</v>
       </c>
-      <c r="N97" s="74" t="s">
+      <c r="N97" s="73" t="s">
         <v>581</v>
       </c>
     </row>
@@ -9536,123 +9700,127 @@
       <c r="A98" s="5">
         <v>97</v>
       </c>
-      <c r="B98" s="72" t="s">
+      <c r="B98" s="71" t="s">
         <v>582</v>
       </c>
-      <c r="C98" s="73"/>
-      <c r="D98" s="74"/>
-      <c r="E98" s="75" t="s">
+      <c r="C98" s="72"/>
+      <c r="D98" s="73" t="s">
+        <v>559</v>
+      </c>
+      <c r="E98" s="74" t="s">
         <v>35</v>
       </c>
-      <c r="F98" s="76" t="s">
+      <c r="F98" s="75" t="s">
         <v>583</v>
       </c>
-      <c r="G98" s="77">
+      <c r="G98" s="76">
         <v>1.0833333333333334E-2</v>
       </c>
-      <c r="H98" s="74" t="s">
+      <c r="H98" s="73" t="s">
         <v>536</v>
       </c>
-      <c r="I98" s="74" t="s">
+      <c r="I98" s="73" t="s">
         <v>252</v>
       </c>
-      <c r="J98" s="74" t="s">
+      <c r="J98" s="73" t="s">
         <v>537</v>
       </c>
-      <c r="K98" s="74" t="s">
+      <c r="K98" s="73" t="s">
         <v>538</v>
       </c>
-      <c r="L98" s="74" t="s">
+      <c r="L98" s="73" t="s">
         <v>584</v>
       </c>
-      <c r="M98" s="78" t="s">
+      <c r="M98" s="77" t="s">
         <v>585</v>
       </c>
-      <c r="N98" s="74" t="s">
+      <c r="N98" s="73" t="s">
         <v>586</v>
       </c>
     </row>
-    <row r="99" spans="1:14" ht="144.6" thickBot="1">
+    <row r="99" spans="1:14" ht="162.6" thickBot="1">
       <c r="A99" s="6">
         <v>98</v>
       </c>
-      <c r="B99" s="72" t="s">
+      <c r="B99" s="71" t="s">
         <v>587</v>
       </c>
-      <c r="C99" s="73"/>
-      <c r="D99" s="74"/>
-      <c r="E99" s="75" t="s">
+      <c r="C99" s="72"/>
+      <c r="D99" s="73" t="s">
+        <v>559</v>
+      </c>
+      <c r="E99" s="74" t="s">
         <v>39</v>
       </c>
-      <c r="F99" s="76" t="s">
+      <c r="F99" s="75" t="s">
         <v>588</v>
       </c>
-      <c r="G99" s="77">
+      <c r="G99" s="76">
         <v>7.7083333333333335E-3</v>
       </c>
-      <c r="H99" s="74" t="s">
+      <c r="H99" s="73" t="s">
         <v>536</v>
       </c>
-      <c r="I99" s="74" t="s">
+      <c r="I99" s="73" t="s">
         <v>252</v>
       </c>
-      <c r="J99" s="74" t="s">
+      <c r="J99" s="73" t="s">
         <v>572</v>
       </c>
-      <c r="K99" s="74" t="s">
+      <c r="K99" s="73" t="s">
         <v>538</v>
       </c>
-      <c r="L99" s="74" t="s">
+      <c r="L99" s="73" t="s">
         <v>589</v>
       </c>
-      <c r="M99" s="78" t="s">
+      <c r="M99" s="77" t="s">
         <v>590</v>
       </c>
-      <c r="N99" s="74" t="s">
+      <c r="N99" s="73" t="s">
         <v>591</v>
       </c>
     </row>
-    <row r="100" spans="1:14" ht="180">
+    <row r="100" spans="1:14" ht="198">
       <c r="A100" s="5">
         <v>99</v>
       </c>
-      <c r="B100" s="79" t="s">
+      <c r="B100" s="78" t="s">
         <v>592</v>
       </c>
-      <c r="C100" s="80" t="s">
+      <c r="C100" s="79" t="s">
         <v>593</v>
       </c>
-      <c r="D100" s="81" t="s">
+      <c r="D100" s="80" t="s">
         <v>594</v>
       </c>
-      <c r="E100" s="82" t="s">
+      <c r="E100" s="81" t="s">
         <v>15</v>
       </c>
-      <c r="F100" s="83" t="s">
+      <c r="F100" s="82" t="s">
         <v>595</v>
       </c>
-      <c r="G100" s="84">
+      <c r="G100" s="83">
         <v>0.63888888888888884</v>
       </c>
-      <c r="H100" s="81" t="s">
+      <c r="H100" s="80" t="s">
         <v>251</v>
       </c>
-      <c r="I100" s="81" t="s">
+      <c r="I100" s="80" t="s">
         <v>252</v>
       </c>
-      <c r="J100" s="81" t="s">
+      <c r="J100" s="80" t="s">
         <v>572</v>
       </c>
-      <c r="K100" s="81" t="s">
+      <c r="K100" s="80" t="s">
         <v>538</v>
       </c>
-      <c r="L100" s="81" t="s">
+      <c r="L100" s="80" t="s">
         <v>596</v>
       </c>
-      <c r="M100" s="85" t="s">
+      <c r="M100" s="84" t="s">
         <v>597</v>
       </c>
-      <c r="N100" s="81" t="s">
+      <c r="N100" s="80" t="s">
         <v>598</v>
       </c>
     </row>
@@ -9660,39 +9828,41 @@
       <c r="A101" s="6">
         <v>100</v>
       </c>
-      <c r="B101" s="79" t="s">
+      <c r="B101" s="78" t="s">
         <v>599</v>
       </c>
-      <c r="C101" s="80"/>
-      <c r="D101" s="81"/>
-      <c r="E101" s="82" t="s">
+      <c r="C101" s="79"/>
+      <c r="D101" s="80" t="s">
+        <v>594</v>
+      </c>
+      <c r="E101" s="81" t="s">
         <v>22</v>
       </c>
-      <c r="F101" s="83" t="s">
+      <c r="F101" s="82" t="s">
         <v>600</v>
       </c>
-      <c r="G101" s="84">
+      <c r="G101" s="83">
         <v>0.36249999999999999</v>
       </c>
-      <c r="H101" s="81" t="s">
+      <c r="H101" s="80" t="s">
         <v>251</v>
       </c>
-      <c r="I101" s="81" t="s">
+      <c r="I101" s="80" t="s">
         <v>252</v>
       </c>
-      <c r="J101" s="81" t="s">
+      <c r="J101" s="80" t="s">
         <v>572</v>
       </c>
-      <c r="K101" s="81" t="s">
+      <c r="K101" s="80" t="s">
         <v>538</v>
       </c>
-      <c r="L101" s="81" t="s">
+      <c r="L101" s="80" t="s">
         <v>601</v>
       </c>
-      <c r="M101" s="85" t="s">
+      <c r="M101" s="84" t="s">
         <v>602</v>
       </c>
-      <c r="N101" s="81" t="s">
+      <c r="N101" s="80" t="s">
         <v>603</v>
       </c>
     </row>
@@ -9700,39 +9870,41 @@
       <c r="A102" s="5">
         <v>101</v>
       </c>
-      <c r="B102" s="79" t="s">
+      <c r="B102" s="78" t="s">
         <v>604</v>
       </c>
-      <c r="C102" s="80"/>
-      <c r="D102" s="81"/>
-      <c r="E102" s="82" t="s">
+      <c r="C102" s="79"/>
+      <c r="D102" s="80" t="s">
+        <v>594</v>
+      </c>
+      <c r="E102" s="81" t="s">
         <v>27</v>
       </c>
-      <c r="F102" s="83" t="s">
+      <c r="F102" s="82" t="s">
         <v>605</v>
       </c>
-      <c r="G102" s="84">
+      <c r="G102" s="83">
         <v>0.40347222222222223</v>
       </c>
-      <c r="H102" s="81" t="s">
+      <c r="H102" s="80" t="s">
         <v>251</v>
       </c>
-      <c r="I102" s="81" t="s">
+      <c r="I102" s="80" t="s">
         <v>252</v>
       </c>
-      <c r="J102" s="81" t="s">
+      <c r="J102" s="80" t="s">
         <v>572</v>
       </c>
-      <c r="K102" s="81" t="s">
+      <c r="K102" s="80" t="s">
         <v>538</v>
       </c>
-      <c r="L102" s="81" t="s">
+      <c r="L102" s="80" t="s">
         <v>606</v>
       </c>
-      <c r="M102" s="85" t="s">
+      <c r="M102" s="84" t="s">
         <v>607</v>
       </c>
-      <c r="N102" s="81" t="s">
+      <c r="N102" s="80" t="s">
         <v>608</v>
       </c>
     </row>
@@ -9740,39 +9912,41 @@
       <c r="A103" s="6">
         <v>102</v>
       </c>
-      <c r="B103" s="79" t="s">
+      <c r="B103" s="78" t="s">
         <v>609</v>
       </c>
-      <c r="C103" s="80"/>
-      <c r="D103" s="81"/>
-      <c r="E103" s="82" t="s">
+      <c r="C103" s="79"/>
+      <c r="D103" s="80" t="s">
+        <v>594</v>
+      </c>
+      <c r="E103" s="81" t="s">
         <v>31</v>
       </c>
-      <c r="F103" s="83" t="s">
+      <c r="F103" s="82" t="s">
         <v>610</v>
       </c>
-      <c r="G103" s="84">
+      <c r="G103" s="83">
         <v>0.56180555555555556</v>
       </c>
-      <c r="H103" s="81" t="s">
+      <c r="H103" s="80" t="s">
         <v>251</v>
       </c>
-      <c r="I103" s="81" t="s">
+      <c r="I103" s="80" t="s">
         <v>252</v>
       </c>
-      <c r="J103" s="81" t="s">
+      <c r="J103" s="80" t="s">
         <v>572</v>
       </c>
-      <c r="K103" s="81" t="s">
+      <c r="K103" s="80" t="s">
         <v>538</v>
       </c>
-      <c r="L103" s="81" t="s">
+      <c r="L103" s="80" t="s">
         <v>611</v>
       </c>
-      <c r="M103" s="85" t="s">
+      <c r="M103" s="84" t="s">
         <v>612</v>
       </c>
-      <c r="N103" s="81" t="s">
+      <c r="N103" s="80" t="s">
         <v>613</v>
       </c>
     </row>
@@ -9780,39 +9954,41 @@
       <c r="A104" s="5">
         <v>103</v>
       </c>
-      <c r="B104" s="79" t="s">
+      <c r="B104" s="78" t="s">
         <v>614</v>
       </c>
-      <c r="C104" s="80"/>
-      <c r="D104" s="81"/>
-      <c r="E104" s="82" t="s">
+      <c r="C104" s="79"/>
+      <c r="D104" s="80" t="s">
+        <v>594</v>
+      </c>
+      <c r="E104" s="81" t="s">
         <v>35</v>
       </c>
-      <c r="F104" s="83" t="s">
+      <c r="F104" s="82" t="s">
         <v>615</v>
       </c>
-      <c r="G104" s="84">
+      <c r="G104" s="83">
         <v>0.5625</v>
       </c>
-      <c r="H104" s="81" t="s">
+      <c r="H104" s="80" t="s">
         <v>251</v>
       </c>
-      <c r="I104" s="81" t="s">
+      <c r="I104" s="80" t="s">
         <v>252</v>
       </c>
-      <c r="J104" s="81" t="s">
+      <c r="J104" s="80" t="s">
         <v>572</v>
       </c>
-      <c r="K104" s="81" t="s">
+      <c r="K104" s="80" t="s">
         <v>538</v>
       </c>
-      <c r="L104" s="81" t="s">
+      <c r="L104" s="80" t="s">
         <v>616</v>
       </c>
-      <c r="M104" s="85" t="s">
+      <c r="M104" s="84" t="s">
         <v>617</v>
       </c>
-      <c r="N104" s="81" t="s">
+      <c r="N104" s="80" t="s">
         <v>618</v>
       </c>
     </row>
@@ -9820,39 +9996,41 @@
       <c r="A105" s="6">
         <v>104</v>
       </c>
-      <c r="B105" s="79" t="s">
+      <c r="B105" s="78" t="s">
         <v>619</v>
       </c>
-      <c r="C105" s="80"/>
-      <c r="D105" s="81"/>
-      <c r="E105" s="82" t="s">
+      <c r="C105" s="79"/>
+      <c r="D105" s="80" t="s">
+        <v>594</v>
+      </c>
+      <c r="E105" s="81" t="s">
         <v>39</v>
       </c>
-      <c r="F105" s="86" t="s">
+      <c r="F105" s="85" t="s">
         <v>620</v>
       </c>
-      <c r="G105" s="84">
+      <c r="G105" s="83">
         <v>0.35416666666666669</v>
       </c>
-      <c r="H105" s="81" t="s">
+      <c r="H105" s="80" t="s">
         <v>251</v>
       </c>
-      <c r="I105" s="81" t="s">
+      <c r="I105" s="80" t="s">
         <v>252</v>
       </c>
-      <c r="J105" s="81" t="s">
+      <c r="J105" s="80" t="s">
         <v>572</v>
       </c>
-      <c r="K105" s="81" t="s">
+      <c r="K105" s="80" t="s">
         <v>538</v>
       </c>
-      <c r="L105" s="81" t="s">
+      <c r="L105" s="80" t="s">
         <v>621</v>
       </c>
-      <c r="M105" s="85" t="s">
+      <c r="M105" s="84" t="s">
         <v>622</v>
       </c>
-      <c r="N105" s="81" t="s">
+      <c r="N105" s="80" t="s">
         <v>623</v>
       </c>
     </row>
@@ -9860,39 +10038,41 @@
       <c r="A106" s="5">
         <v>105</v>
       </c>
-      <c r="B106" s="79" t="s">
+      <c r="B106" s="78" t="s">
         <v>624</v>
       </c>
-      <c r="C106" s="80"/>
-      <c r="D106" s="81"/>
-      <c r="E106" s="82" t="s">
+      <c r="C106" s="79"/>
+      <c r="D106" s="80" t="s">
+        <v>594</v>
+      </c>
+      <c r="E106" s="81" t="s">
         <v>43</v>
       </c>
-      <c r="F106" s="86" t="s">
+      <c r="F106" s="85" t="s">
         <v>625</v>
       </c>
-      <c r="G106" s="84">
+      <c r="G106" s="83">
         <v>0.52500000000000002</v>
       </c>
-      <c r="H106" s="81" t="s">
+      <c r="H106" s="80" t="s">
         <v>251</v>
       </c>
-      <c r="I106" s="81" t="s">
+      <c r="I106" s="80" t="s">
         <v>252</v>
       </c>
-      <c r="J106" s="81" t="s">
+      <c r="J106" s="80" t="s">
         <v>572</v>
       </c>
-      <c r="K106" s="81" t="s">
+      <c r="K106" s="80" t="s">
         <v>538</v>
       </c>
-      <c r="L106" s="81" t="s">
+      <c r="L106" s="80" t="s">
         <v>626</v>
       </c>
-      <c r="M106" s="85" t="s">
+      <c r="M106" s="84" t="s">
         <v>627</v>
       </c>
-      <c r="N106" s="81" t="s">
+      <c r="N106" s="80" t="s">
         <v>628</v>
       </c>
     </row>
@@ -9900,39 +10080,41 @@
       <c r="A107" s="6">
         <v>106</v>
       </c>
-      <c r="B107" s="79" t="s">
+      <c r="B107" s="78" t="s">
         <v>629</v>
       </c>
-      <c r="C107" s="80"/>
-      <c r="D107" s="81"/>
-      <c r="E107" s="82" t="s">
+      <c r="C107" s="79"/>
+      <c r="D107" s="80" t="s">
+        <v>594</v>
+      </c>
+      <c r="E107" s="81" t="s">
         <v>48</v>
       </c>
-      <c r="F107" s="83" t="s">
+      <c r="F107" s="82" t="s">
         <v>630</v>
       </c>
-      <c r="G107" s="84">
+      <c r="G107" s="83">
         <v>0.4284722222222222</v>
       </c>
-      <c r="H107" s="81" t="s">
+      <c r="H107" s="80" t="s">
         <v>251</v>
       </c>
-      <c r="I107" s="81" t="s">
+      <c r="I107" s="80" t="s">
         <v>252</v>
       </c>
-      <c r="J107" s="81" t="s">
+      <c r="J107" s="80" t="s">
         <v>572</v>
       </c>
-      <c r="K107" s="81" t="s">
+      <c r="K107" s="80" t="s">
         <v>538</v>
       </c>
-      <c r="L107" s="81" t="s">
+      <c r="L107" s="80" t="s">
         <v>631</v>
       </c>
-      <c r="M107" s="85" t="s">
+      <c r="M107" s="84" t="s">
         <v>632</v>
       </c>
-      <c r="N107" s="81" t="s">
+      <c r="N107" s="80" t="s">
         <v>633</v>
       </c>
     </row>
@@ -9940,39 +10122,41 @@
       <c r="A108" s="5">
         <v>107</v>
       </c>
-      <c r="B108" s="79" t="s">
+      <c r="B108" s="78" t="s">
         <v>634</v>
       </c>
-      <c r="C108" s="80"/>
-      <c r="D108" s="81"/>
-      <c r="E108" s="82" t="s">
+      <c r="C108" s="79"/>
+      <c r="D108" s="80" t="s">
+        <v>594</v>
+      </c>
+      <c r="E108" s="81" t="s">
         <v>52</v>
       </c>
-      <c r="F108" s="83" t="s">
+      <c r="F108" s="82" t="s">
         <v>635</v>
       </c>
-      <c r="G108" s="84">
+      <c r="G108" s="83">
         <v>0.5395833333333333</v>
       </c>
-      <c r="H108" s="81" t="s">
+      <c r="H108" s="80" t="s">
         <v>251</v>
       </c>
-      <c r="I108" s="81" t="s">
+      <c r="I108" s="80" t="s">
         <v>252</v>
       </c>
-      <c r="J108" s="81" t="s">
+      <c r="J108" s="80" t="s">
         <v>572</v>
       </c>
-      <c r="K108" s="81" t="s">
+      <c r="K108" s="80" t="s">
         <v>538</v>
       </c>
-      <c r="L108" s="81" t="s">
+      <c r="L108" s="80" t="s">
         <v>636</v>
       </c>
-      <c r="M108" s="85" t="s">
+      <c r="M108" s="84" t="s">
         <v>637</v>
       </c>
-      <c r="N108" s="81" t="s">
+      <c r="N108" s="80" t="s">
         <v>638</v>
       </c>
     </row>
@@ -9980,39 +10164,41 @@
       <c r="A109" s="6">
         <v>108</v>
       </c>
-      <c r="B109" s="79" t="s">
+      <c r="B109" s="78" t="s">
         <v>639</v>
       </c>
-      <c r="C109" s="80"/>
-      <c r="D109" s="81"/>
-      <c r="E109" s="82" t="s">
+      <c r="C109" s="79"/>
+      <c r="D109" s="80" t="s">
+        <v>594</v>
+      </c>
+      <c r="E109" s="81" t="s">
         <v>56</v>
       </c>
-      <c r="F109" s="83" t="s">
+      <c r="F109" s="82" t="s">
         <v>640</v>
       </c>
-      <c r="G109" s="84">
+      <c r="G109" s="83">
         <v>0.62916666666666665</v>
       </c>
-      <c r="H109" s="81" t="s">
+      <c r="H109" s="80" t="s">
         <v>251</v>
       </c>
-      <c r="I109" s="81" t="s">
+      <c r="I109" s="80" t="s">
         <v>252</v>
       </c>
-      <c r="J109" s="81" t="s">
+      <c r="J109" s="80" t="s">
         <v>641</v>
       </c>
-      <c r="K109" s="81" t="s">
+      <c r="K109" s="80" t="s">
         <v>538</v>
       </c>
-      <c r="L109" s="81" t="s">
+      <c r="L109" s="80" t="s">
         <v>642</v>
       </c>
-      <c r="M109" s="85" t="s">
+      <c r="M109" s="84" t="s">
         <v>643</v>
       </c>
-      <c r="N109" s="81" t="s">
+      <c r="N109" s="80" t="s">
         <v>644</v>
       </c>
     </row>
@@ -10020,43 +10206,43 @@
       <c r="A110" s="5">
         <v>109</v>
       </c>
-      <c r="B110" s="87" t="s">
+      <c r="B110" s="86" t="s">
         <v>645</v>
       </c>
-      <c r="C110" s="88" t="s">
+      <c r="C110" s="87" t="s">
         <v>646</v>
       </c>
-      <c r="D110" s="89" t="s">
+      <c r="D110" s="88" t="s">
         <v>647</v>
       </c>
-      <c r="E110" s="90" t="s">
+      <c r="E110" s="89" t="s">
         <v>15</v>
       </c>
-      <c r="F110" s="91" t="s">
+      <c r="F110" s="90" t="s">
         <v>648</v>
       </c>
-      <c r="G110" s="92">
+      <c r="G110" s="91">
         <v>1.2013888888888888E-2</v>
       </c>
-      <c r="H110" s="89" t="s">
+      <c r="H110" s="88" t="s">
         <v>649</v>
       </c>
-      <c r="I110" s="89" t="s">
+      <c r="I110" s="88" t="s">
         <v>341</v>
       </c>
-      <c r="J110" s="89" t="s">
+      <c r="J110" s="88" t="s">
         <v>561</v>
       </c>
-      <c r="K110" s="89" t="s">
+      <c r="K110" s="88" t="s">
         <v>538</v>
       </c>
-      <c r="L110" s="89" t="s">
+      <c r="L110" s="88" t="s">
         <v>650</v>
       </c>
-      <c r="M110" s="93" t="s">
+      <c r="M110" s="92" t="s">
         <v>651</v>
       </c>
-      <c r="N110" s="89" t="s">
+      <c r="N110" s="88" t="s">
         <v>652</v>
       </c>
     </row>
@@ -10064,39 +10250,41 @@
       <c r="A111" s="6">
         <v>110</v>
       </c>
-      <c r="B111" s="87" t="s">
+      <c r="B111" s="86" t="s">
         <v>653</v>
       </c>
-      <c r="C111" s="88"/>
-      <c r="D111" s="89"/>
-      <c r="E111" s="90" t="s">
+      <c r="C111" s="87"/>
+      <c r="D111" s="88" t="s">
+        <v>647</v>
+      </c>
+      <c r="E111" s="89" t="s">
         <v>22</v>
       </c>
-      <c r="F111" s="91" t="s">
+      <c r="F111" s="90" t="s">
         <v>654</v>
       </c>
-      <c r="G111" s="92">
+      <c r="G111" s="91">
         <v>5.4861111111111109E-3</v>
       </c>
-      <c r="H111" s="89" t="s">
+      <c r="H111" s="88" t="s">
         <v>649</v>
       </c>
-      <c r="I111" s="89" t="s">
+      <c r="I111" s="88" t="s">
         <v>341</v>
       </c>
-      <c r="J111" s="89" t="s">
+      <c r="J111" s="88" t="s">
         <v>578</v>
       </c>
-      <c r="K111" s="89" t="s">
+      <c r="K111" s="88" t="s">
         <v>538</v>
       </c>
-      <c r="L111" s="89" t="s">
+      <c r="L111" s="88" t="s">
         <v>655</v>
       </c>
-      <c r="M111" s="93" t="s">
+      <c r="M111" s="92" t="s">
         <v>656</v>
       </c>
-      <c r="N111" s="89" t="s">
+      <c r="N111" s="88" t="s">
         <v>657</v>
       </c>
     </row>
@@ -10104,79 +10292,83 @@
       <c r="A112" s="5">
         <v>111</v>
       </c>
-      <c r="B112" s="87" t="s">
+      <c r="B112" s="86" t="s">
         <v>658</v>
       </c>
-      <c r="C112" s="88"/>
-      <c r="D112" s="89"/>
-      <c r="E112" s="90" t="s">
+      <c r="C112" s="87"/>
+      <c r="D112" s="88" t="s">
+        <v>647</v>
+      </c>
+      <c r="E112" s="89" t="s">
         <v>27</v>
       </c>
-      <c r="F112" s="91" t="s">
+      <c r="F112" s="90" t="s">
         <v>659</v>
       </c>
-      <c r="G112" s="92">
+      <c r="G112" s="91">
         <v>1.4421296296296297E-2</v>
       </c>
-      <c r="H112" s="89" t="s">
+      <c r="H112" s="88" t="s">
         <v>649</v>
       </c>
-      <c r="I112" s="89" t="s">
+      <c r="I112" s="88" t="s">
         <v>341</v>
       </c>
-      <c r="J112" s="89" t="s">
+      <c r="J112" s="88" t="s">
         <v>561</v>
       </c>
-      <c r="K112" s="89" t="s">
+      <c r="K112" s="88" t="s">
         <v>538</v>
       </c>
-      <c r="L112" s="89" t="s">
+      <c r="L112" s="88" t="s">
         <v>660</v>
       </c>
-      <c r="M112" s="93" t="s">
+      <c r="M112" s="92" t="s">
         <v>661</v>
       </c>
-      <c r="N112" s="89" t="s">
+      <c r="N112" s="88" t="s">
         <v>662</v>
       </c>
     </row>
-    <row r="113" spans="1:14" ht="162.6" thickBot="1">
+    <row r="113" spans="1:14" ht="180.6" thickBot="1">
       <c r="A113" s="6">
         <v>112</v>
       </c>
-      <c r="B113" s="87" t="s">
+      <c r="B113" s="86" t="s">
         <v>663</v>
       </c>
-      <c r="C113" s="88"/>
-      <c r="D113" s="89"/>
-      <c r="E113" s="90" t="s">
+      <c r="C113" s="87"/>
+      <c r="D113" s="88" t="s">
+        <v>647</v>
+      </c>
+      <c r="E113" s="89" t="s">
         <v>31</v>
       </c>
-      <c r="F113" s="91" t="s">
+      <c r="F113" s="90" t="s">
         <v>664</v>
       </c>
-      <c r="G113" s="92">
+      <c r="G113" s="91">
         <v>1.050925925925926E-2</v>
       </c>
-      <c r="H113" s="89" t="s">
+      <c r="H113" s="88" t="s">
         <v>649</v>
       </c>
-      <c r="I113" s="89" t="s">
+      <c r="I113" s="88" t="s">
         <v>341</v>
       </c>
-      <c r="J113" s="89" t="s">
+      <c r="J113" s="88" t="s">
         <v>572</v>
       </c>
-      <c r="K113" s="89" t="s">
+      <c r="K113" s="88" t="s">
         <v>538</v>
       </c>
-      <c r="L113" s="89" t="s">
+      <c r="L113" s="88" t="s">
         <v>665</v>
       </c>
-      <c r="M113" s="93" t="s">
+      <c r="M113" s="92" t="s">
         <v>666</v>
       </c>
-      <c r="N113" s="89" t="s">
+      <c r="N113" s="88" t="s">
         <v>667</v>
       </c>
     </row>
@@ -10184,39 +10376,41 @@
       <c r="A114" s="5">
         <v>113</v>
       </c>
-      <c r="B114" s="87" t="s">
+      <c r="B114" s="86" t="s">
         <v>668</v>
       </c>
-      <c r="C114" s="88"/>
-      <c r="D114" s="89"/>
-      <c r="E114" s="90" t="s">
+      <c r="C114" s="87"/>
+      <c r="D114" s="88" t="s">
+        <v>647</v>
+      </c>
+      <c r="E114" s="89" t="s">
         <v>35</v>
       </c>
-      <c r="F114" s="91" t="s">
+      <c r="F114" s="90" t="s">
         <v>669</v>
       </c>
-      <c r="G114" s="92">
+      <c r="G114" s="91">
         <v>9.8958333333333329E-3</v>
       </c>
-      <c r="H114" s="89" t="s">
+      <c r="H114" s="88" t="s">
         <v>649</v>
       </c>
-      <c r="I114" s="89" t="s">
+      <c r="I114" s="88" t="s">
         <v>341</v>
       </c>
-      <c r="J114" s="89" t="s">
+      <c r="J114" s="88" t="s">
         <v>572</v>
       </c>
-      <c r="K114" s="89" t="s">
+      <c r="K114" s="88" t="s">
         <v>538</v>
       </c>
-      <c r="L114" s="89" t="s">
+      <c r="L114" s="88" t="s">
         <v>670</v>
       </c>
-      <c r="M114" s="93" t="s">
+      <c r="M114" s="92" t="s">
         <v>671</v>
       </c>
-      <c r="N114" s="89" t="s">
+      <c r="N114" s="88" t="s">
         <v>672</v>
       </c>
     </row>
@@ -10224,39 +10418,41 @@
       <c r="A115" s="6">
         <v>114</v>
       </c>
-      <c r="B115" s="87" t="s">
+      <c r="B115" s="86" t="s">
         <v>673</v>
       </c>
-      <c r="C115" s="88"/>
-      <c r="D115" s="89"/>
-      <c r="E115" s="90" t="s">
+      <c r="C115" s="87"/>
+      <c r="D115" s="88" t="s">
+        <v>647</v>
+      </c>
+      <c r="E115" s="89" t="s">
         <v>39</v>
       </c>
-      <c r="F115" s="91" t="s">
+      <c r="F115" s="90" t="s">
         <v>674</v>
       </c>
-      <c r="G115" s="92">
+      <c r="G115" s="91">
         <v>5.7754629629629631E-3</v>
       </c>
-      <c r="H115" s="89" t="s">
+      <c r="H115" s="88" t="s">
         <v>649</v>
       </c>
-      <c r="I115" s="89" t="s">
+      <c r="I115" s="88" t="s">
         <v>341</v>
       </c>
-      <c r="J115" s="89" t="s">
+      <c r="J115" s="88" t="s">
         <v>578</v>
       </c>
-      <c r="K115" s="89" t="s">
+      <c r="K115" s="88" t="s">
         <v>538</v>
       </c>
-      <c r="L115" s="89" t="s">
+      <c r="L115" s="88" t="s">
         <v>675</v>
       </c>
-      <c r="M115" s="93" t="s">
+      <c r="M115" s="92" t="s">
         <v>676</v>
       </c>
-      <c r="N115" s="89" t="s">
+      <c r="N115" s="88" t="s">
         <v>677</v>
       </c>
     </row>
@@ -10264,39 +10460,41 @@
       <c r="A116" s="5">
         <v>115</v>
       </c>
-      <c r="B116" s="87" t="s">
+      <c r="B116" s="86" t="s">
         <v>678</v>
       </c>
-      <c r="C116" s="88"/>
-      <c r="D116" s="89"/>
-      <c r="E116" s="90" t="s">
+      <c r="C116" s="87"/>
+      <c r="D116" s="88" t="s">
+        <v>647</v>
+      </c>
+      <c r="E116" s="89" t="s">
         <v>43</v>
       </c>
-      <c r="F116" s="91" t="s">
+      <c r="F116" s="90" t="s">
         <v>679</v>
       </c>
-      <c r="G116" s="92">
+      <c r="G116" s="91">
         <v>1.150462962962963E-2</v>
       </c>
-      <c r="H116" s="89" t="s">
+      <c r="H116" s="88" t="s">
         <v>649</v>
       </c>
-      <c r="I116" s="89" t="s">
+      <c r="I116" s="88" t="s">
         <v>341</v>
       </c>
-      <c r="J116" s="89" t="s">
+      <c r="J116" s="88" t="s">
         <v>572</v>
       </c>
-      <c r="K116" s="89" t="s">
+      <c r="K116" s="88" t="s">
         <v>538</v>
       </c>
-      <c r="L116" s="89" t="s">
+      <c r="L116" s="88" t="s">
         <v>680</v>
       </c>
-      <c r="M116" s="93" t="s">
+      <c r="M116" s="92" t="s">
         <v>681</v>
       </c>
-      <c r="N116" s="89" t="s">
+      <c r="N116" s="88" t="s">
         <v>682</v>
       </c>
     </row>
@@ -10304,39 +10502,41 @@
       <c r="A117" s="6">
         <v>116</v>
       </c>
-      <c r="B117" s="87" t="s">
+      <c r="B117" s="86" t="s">
         <v>683</v>
       </c>
-      <c r="C117" s="88"/>
-      <c r="D117" s="89"/>
-      <c r="E117" s="90" t="s">
+      <c r="C117" s="87"/>
+      <c r="D117" s="88" t="s">
+        <v>647</v>
+      </c>
+      <c r="E117" s="89" t="s">
         <v>48</v>
       </c>
-      <c r="F117" s="94" t="s">
+      <c r="F117" s="93" t="s">
         <v>684</v>
       </c>
-      <c r="G117" s="92">
+      <c r="G117" s="91">
         <v>5.092592592592593E-3</v>
       </c>
-      <c r="H117" s="89" t="s">
+      <c r="H117" s="88" t="s">
         <v>649</v>
       </c>
-      <c r="I117" s="89" t="s">
+      <c r="I117" s="88" t="s">
         <v>341</v>
       </c>
-      <c r="J117" s="89" t="s">
+      <c r="J117" s="88" t="s">
         <v>578</v>
       </c>
-      <c r="K117" s="89" t="s">
+      <c r="K117" s="88" t="s">
         <v>538</v>
       </c>
-      <c r="L117" s="89" t="s">
+      <c r="L117" s="88" t="s">
         <v>685</v>
       </c>
-      <c r="M117" s="93" t="s">
+      <c r="M117" s="92" t="s">
         <v>686</v>
       </c>
-      <c r="N117" s="89" t="s">
+      <c r="N117" s="88" t="s">
         <v>687</v>
       </c>
     </row>
@@ -10344,39 +10544,41 @@
       <c r="A118" s="5">
         <v>117</v>
       </c>
-      <c r="B118" s="87" t="s">
+      <c r="B118" s="86" t="s">
         <v>688</v>
       </c>
-      <c r="C118" s="88"/>
-      <c r="D118" s="89"/>
-      <c r="E118" s="90" t="s">
+      <c r="C118" s="87"/>
+      <c r="D118" s="88" t="s">
+        <v>647</v>
+      </c>
+      <c r="E118" s="89" t="s">
         <v>52</v>
       </c>
-      <c r="F118" s="91" t="s">
+      <c r="F118" s="90" t="s">
         <v>689</v>
       </c>
-      <c r="G118" s="92">
+      <c r="G118" s="91">
         <v>8.1481481481481474E-3</v>
       </c>
-      <c r="H118" s="89" t="s">
+      <c r="H118" s="88" t="s">
         <v>649</v>
       </c>
-      <c r="I118" s="89" t="s">
+      <c r="I118" s="88" t="s">
         <v>341</v>
       </c>
-      <c r="J118" s="89" t="s">
+      <c r="J118" s="88" t="s">
         <v>572</v>
       </c>
-      <c r="K118" s="89" t="s">
+      <c r="K118" s="88" t="s">
         <v>538</v>
       </c>
-      <c r="L118" s="89" t="s">
+      <c r="L118" s="88" t="s">
         <v>690</v>
       </c>
-      <c r="M118" s="93" t="s">
+      <c r="M118" s="92" t="s">
         <v>691</v>
       </c>
-      <c r="N118" s="89" t="s">
+      <c r="N118" s="88" t="s">
         <v>692</v>
       </c>
     </row>
@@ -10384,39 +10586,41 @@
       <c r="A119" s="6">
         <v>118</v>
       </c>
-      <c r="B119" s="87" t="s">
+      <c r="B119" s="86" t="s">
         <v>693</v>
       </c>
-      <c r="C119" s="88"/>
-      <c r="D119" s="89"/>
-      <c r="E119" s="90" t="s">
+      <c r="C119" s="87"/>
+      <c r="D119" s="88" t="s">
+        <v>647</v>
+      </c>
+      <c r="E119" s="89" t="s">
         <v>56</v>
       </c>
-      <c r="F119" s="94" t="s">
+      <c r="F119" s="93" t="s">
         <v>694</v>
       </c>
-      <c r="G119" s="92">
+      <c r="G119" s="91">
         <v>8.9583333333333338E-3</v>
       </c>
-      <c r="H119" s="89" t="s">
+      <c r="H119" s="88" t="s">
         <v>649</v>
       </c>
-      <c r="I119" s="89" t="s">
+      <c r="I119" s="88" t="s">
         <v>341</v>
       </c>
-      <c r="J119" s="89" t="s">
+      <c r="J119" s="88" t="s">
         <v>561</v>
       </c>
-      <c r="K119" s="89" t="s">
+      <c r="K119" s="88" t="s">
         <v>538</v>
       </c>
-      <c r="L119" s="89" t="s">
+      <c r="L119" s="88" t="s">
         <v>695</v>
       </c>
-      <c r="M119" s="93" t="s">
+      <c r="M119" s="92" t="s">
         <v>696</v>
       </c>
-      <c r="N119" s="89" t="s">
+      <c r="N119" s="88" t="s">
         <v>697</v>
       </c>
     </row>
@@ -10424,39 +10628,41 @@
       <c r="A120" s="5">
         <v>119</v>
       </c>
-      <c r="B120" s="87" t="s">
+      <c r="B120" s="86" t="s">
         <v>698</v>
       </c>
-      <c r="C120" s="88"/>
-      <c r="D120" s="89"/>
-      <c r="E120" s="90" t="s">
+      <c r="C120" s="87"/>
+      <c r="D120" s="88" t="s">
+        <v>647</v>
+      </c>
+      <c r="E120" s="89" t="s">
         <v>61</v>
       </c>
-      <c r="F120" s="91" t="s">
+      <c r="F120" s="90" t="s">
         <v>699</v>
       </c>
-      <c r="G120" s="92">
+      <c r="G120" s="91">
         <v>1.0185185185185186E-2</v>
       </c>
-      <c r="H120" s="89" t="s">
+      <c r="H120" s="88" t="s">
         <v>649</v>
       </c>
-      <c r="I120" s="89" t="s">
+      <c r="I120" s="88" t="s">
         <v>341</v>
       </c>
-      <c r="J120" s="89" t="s">
+      <c r="J120" s="88" t="s">
         <v>561</v>
       </c>
-      <c r="K120" s="89" t="s">
+      <c r="K120" s="88" t="s">
         <v>538</v>
       </c>
-      <c r="L120" s="89" t="s">
+      <c r="L120" s="88" t="s">
         <v>700</v>
       </c>
-      <c r="M120" s="93" t="s">
+      <c r="M120" s="92" t="s">
         <v>701</v>
       </c>
-      <c r="N120" s="89" t="s">
+      <c r="N120" s="88" t="s">
         <v>702</v>
       </c>
     </row>
@@ -10464,41 +10670,41 @@
       <c r="A121" s="6">
         <v>120</v>
       </c>
-      <c r="B121" s="95"/>
-      <c r="C121" s="96" t="s">
+      <c r="B121" s="94"/>
+      <c r="C121" s="95" t="s">
         <v>104</v>
       </c>
-      <c r="D121" s="97" t="s">
+      <c r="D121" s="96" t="s">
         <v>703</v>
       </c>
-      <c r="E121" s="98">
+      <c r="E121" s="97">
         <v>1</v>
       </c>
-      <c r="F121" s="99" t="s">
+      <c r="F121" s="98" t="s">
         <v>704</v>
       </c>
-      <c r="G121" s="100">
+      <c r="G121" s="99">
         <v>1.5636574074074074E-2</v>
       </c>
-      <c r="H121" s="97" t="s">
+      <c r="H121" s="96" t="s">
         <v>244</v>
       </c>
-      <c r="I121" s="97" t="s">
+      <c r="I121" s="96" t="s">
         <v>245</v>
       </c>
-      <c r="J121" s="97" t="s">
+      <c r="J121" s="96" t="s">
         <v>705</v>
       </c>
-      <c r="K121" s="97" t="s">
+      <c r="K121" s="96" t="s">
         <v>538</v>
       </c>
-      <c r="L121" s="97" t="s">
+      <c r="L121" s="96" t="s">
         <v>706</v>
       </c>
-      <c r="M121" s="101" t="s">
+      <c r="M121" s="100" t="s">
         <v>707</v>
       </c>
-      <c r="N121" s="97" t="s">
+      <c r="N121" s="96" t="s">
         <v>708</v>
       </c>
     </row>
@@ -10506,113 +10712,119 @@
       <c r="A122" s="5">
         <v>121</v>
       </c>
-      <c r="B122" s="95"/>
-      <c r="C122" s="96"/>
-      <c r="D122" s="97"/>
-      <c r="E122" s="98">
+      <c r="B122" s="94"/>
+      <c r="C122" s="95"/>
+      <c r="D122" s="96" t="s">
+        <v>703</v>
+      </c>
+      <c r="E122" s="97">
         <v>2</v>
       </c>
-      <c r="F122" s="99" t="s">
+      <c r="F122" s="98" t="s">
         <v>709</v>
       </c>
-      <c r="G122" s="100">
+      <c r="G122" s="99">
         <v>1.173611111111111E-2</v>
       </c>
-      <c r="H122" s="97" t="s">
+      <c r="H122" s="96" t="s">
         <v>244</v>
       </c>
-      <c r="I122" s="97" t="s">
+      <c r="I122" s="96" t="s">
         <v>245</v>
       </c>
-      <c r="J122" s="97" t="s">
+      <c r="J122" s="96" t="s">
         <v>705</v>
       </c>
-      <c r="K122" s="97" t="s">
+      <c r="K122" s="96" t="s">
         <v>538</v>
       </c>
-      <c r="L122" s="97" t="s">
+      <c r="L122" s="96" t="s">
         <v>710</v>
       </c>
-      <c r="M122" s="101" t="s">
+      <c r="M122" s="100" t="s">
         <v>711</v>
       </c>
-      <c r="N122" s="97" t="s">
+      <c r="N122" s="96" t="s">
         <v>712</v>
       </c>
     </row>
-    <row r="123" spans="1:14" ht="180.6" thickBot="1">
+    <row r="123" spans="1:14" ht="198.6" thickBot="1">
       <c r="A123" s="6">
         <v>122</v>
       </c>
-      <c r="B123" s="95"/>
-      <c r="C123" s="96"/>
-      <c r="D123" s="97"/>
-      <c r="E123" s="98">
+      <c r="B123" s="94"/>
+      <c r="C123" s="95"/>
+      <c r="D123" s="96" t="s">
+        <v>703</v>
+      </c>
+      <c r="E123" s="97">
         <v>3</v>
       </c>
-      <c r="F123" s="99" t="s">
+      <c r="F123" s="98" t="s">
         <v>713</v>
       </c>
-      <c r="G123" s="100">
+      <c r="G123" s="99">
         <v>2.0960648148148148E-2</v>
       </c>
-      <c r="H123" s="97" t="s">
+      <c r="H123" s="96" t="s">
         <v>244</v>
       </c>
-      <c r="I123" s="97" t="s">
+      <c r="I123" s="96" t="s">
         <v>245</v>
       </c>
-      <c r="J123" s="97" t="s">
+      <c r="J123" s="96" t="s">
         <v>705</v>
       </c>
-      <c r="K123" s="97" t="s">
+      <c r="K123" s="96" t="s">
         <v>538</v>
       </c>
-      <c r="L123" s="97" t="s">
+      <c r="L123" s="96" t="s">
         <v>714</v>
       </c>
-      <c r="M123" s="101" t="s">
+      <c r="M123" s="100" t="s">
         <v>715</v>
       </c>
-      <c r="N123" s="97" t="s">
+      <c r="N123" s="96" t="s">
         <v>716</v>
       </c>
     </row>
-    <row r="124" spans="1:14" ht="198">
+    <row r="124" spans="1:14" ht="216">
       <c r="A124" s="5">
         <v>123</v>
       </c>
-      <c r="B124" s="95"/>
-      <c r="C124" s="96"/>
-      <c r="D124" s="97"/>
-      <c r="E124" s="98">
+      <c r="B124" s="94"/>
+      <c r="C124" s="95"/>
+      <c r="D124" s="96" t="s">
+        <v>703</v>
+      </c>
+      <c r="E124" s="97">
         <v>4</v>
       </c>
-      <c r="F124" s="99" t="s">
+      <c r="F124" s="98" t="s">
         <v>717</v>
       </c>
-      <c r="G124" s="100">
+      <c r="G124" s="99">
         <v>2.193287037037037E-2</v>
       </c>
-      <c r="H124" s="97" t="s">
+      <c r="H124" s="96" t="s">
         <v>244</v>
       </c>
-      <c r="I124" s="97" t="s">
+      <c r="I124" s="96" t="s">
         <v>245</v>
       </c>
-      <c r="J124" s="97" t="s">
+      <c r="J124" s="96" t="s">
         <v>705</v>
       </c>
-      <c r="K124" s="97" t="s">
+      <c r="K124" s="96" t="s">
         <v>538</v>
       </c>
-      <c r="L124" s="97" t="s">
+      <c r="L124" s="96" t="s">
         <v>718</v>
       </c>
-      <c r="M124" s="101" t="s">
+      <c r="M124" s="100" t="s">
         <v>719</v>
       </c>
-      <c r="N124" s="97" t="s">
+      <c r="N124" s="96" t="s">
         <v>720</v>
       </c>
     </row>
@@ -10620,37 +10832,39 @@
       <c r="A125" s="6">
         <v>124</v>
       </c>
-      <c r="B125" s="95"/>
-      <c r="C125" s="96"/>
-      <c r="D125" s="97"/>
-      <c r="E125" s="98">
+      <c r="B125" s="94"/>
+      <c r="C125" s="95"/>
+      <c r="D125" s="96" t="s">
+        <v>703</v>
+      </c>
+      <c r="E125" s="97">
         <v>5</v>
       </c>
-      <c r="F125" s="99" t="s">
+      <c r="F125" s="98" t="s">
         <v>721</v>
       </c>
-      <c r="G125" s="100">
+      <c r="G125" s="99">
         <v>1.3865740740740741E-2</v>
       </c>
-      <c r="H125" s="97" t="s">
+      <c r="H125" s="96" t="s">
         <v>244</v>
       </c>
-      <c r="I125" s="97" t="s">
+      <c r="I125" s="96" t="s">
         <v>245</v>
       </c>
-      <c r="J125" s="97" t="s">
+      <c r="J125" s="96" t="s">
         <v>705</v>
       </c>
-      <c r="K125" s="97" t="s">
+      <c r="K125" s="96" t="s">
         <v>538</v>
       </c>
-      <c r="L125" s="97" t="s">
+      <c r="L125" s="96" t="s">
         <v>722</v>
       </c>
-      <c r="M125" s="101" t="s">
+      <c r="M125" s="100" t="s">
         <v>723</v>
       </c>
-      <c r="N125" s="97" t="s">
+      <c r="N125" s="96" t="s">
         <v>724</v>
       </c>
     </row>
@@ -10658,37 +10872,39 @@
       <c r="A126" s="5">
         <v>125</v>
       </c>
-      <c r="B126" s="95"/>
-      <c r="C126" s="96"/>
-      <c r="D126" s="97"/>
-      <c r="E126" s="98">
+      <c r="B126" s="94"/>
+      <c r="C126" s="95"/>
+      <c r="D126" s="96" t="s">
+        <v>703</v>
+      </c>
+      <c r="E126" s="97">
         <v>6</v>
       </c>
-      <c r="F126" s="99" t="s">
+      <c r="F126" s="98" t="s">
         <v>725</v>
       </c>
-      <c r="G126" s="100">
+      <c r="G126" s="99">
         <v>1.1296296296296296E-2</v>
       </c>
-      <c r="H126" s="97" t="s">
+      <c r="H126" s="96" t="s">
         <v>244</v>
       </c>
-      <c r="I126" s="97" t="s">
+      <c r="I126" s="96" t="s">
         <v>245</v>
       </c>
-      <c r="J126" s="97" t="s">
+      <c r="J126" s="96" t="s">
         <v>705</v>
       </c>
-      <c r="K126" s="97" t="s">
+      <c r="K126" s="96" t="s">
         <v>538</v>
       </c>
-      <c r="L126" s="97" t="s">
+      <c r="L126" s="96" t="s">
         <v>726</v>
       </c>
-      <c r="M126" s="101" t="s">
+      <c r="M126" s="100" t="s">
         <v>727</v>
       </c>
-      <c r="N126" s="97" t="s">
+      <c r="N126" s="96" t="s">
         <v>728</v>
       </c>
     </row>
@@ -10696,37 +10912,39 @@
       <c r="A127" s="6">
         <v>126</v>
       </c>
-      <c r="B127" s="95"/>
-      <c r="C127" s="96"/>
-      <c r="D127" s="97"/>
-      <c r="E127" s="98">
+      <c r="B127" s="94"/>
+      <c r="C127" s="95"/>
+      <c r="D127" s="96" t="s">
+        <v>703</v>
+      </c>
+      <c r="E127" s="97">
         <v>7</v>
       </c>
-      <c r="F127" s="99" t="s">
+      <c r="F127" s="98" t="s">
         <v>729</v>
       </c>
-      <c r="G127" s="100">
+      <c r="G127" s="99">
         <v>1.6736111111111111E-2</v>
       </c>
-      <c r="H127" s="97" t="s">
+      <c r="H127" s="96" t="s">
         <v>244</v>
       </c>
-      <c r="I127" s="97" t="s">
+      <c r="I127" s="96" t="s">
         <v>245</v>
       </c>
-      <c r="J127" s="97" t="s">
+      <c r="J127" s="96" t="s">
         <v>705</v>
       </c>
-      <c r="K127" s="97" t="s">
+      <c r="K127" s="96" t="s">
         <v>538</v>
       </c>
-      <c r="L127" s="97" t="s">
+      <c r="L127" s="96" t="s">
         <v>730</v>
       </c>
-      <c r="M127" s="101" t="s">
+      <c r="M127" s="100" t="s">
         <v>731</v>
       </c>
-      <c r="N127" s="97" t="s">
+      <c r="N127" s="96" t="s">
         <v>732</v>
       </c>
     </row>
@@ -10734,41 +10952,41 @@
       <c r="A128" s="5">
         <v>127</v>
       </c>
-      <c r="B128" s="102"/>
-      <c r="C128" s="103" t="s">
+      <c r="B128" s="101"/>
+      <c r="C128" s="102" t="s">
         <v>141</v>
       </c>
-      <c r="D128" s="104" t="s">
+      <c r="D128" s="103" t="s">
         <v>733</v>
       </c>
-      <c r="E128" s="105">
+      <c r="E128" s="104">
         <v>1</v>
       </c>
-      <c r="F128" s="106" t="s">
+      <c r="F128" s="105" t="s">
         <v>734</v>
       </c>
-      <c r="G128" s="107">
+      <c r="G128" s="106">
         <v>1.2847222222222222E-2</v>
       </c>
-      <c r="H128" s="104" t="s">
+      <c r="H128" s="103" t="s">
         <v>251</v>
       </c>
-      <c r="I128" s="104" t="s">
+      <c r="I128" s="103" t="s">
         <v>735</v>
       </c>
-      <c r="J128" s="104" t="s">
+      <c r="J128" s="103" t="s">
         <v>705</v>
       </c>
-      <c r="K128" s="104" t="s">
+      <c r="K128" s="103" t="s">
         <v>538</v>
       </c>
-      <c r="L128" s="104" t="s">
+      <c r="L128" s="103" t="s">
         <v>736</v>
       </c>
-      <c r="M128" s="108" t="s">
+      <c r="M128" s="107" t="s">
         <v>737</v>
       </c>
-      <c r="N128" s="104" t="s">
+      <c r="N128" s="103" t="s">
         <v>738</v>
       </c>
     </row>
@@ -10776,37 +10994,39 @@
       <c r="A129" s="6">
         <v>128</v>
       </c>
-      <c r="B129" s="102"/>
-      <c r="C129" s="103"/>
-      <c r="D129" s="104"/>
-      <c r="E129" s="105">
+      <c r="B129" s="101"/>
+      <c r="C129" s="102"/>
+      <c r="D129" s="103" t="s">
+        <v>733</v>
+      </c>
+      <c r="E129" s="104">
         <v>2</v>
       </c>
-      <c r="F129" s="106" t="s">
+      <c r="F129" s="105" t="s">
         <v>739</v>
       </c>
-      <c r="G129" s="107">
+      <c r="G129" s="106">
         <v>1.068287037037037E-2</v>
       </c>
-      <c r="H129" s="104" t="s">
+      <c r="H129" s="103" t="s">
         <v>374</v>
       </c>
-      <c r="I129" s="104" t="s">
+      <c r="I129" s="103" t="s">
         <v>189</v>
       </c>
-      <c r="J129" s="104" t="s">
+      <c r="J129" s="103" t="s">
         <v>705</v>
       </c>
-      <c r="K129" s="104" t="s">
+      <c r="K129" s="103" t="s">
         <v>538</v>
       </c>
-      <c r="L129" s="104" t="s">
+      <c r="L129" s="103" t="s">
         <v>740</v>
       </c>
-      <c r="M129" s="108" t="s">
+      <c r="M129" s="107" t="s">
         <v>741</v>
       </c>
-      <c r="N129" s="104" t="s">
+      <c r="N129" s="103" t="s">
         <v>742</v>
       </c>
     </row>
@@ -10814,37 +11034,39 @@
       <c r="A130" s="5">
         <v>129</v>
       </c>
-      <c r="B130" s="102"/>
-      <c r="C130" s="103"/>
-      <c r="D130" s="104"/>
-      <c r="E130" s="105">
+      <c r="B130" s="101"/>
+      <c r="C130" s="102"/>
+      <c r="D130" s="103" t="s">
+        <v>733</v>
+      </c>
+      <c r="E130" s="104">
         <v>3</v>
       </c>
-      <c r="F130" s="106" t="s">
+      <c r="F130" s="105" t="s">
         <v>743</v>
       </c>
-      <c r="G130" s="107">
+      <c r="G130" s="106">
         <v>1.1111111111111112E-2</v>
       </c>
-      <c r="H130" s="104" t="s">
+      <c r="H130" s="103" t="s">
         <v>251</v>
       </c>
-      <c r="I130" s="104" t="s">
+      <c r="I130" s="103" t="s">
         <v>735</v>
       </c>
-      <c r="J130" s="104" t="s">
+      <c r="J130" s="103" t="s">
         <v>705</v>
       </c>
-      <c r="K130" s="104" t="s">
+      <c r="K130" s="103" t="s">
         <v>538</v>
       </c>
-      <c r="L130" s="104" t="s">
+      <c r="L130" s="103" t="s">
         <v>744</v>
       </c>
-      <c r="M130" s="108" t="s">
+      <c r="M130" s="107" t="s">
         <v>745</v>
       </c>
-      <c r="N130" s="104" t="s">
+      <c r="N130" s="103" t="s">
         <v>746</v>
       </c>
     </row>
@@ -10852,37 +11074,39 @@
       <c r="A131" s="6">
         <v>130</v>
       </c>
-      <c r="B131" s="102"/>
-      <c r="C131" s="103"/>
-      <c r="D131" s="104"/>
-      <c r="E131" s="105">
+      <c r="B131" s="101"/>
+      <c r="C131" s="102"/>
+      <c r="D131" s="103" t="s">
+        <v>733</v>
+      </c>
+      <c r="E131" s="104">
         <v>4</v>
       </c>
-      <c r="F131" s="106" t="s">
+      <c r="F131" s="105" t="s">
         <v>747</v>
       </c>
-      <c r="G131" s="107">
+      <c r="G131" s="106">
         <v>1.1712962962962963E-2</v>
       </c>
-      <c r="H131" s="104" t="s">
+      <c r="H131" s="103" t="s">
         <v>95</v>
       </c>
-      <c r="I131" s="104" t="s">
+      <c r="I131" s="103" t="s">
         <v>748</v>
       </c>
-      <c r="J131" s="104" t="s">
+      <c r="J131" s="103" t="s">
         <v>705</v>
       </c>
-      <c r="K131" s="104" t="s">
+      <c r="K131" s="103" t="s">
         <v>538</v>
       </c>
-      <c r="L131" s="104" t="s">
+      <c r="L131" s="103" t="s">
         <v>749</v>
       </c>
-      <c r="M131" s="108" t="s">
+      <c r="M131" s="107" t="s">
         <v>750</v>
       </c>
-      <c r="N131" s="104" t="s">
+      <c r="N131" s="103" t="s">
         <v>751</v>
       </c>
     </row>
@@ -10890,113 +11114,119 @@
       <c r="A132" s="5">
         <v>131</v>
       </c>
-      <c r="B132" s="102"/>
-      <c r="C132" s="103"/>
-      <c r="D132" s="104"/>
-      <c r="E132" s="105">
+      <c r="B132" s="101"/>
+      <c r="C132" s="102"/>
+      <c r="D132" s="103" t="s">
+        <v>733</v>
+      </c>
+      <c r="E132" s="104">
         <v>5</v>
       </c>
-      <c r="F132" s="106" t="s">
+      <c r="F132" s="105" t="s">
         <v>752</v>
       </c>
-      <c r="G132" s="107">
+      <c r="G132" s="106">
         <v>1.5856481481481482E-2</v>
       </c>
-      <c r="H132" s="104" t="s">
+      <c r="H132" s="103" t="s">
         <v>107</v>
       </c>
-      <c r="I132" s="104" t="s">
+      <c r="I132" s="103" t="s">
         <v>753</v>
       </c>
-      <c r="J132" s="104" t="s">
+      <c r="J132" s="103" t="s">
         <v>705</v>
       </c>
-      <c r="K132" s="104" t="s">
+      <c r="K132" s="103" t="s">
         <v>538</v>
       </c>
-      <c r="L132" s="104" t="s">
+      <c r="L132" s="103" t="s">
         <v>754</v>
       </c>
-      <c r="M132" s="108" t="s">
+      <c r="M132" s="107" t="s">
         <v>755</v>
       </c>
-      <c r="N132" s="104" t="s">
+      <c r="N132" s="103" t="s">
         <v>756</v>
       </c>
     </row>
-    <row r="133" spans="1:14" ht="162.6" thickBot="1">
+    <row r="133" spans="1:14" ht="180.6" thickBot="1">
       <c r="A133" s="6">
         <v>132</v>
       </c>
-      <c r="B133" s="102"/>
-      <c r="C133" s="103"/>
-      <c r="D133" s="104"/>
-      <c r="E133" s="105">
+      <c r="B133" s="101"/>
+      <c r="C133" s="102"/>
+      <c r="D133" s="103" t="s">
+        <v>733</v>
+      </c>
+      <c r="E133" s="104">
         <v>6</v>
       </c>
-      <c r="F133" s="106" t="s">
+      <c r="F133" s="105" t="s">
         <v>757</v>
       </c>
-      <c r="G133" s="107">
+      <c r="G133" s="106">
         <v>8.1481481481481474E-3</v>
       </c>
-      <c r="H133" s="104" t="s">
+      <c r="H133" s="103" t="s">
         <v>374</v>
       </c>
-      <c r="I133" s="104" t="s">
+      <c r="I133" s="103" t="s">
         <v>753</v>
       </c>
-      <c r="J133" s="104" t="s">
+      <c r="J133" s="103" t="s">
         <v>705</v>
       </c>
-      <c r="K133" s="104" t="s">
+      <c r="K133" s="103" t="s">
         <v>538</v>
       </c>
-      <c r="L133" s="104" t="s">
+      <c r="L133" s="103" t="s">
         <v>758</v>
       </c>
-      <c r="M133" s="108" t="s">
+      <c r="M133" s="107" t="s">
         <v>759</v>
       </c>
-      <c r="N133" s="104" t="s">
+      <c r="N133" s="103" t="s">
         <v>760</v>
       </c>
     </row>
-    <row r="134" spans="1:14" ht="162">
+    <row r="134" spans="1:14" ht="180">
       <c r="A134" s="5">
         <v>133</v>
       </c>
-      <c r="B134" s="102"/>
-      <c r="C134" s="103"/>
-      <c r="D134" s="104"/>
-      <c r="E134" s="105">
+      <c r="B134" s="101"/>
+      <c r="C134" s="102"/>
+      <c r="D134" s="103" t="s">
+        <v>733</v>
+      </c>
+      <c r="E134" s="104">
         <v>7</v>
       </c>
-      <c r="F134" s="106" t="s">
+      <c r="F134" s="105" t="s">
         <v>761</v>
       </c>
-      <c r="G134" s="107">
+      <c r="G134" s="106">
         <v>1.119212962962963E-2</v>
       </c>
-      <c r="H134" s="104" t="s">
+      <c r="H134" s="103" t="s">
         <v>244</v>
       </c>
-      <c r="I134" s="104" t="s">
+      <c r="I134" s="103" t="s">
         <v>341</v>
       </c>
-      <c r="J134" s="104" t="s">
+      <c r="J134" s="103" t="s">
         <v>705</v>
       </c>
-      <c r="K134" s="104" t="s">
+      <c r="K134" s="103" t="s">
         <v>538</v>
       </c>
-      <c r="L134" s="104" t="s">
+      <c r="L134" s="103" t="s">
         <v>762</v>
       </c>
-      <c r="M134" s="108" t="s">
+      <c r="M134" s="107" t="s">
         <v>763</v>
       </c>
-      <c r="N134" s="104" t="s">
+      <c r="N134" s="103" t="s">
         <v>764</v>
       </c>
     </row>
@@ -11004,77 +11234,79 @@
       <c r="A135" s="6">
         <v>134</v>
       </c>
-      <c r="B135" s="102"/>
-      <c r="C135" s="103"/>
-      <c r="D135" s="104"/>
-      <c r="E135" s="105">
+      <c r="B135" s="101"/>
+      <c r="C135" s="102"/>
+      <c r="D135" s="103" t="s">
+        <v>733</v>
+      </c>
+      <c r="E135" s="104">
         <v>8</v>
       </c>
-      <c r="F135" s="106" t="s">
+      <c r="F135" s="105" t="s">
         <v>765</v>
       </c>
-      <c r="G135" s="107">
+      <c r="G135" s="106">
         <v>1.2141203703703704E-2</v>
       </c>
-      <c r="H135" s="104" t="s">
+      <c r="H135" s="103" t="s">
         <v>244</v>
       </c>
-      <c r="I135" s="104" t="s">
+      <c r="I135" s="103" t="s">
         <v>341</v>
       </c>
-      <c r="J135" s="104" t="s">
+      <c r="J135" s="103" t="s">
         <v>705</v>
       </c>
-      <c r="K135" s="104" t="s">
+      <c r="K135" s="103" t="s">
         <v>538</v>
       </c>
-      <c r="L135" s="104" t="s">
+      <c r="L135" s="103" t="s">
         <v>766</v>
       </c>
-      <c r="M135" s="108" t="s">
+      <c r="M135" s="107" t="s">
         <v>767</v>
       </c>
-      <c r="N135" s="104" t="s">
+      <c r="N135" s="103" t="s">
         <v>768</v>
       </c>
     </row>
-    <row r="136" spans="1:14" ht="216">
+    <row r="136" spans="1:14" ht="234">
       <c r="A136" s="5">
         <v>135</v>
       </c>
-      <c r="B136" s="109"/>
-      <c r="C136" s="110" t="s">
+      <c r="B136" s="108"/>
+      <c r="C136" s="109" t="s">
         <v>160</v>
       </c>
-      <c r="D136" s="111" t="s">
+      <c r="D136" s="110" t="s">
         <v>769</v>
       </c>
-      <c r="E136" s="112">
+      <c r="E136" s="111">
         <v>1</v>
       </c>
-      <c r="F136" s="111" t="s">
+      <c r="F136" s="110" t="s">
         <v>770</v>
       </c>
-      <c r="G136" s="113">
+      <c r="G136" s="112">
         <v>1.5243055555555555E-2</v>
       </c>
-      <c r="H136" s="111" t="s">
+      <c r="H136" s="110" t="s">
         <v>771</v>
       </c>
-      <c r="I136" s="111" t="s">
+      <c r="I136" s="110" t="s">
         <v>772</v>
       </c>
-      <c r="J136" s="111"/>
-      <c r="K136" s="111" t="s">
+      <c r="J136" s="110"/>
+      <c r="K136" s="110" t="s">
         <v>538</v>
       </c>
-      <c r="L136" s="111" t="s">
+      <c r="L136" s="110" t="s">
         <v>773</v>
       </c>
-      <c r="M136" s="114" t="s">
+      <c r="M136" s="113" t="s">
         <v>774</v>
       </c>
-      <c r="N136" s="111" t="s">
+      <c r="N136" s="110" t="s">
         <v>775</v>
       </c>
     </row>
@@ -11082,41 +11314,41 @@
       <c r="A137" s="6">
         <v>136</v>
       </c>
-      <c r="B137" s="115"/>
-      <c r="C137" s="116" t="s">
+      <c r="B137" s="114"/>
+      <c r="C137" s="115" t="s">
         <v>241</v>
       </c>
-      <c r="D137" s="117" t="s">
+      <c r="D137" s="116" t="s">
         <v>776</v>
       </c>
-      <c r="E137" s="118">
+      <c r="E137" s="117">
         <v>1</v>
       </c>
-      <c r="F137" s="119" t="s">
+      <c r="F137" s="118" t="s">
         <v>777</v>
       </c>
-      <c r="G137" s="120">
+      <c r="G137" s="119">
         <v>8.9236111111111113E-3</v>
       </c>
-      <c r="H137" s="117" t="s">
+      <c r="H137" s="116" t="s">
         <v>107</v>
       </c>
-      <c r="I137" s="117" t="s">
+      <c r="I137" s="116" t="s">
         <v>778</v>
       </c>
-      <c r="J137" s="117" t="s">
+      <c r="J137" s="116" t="s">
         <v>705</v>
       </c>
-      <c r="K137" s="117" t="s">
+      <c r="K137" s="116" t="s">
         <v>538</v>
       </c>
-      <c r="L137" s="117" t="s">
+      <c r="L137" s="116" t="s">
         <v>779</v>
       </c>
-      <c r="M137" s="121" t="s">
+      <c r="M137" s="120" t="s">
         <v>780</v>
       </c>
-      <c r="N137" s="117" t="s">
+      <c r="N137" s="116" t="s">
         <v>781</v>
       </c>
     </row>
@@ -11124,37 +11356,39 @@
       <c r="A138" s="5">
         <v>137</v>
       </c>
-      <c r="B138" s="115"/>
-      <c r="C138" s="116"/>
-      <c r="D138" s="117"/>
-      <c r="E138" s="118">
+      <c r="B138" s="114"/>
+      <c r="C138" s="115"/>
+      <c r="D138" s="116" t="s">
+        <v>776</v>
+      </c>
+      <c r="E138" s="117">
         <v>2</v>
       </c>
-      <c r="F138" s="119" t="s">
+      <c r="F138" s="118" t="s">
         <v>782</v>
       </c>
-      <c r="G138" s="120">
+      <c r="G138" s="119">
         <v>1.9097222222222224E-2</v>
       </c>
-      <c r="H138" s="117" t="s">
+      <c r="H138" s="116" t="s">
         <v>783</v>
       </c>
-      <c r="I138" s="117" t="s">
+      <c r="I138" s="116" t="s">
         <v>784</v>
       </c>
-      <c r="J138" s="117" t="s">
+      <c r="J138" s="116" t="s">
         <v>705</v>
       </c>
-      <c r="K138" s="117" t="s">
+      <c r="K138" s="116" t="s">
         <v>538</v>
       </c>
-      <c r="L138" s="117" t="s">
+      <c r="L138" s="116" t="s">
         <v>785</v>
       </c>
-      <c r="M138" s="121" t="s">
+      <c r="M138" s="120" t="s">
         <v>786</v>
       </c>
-      <c r="N138" s="117" t="s">
+      <c r="N138" s="116" t="s">
         <v>787</v>
       </c>
     </row>
@@ -11162,37 +11396,39 @@
       <c r="A139" s="6">
         <v>138</v>
       </c>
-      <c r="B139" s="115"/>
-      <c r="C139" s="116"/>
-      <c r="D139" s="117"/>
-      <c r="E139" s="118">
+      <c r="B139" s="114"/>
+      <c r="C139" s="115"/>
+      <c r="D139" s="116" t="s">
+        <v>776</v>
+      </c>
+      <c r="E139" s="117">
         <v>3</v>
       </c>
-      <c r="F139" s="119" t="s">
+      <c r="F139" s="118" t="s">
         <v>788</v>
       </c>
-      <c r="G139" s="120">
+      <c r="G139" s="119">
         <v>8.9351851851851849E-3</v>
       </c>
-      <c r="H139" s="117" t="s">
+      <c r="H139" s="116" t="s">
         <v>107</v>
       </c>
-      <c r="I139" s="117" t="s">
+      <c r="I139" s="116" t="s">
         <v>778</v>
       </c>
-      <c r="J139" s="117" t="s">
+      <c r="J139" s="116" t="s">
         <v>705</v>
       </c>
-      <c r="K139" s="117" t="s">
+      <c r="K139" s="116" t="s">
         <v>538</v>
       </c>
-      <c r="L139" s="117" t="s">
+      <c r="L139" s="116" t="s">
         <v>789</v>
       </c>
-      <c r="M139" s="121" t="s">
+      <c r="M139" s="120" t="s">
         <v>790</v>
       </c>
-      <c r="N139" s="117" t="s">
+      <c r="N139" s="116" t="s">
         <v>791</v>
       </c>
     </row>
@@ -11200,37 +11436,39 @@
       <c r="A140" s="5">
         <v>139</v>
       </c>
-      <c r="B140" s="115"/>
-      <c r="C140" s="116"/>
-      <c r="D140" s="117"/>
-      <c r="E140" s="118">
+      <c r="B140" s="114"/>
+      <c r="C140" s="115"/>
+      <c r="D140" s="116" t="s">
+        <v>776</v>
+      </c>
+      <c r="E140" s="117">
         <v>4</v>
       </c>
-      <c r="F140" s="119" t="s">
+      <c r="F140" s="118" t="s">
         <v>792</v>
       </c>
-      <c r="G140" s="120">
+      <c r="G140" s="119">
         <v>1.0868055555555556E-2</v>
       </c>
-      <c r="H140" s="117" t="s">
+      <c r="H140" s="116" t="s">
         <v>95</v>
       </c>
-      <c r="I140" s="117" t="s">
+      <c r="I140" s="116" t="s">
         <v>267</v>
       </c>
-      <c r="J140" s="117" t="s">
+      <c r="J140" s="116" t="s">
         <v>705</v>
       </c>
-      <c r="K140" s="117" t="s">
+      <c r="K140" s="116" t="s">
         <v>538</v>
       </c>
-      <c r="L140" s="117" t="s">
+      <c r="L140" s="116" t="s">
         <v>793</v>
       </c>
-      <c r="M140" s="121" t="s">
+      <c r="M140" s="120" t="s">
         <v>794</v>
       </c>
-      <c r="N140" s="117" t="s">
+      <c r="N140" s="116" t="s">
         <v>795</v>
       </c>
     </row>
@@ -11238,37 +11476,39 @@
       <c r="A141" s="6">
         <v>140</v>
       </c>
-      <c r="B141" s="115"/>
-      <c r="C141" s="116"/>
-      <c r="D141" s="117"/>
-      <c r="E141" s="118">
+      <c r="B141" s="114"/>
+      <c r="C141" s="115"/>
+      <c r="D141" s="116" t="s">
+        <v>776</v>
+      </c>
+      <c r="E141" s="117">
         <v>5</v>
       </c>
-      <c r="F141" s="119" t="s">
+      <c r="F141" s="118" t="s">
         <v>796</v>
       </c>
-      <c r="G141" s="120">
+      <c r="G141" s="119">
         <v>1.3101851851851852E-2</v>
       </c>
-      <c r="H141" s="117" t="s">
+      <c r="H141" s="116" t="s">
         <v>107</v>
       </c>
-      <c r="I141" s="117" t="s">
+      <c r="I141" s="116" t="s">
         <v>778</v>
       </c>
-      <c r="J141" s="117" t="s">
+      <c r="J141" s="116" t="s">
         <v>705</v>
       </c>
-      <c r="K141" s="117" t="s">
+      <c r="K141" s="116" t="s">
         <v>538</v>
       </c>
-      <c r="L141" s="117" t="s">
+      <c r="L141" s="116" t="s">
         <v>797</v>
       </c>
-      <c r="M141" s="121" t="s">
+      <c r="M141" s="120" t="s">
         <v>798</v>
       </c>
-      <c r="N141" s="117" t="s">
+      <c r="N141" s="116" t="s">
         <v>799</v>
       </c>
     </row>
@@ -11276,37 +11516,39 @@
       <c r="A142" s="5">
         <v>141</v>
       </c>
-      <c r="B142" s="115"/>
-      <c r="C142" s="116"/>
-      <c r="D142" s="117"/>
-      <c r="E142" s="118">
+      <c r="B142" s="114"/>
+      <c r="C142" s="115"/>
+      <c r="D142" s="116" t="s">
+        <v>776</v>
+      </c>
+      <c r="E142" s="117">
         <v>6</v>
       </c>
-      <c r="F142" s="119" t="s">
+      <c r="F142" s="118" t="s">
         <v>800</v>
       </c>
-      <c r="G142" s="120">
+      <c r="G142" s="119">
         <v>8.0324074074074082E-3</v>
       </c>
-      <c r="H142" s="117" t="s">
+      <c r="H142" s="116" t="s">
         <v>107</v>
       </c>
-      <c r="I142" s="117" t="s">
+      <c r="I142" s="116" t="s">
         <v>778</v>
       </c>
-      <c r="J142" s="117" t="s">
+      <c r="J142" s="116" t="s">
         <v>705</v>
       </c>
-      <c r="K142" s="117" t="s">
+      <c r="K142" s="116" t="s">
         <v>538</v>
       </c>
-      <c r="L142" s="117" t="s">
+      <c r="L142" s="116" t="s">
         <v>801</v>
       </c>
-      <c r="M142" s="121" t="s">
+      <c r="M142" s="120" t="s">
         <v>802</v>
       </c>
-      <c r="N142" s="117" t="s">
+      <c r="N142" s="116" t="s">
         <v>803</v>
       </c>
     </row>
@@ -11314,37 +11556,39 @@
       <c r="A143" s="6">
         <v>142</v>
       </c>
-      <c r="B143" s="115"/>
-      <c r="C143" s="116"/>
-      <c r="D143" s="117"/>
-      <c r="E143" s="118">
+      <c r="B143" s="114"/>
+      <c r="C143" s="115"/>
+      <c r="D143" s="116" t="s">
+        <v>776</v>
+      </c>
+      <c r="E143" s="117">
         <v>7</v>
       </c>
-      <c r="F143" s="119" t="s">
+      <c r="F143" s="118" t="s">
         <v>804</v>
       </c>
-      <c r="G143" s="120">
+      <c r="G143" s="119">
         <v>1.2500000000000001E-2</v>
       </c>
-      <c r="H143" s="117" t="s">
+      <c r="H143" s="116" t="s">
         <v>107</v>
       </c>
-      <c r="I143" s="117" t="s">
+      <c r="I143" s="116" t="s">
         <v>778</v>
       </c>
-      <c r="J143" s="117" t="s">
+      <c r="J143" s="116" t="s">
         <v>705</v>
       </c>
-      <c r="K143" s="117" t="s">
+      <c r="K143" s="116" t="s">
         <v>538</v>
       </c>
-      <c r="L143" s="117" t="s">
+      <c r="L143" s="116" t="s">
         <v>805</v>
       </c>
-      <c r="M143" s="121" t="s">
+      <c r="M143" s="120" t="s">
         <v>806</v>
       </c>
-      <c r="N143" s="117" t="s">
+      <c r="N143" s="116" t="s">
         <v>807</v>
       </c>
     </row>
@@ -11352,37 +11596,39 @@
       <c r="A144" s="5">
         <v>143</v>
       </c>
-      <c r="B144" s="115"/>
-      <c r="C144" s="116"/>
-      <c r="D144" s="117"/>
-      <c r="E144" s="118">
+      <c r="B144" s="114"/>
+      <c r="C144" s="115"/>
+      <c r="D144" s="116" t="s">
+        <v>776</v>
+      </c>
+      <c r="E144" s="117">
         <v>8</v>
       </c>
-      <c r="F144" s="119" t="s">
+      <c r="F144" s="118" t="s">
         <v>808</v>
       </c>
-      <c r="G144" s="120">
+      <c r="G144" s="119">
         <v>1.0462962962962962E-2</v>
       </c>
-      <c r="H144" s="117" t="s">
+      <c r="H144" s="116" t="s">
         <v>107</v>
       </c>
-      <c r="I144" s="117" t="s">
+      <c r="I144" s="116" t="s">
         <v>778</v>
       </c>
-      <c r="J144" s="117" t="s">
+      <c r="J144" s="116" t="s">
         <v>705</v>
       </c>
-      <c r="K144" s="117" t="s">
+      <c r="K144" s="116" t="s">
         <v>538</v>
       </c>
-      <c r="L144" s="117" t="s">
+      <c r="L144" s="116" t="s">
         <v>809</v>
       </c>
-      <c r="M144" s="121" t="s">
+      <c r="M144" s="120" t="s">
         <v>810</v>
       </c>
-      <c r="N144" s="117" t="s">
+      <c r="N144" s="116" t="s">
         <v>811</v>
       </c>
     </row>
@@ -11390,37 +11636,39 @@
       <c r="A145" s="6">
         <v>144</v>
       </c>
-      <c r="B145" s="115"/>
-      <c r="C145" s="116"/>
-      <c r="D145" s="117"/>
-      <c r="E145" s="118">
+      <c r="B145" s="114"/>
+      <c r="C145" s="115"/>
+      <c r="D145" s="116" t="s">
+        <v>776</v>
+      </c>
+      <c r="E145" s="117">
         <v>9</v>
       </c>
-      <c r="F145" s="119" t="s">
+      <c r="F145" s="118" t="s">
         <v>812</v>
       </c>
-      <c r="G145" s="120">
+      <c r="G145" s="119">
         <v>1.3703703703703704E-2</v>
       </c>
-      <c r="H145" s="117" t="s">
+      <c r="H145" s="116" t="s">
         <v>107</v>
       </c>
-      <c r="I145" s="117" t="s">
+      <c r="I145" s="116" t="s">
         <v>778</v>
       </c>
-      <c r="J145" s="117" t="s">
+      <c r="J145" s="116" t="s">
         <v>705</v>
       </c>
-      <c r="K145" s="117" t="s">
+      <c r="K145" s="116" t="s">
         <v>538</v>
       </c>
-      <c r="L145" s="117" t="s">
+      <c r="L145" s="116" t="s">
         <v>813</v>
       </c>
-      <c r="M145" s="121" t="s">
+      <c r="M145" s="120" t="s">
         <v>814</v>
       </c>
-      <c r="N145" s="117" t="s">
+      <c r="N145" s="116" t="s">
         <v>815</v>
       </c>
     </row>
@@ -11428,37 +11676,39 @@
       <c r="A146" s="5">
         <v>145</v>
       </c>
-      <c r="B146" s="115"/>
-      <c r="C146" s="116"/>
-      <c r="D146" s="117"/>
-      <c r="E146" s="118">
+      <c r="B146" s="114"/>
+      <c r="C146" s="115"/>
+      <c r="D146" s="116" t="s">
+        <v>776</v>
+      </c>
+      <c r="E146" s="117">
         <v>10</v>
       </c>
-      <c r="F146" s="119" t="s">
+      <c r="F146" s="118" t="s">
         <v>816</v>
       </c>
-      <c r="G146" s="120">
+      <c r="G146" s="119">
         <v>1.0162037037037037E-2</v>
       </c>
-      <c r="H146" s="117" t="s">
+      <c r="H146" s="116" t="s">
         <v>783</v>
       </c>
-      <c r="I146" s="117" t="s">
+      <c r="I146" s="116" t="s">
         <v>184</v>
       </c>
-      <c r="J146" s="117" t="s">
+      <c r="J146" s="116" t="s">
         <v>705</v>
       </c>
-      <c r="K146" s="117" t="s">
+      <c r="K146" s="116" t="s">
         <v>538</v>
       </c>
-      <c r="L146" s="117" t="s">
+      <c r="L146" s="116" t="s">
         <v>817</v>
       </c>
-      <c r="M146" s="121" t="s">
+      <c r="M146" s="120" t="s">
         <v>818</v>
       </c>
-      <c r="N146" s="117" t="s">
+      <c r="N146" s="116" t="s">
         <v>819</v>
       </c>
     </row>
@@ -11466,37 +11716,39 @@
       <c r="A147" s="6">
         <v>146</v>
       </c>
-      <c r="B147" s="115"/>
-      <c r="C147" s="116"/>
-      <c r="D147" s="117"/>
-      <c r="E147" s="118">
+      <c r="B147" s="114"/>
+      <c r="C147" s="115"/>
+      <c r="D147" s="116" t="s">
+        <v>776</v>
+      </c>
+      <c r="E147" s="117">
         <v>11</v>
       </c>
-      <c r="F147" s="119" t="s">
+      <c r="F147" s="118" t="s">
         <v>820</v>
       </c>
-      <c r="G147" s="120">
+      <c r="G147" s="119">
         <v>4.0393518518518521E-3</v>
       </c>
-      <c r="H147" s="117" t="s">
+      <c r="H147" s="116" t="s">
         <v>783</v>
       </c>
-      <c r="I147" s="117" t="s">
+      <c r="I147" s="116" t="s">
         <v>267</v>
       </c>
-      <c r="J147" s="117" t="s">
+      <c r="J147" s="116" t="s">
         <v>705</v>
       </c>
-      <c r="K147" s="117" t="s">
+      <c r="K147" s="116" t="s">
         <v>538</v>
       </c>
-      <c r="L147" s="117" t="s">
+      <c r="L147" s="116" t="s">
         <v>821</v>
       </c>
-      <c r="M147" s="121" t="s">
+      <c r="M147" s="120" t="s">
         <v>822</v>
       </c>
-      <c r="N147" s="117" t="s">
+      <c r="N147" s="116" t="s">
         <v>823</v>
       </c>
     </row>
@@ -11504,37 +11756,39 @@
       <c r="A148" s="5">
         <v>147</v>
       </c>
-      <c r="B148" s="115"/>
-      <c r="C148" s="116"/>
-      <c r="D148" s="117"/>
-      <c r="E148" s="118">
+      <c r="B148" s="114"/>
+      <c r="C148" s="115"/>
+      <c r="D148" s="116" t="s">
+        <v>776</v>
+      </c>
+      <c r="E148" s="117">
         <v>12</v>
       </c>
-      <c r="F148" s="119" t="s">
+      <c r="F148" s="118" t="s">
         <v>824</v>
       </c>
-      <c r="G148" s="120">
+      <c r="G148" s="119">
         <v>1.681712962962963E-2</v>
       </c>
-      <c r="H148" s="117" t="s">
+      <c r="H148" s="116" t="s">
         <v>783</v>
       </c>
-      <c r="I148" s="117" t="s">
+      <c r="I148" s="116" t="s">
         <v>267</v>
       </c>
-      <c r="J148" s="117" t="s">
+      <c r="J148" s="116" t="s">
         <v>705</v>
       </c>
-      <c r="K148" s="117" t="s">
+      <c r="K148" s="116" t="s">
         <v>538</v>
       </c>
-      <c r="L148" s="117" t="s">
+      <c r="L148" s="116" t="s">
         <v>825</v>
       </c>
-      <c r="M148" s="121" t="s">
+      <c r="M148" s="120" t="s">
         <v>826</v>
       </c>
-      <c r="N148" s="117" t="s">
+      <c r="N148" s="116" t="s">
         <v>827</v>
       </c>
     </row>
@@ -11542,37 +11796,39 @@
       <c r="A149" s="6">
         <v>148</v>
       </c>
-      <c r="B149" s="115"/>
-      <c r="C149" s="116"/>
-      <c r="D149" s="117"/>
-      <c r="E149" s="118">
+      <c r="B149" s="114"/>
+      <c r="C149" s="115"/>
+      <c r="D149" s="116" t="s">
+        <v>776</v>
+      </c>
+      <c r="E149" s="117">
         <v>13</v>
       </c>
-      <c r="F149" s="119" t="s">
+      <c r="F149" s="118" t="s">
         <v>828</v>
       </c>
-      <c r="G149" s="120">
+      <c r="G149" s="119">
         <v>1.5300925925925926E-2</v>
       </c>
-      <c r="H149" s="117" t="s">
+      <c r="H149" s="116" t="s">
         <v>783</v>
       </c>
-      <c r="I149" s="117" t="s">
+      <c r="I149" s="116" t="s">
         <v>267</v>
       </c>
-      <c r="J149" s="117" t="s">
+      <c r="J149" s="116" t="s">
         <v>705</v>
       </c>
-      <c r="K149" s="117" t="s">
+      <c r="K149" s="116" t="s">
         <v>538</v>
       </c>
-      <c r="L149" s="117" t="s">
+      <c r="L149" s="116" t="s">
         <v>829</v>
       </c>
-      <c r="M149" s="121" t="s">
+      <c r="M149" s="120" t="s">
         <v>830</v>
       </c>
-      <c r="N149" s="117" t="s">
+      <c r="N149" s="116" t="s">
         <v>831</v>
       </c>
     </row>
@@ -11580,75 +11836,79 @@
       <c r="A150" s="5">
         <v>149</v>
       </c>
-      <c r="B150" s="115"/>
-      <c r="C150" s="116"/>
-      <c r="D150" s="117"/>
-      <c r="E150" s="118">
+      <c r="B150" s="114"/>
+      <c r="C150" s="115"/>
+      <c r="D150" s="116" t="s">
+        <v>776</v>
+      </c>
+      <c r="E150" s="117">
         <v>14</v>
       </c>
-      <c r="F150" s="119" t="s">
+      <c r="F150" s="118" t="s">
         <v>832</v>
       </c>
-      <c r="G150" s="120">
+      <c r="G150" s="119">
         <v>2.2916666666666665E-2</v>
       </c>
-      <c r="H150" s="117" t="s">
+      <c r="H150" s="116" t="s">
         <v>783</v>
       </c>
-      <c r="I150" s="117" t="s">
+      <c r="I150" s="116" t="s">
         <v>267</v>
       </c>
-      <c r="J150" s="117" t="s">
+      <c r="J150" s="116" t="s">
         <v>705</v>
       </c>
-      <c r="K150" s="117" t="s">
+      <c r="K150" s="116" t="s">
         <v>538</v>
       </c>
-      <c r="L150" s="117" t="s">
+      <c r="L150" s="116" t="s">
         <v>833</v>
       </c>
-      <c r="M150" s="121" t="s">
+      <c r="M150" s="120" t="s">
         <v>834</v>
       </c>
-      <c r="N150" s="117" t="s">
+      <c r="N150" s="116" t="s">
         <v>835</v>
       </c>
     </row>
-    <row r="151" spans="1:14" ht="198.6" thickBot="1">
+    <row r="151" spans="1:14" ht="216.6" thickBot="1">
       <c r="A151" s="6">
         <v>150</v>
       </c>
-      <c r="B151" s="115"/>
-      <c r="C151" s="116"/>
-      <c r="D151" s="117"/>
-      <c r="E151" s="118">
+      <c r="B151" s="114"/>
+      <c r="C151" s="115"/>
+      <c r="D151" s="116" t="s">
+        <v>776</v>
+      </c>
+      <c r="E151" s="117">
         <v>15</v>
       </c>
-      <c r="F151" s="119" t="s">
+      <c r="F151" s="118" t="s">
         <v>836</v>
       </c>
-      <c r="G151" s="120">
+      <c r="G151" s="119">
         <v>1.4641203703703703E-2</v>
       </c>
-      <c r="H151" s="117" t="s">
+      <c r="H151" s="116" t="s">
         <v>783</v>
       </c>
-      <c r="I151" s="117" t="s">
+      <c r="I151" s="116" t="s">
         <v>837</v>
       </c>
-      <c r="J151" s="117" t="s">
+      <c r="J151" s="116" t="s">
         <v>705</v>
       </c>
-      <c r="K151" s="117" t="s">
+      <c r="K151" s="116" t="s">
         <v>538</v>
       </c>
-      <c r="L151" s="117" t="s">
+      <c r="L151" s="116" t="s">
         <v>838</v>
       </c>
-      <c r="M151" s="121" t="s">
+      <c r="M151" s="120" t="s">
         <v>839</v>
       </c>
-      <c r="N151" s="117" t="s">
+      <c r="N151" s="116" t="s">
         <v>840</v>
       </c>
     </row>
@@ -11656,37 +11916,39 @@
       <c r="A152" s="5">
         <v>151</v>
       </c>
-      <c r="B152" s="115"/>
-      <c r="C152" s="116"/>
-      <c r="D152" s="117"/>
-      <c r="E152" s="118">
+      <c r="B152" s="114"/>
+      <c r="C152" s="115"/>
+      <c r="D152" s="116" t="s">
+        <v>776</v>
+      </c>
+      <c r="E152" s="117">
         <v>16</v>
       </c>
-      <c r="F152" s="119" t="s">
+      <c r="F152" s="118" t="s">
         <v>841</v>
       </c>
-      <c r="G152" s="120">
+      <c r="G152" s="119">
         <v>1.7881944444444443E-2</v>
       </c>
-      <c r="H152" s="117" t="s">
+      <c r="H152" s="116" t="s">
         <v>251</v>
       </c>
-      <c r="I152" s="117" t="s">
+      <c r="I152" s="116" t="s">
         <v>735</v>
       </c>
-      <c r="J152" s="117" t="s">
+      <c r="J152" s="116" t="s">
         <v>705</v>
       </c>
-      <c r="K152" s="117" t="s">
+      <c r="K152" s="116" t="s">
         <v>538</v>
       </c>
-      <c r="L152" s="117" t="s">
+      <c r="L152" s="116" t="s">
         <v>842</v>
       </c>
-      <c r="M152" s="121" t="s">
+      <c r="M152" s="120" t="s">
         <v>843</v>
       </c>
-      <c r="N152" s="117" t="s">
+      <c r="N152" s="116" t="s">
         <v>844</v>
       </c>
     </row>
@@ -11694,37 +11956,39 @@
       <c r="A153" s="6">
         <v>152</v>
       </c>
-      <c r="B153" s="115"/>
-      <c r="C153" s="116"/>
-      <c r="D153" s="117"/>
-      <c r="E153" s="118">
+      <c r="B153" s="114"/>
+      <c r="C153" s="115"/>
+      <c r="D153" s="116" t="s">
+        <v>776</v>
+      </c>
+      <c r="E153" s="117">
         <v>17</v>
       </c>
-      <c r="F153" s="119" t="s">
+      <c r="F153" s="118" t="s">
         <v>845</v>
       </c>
-      <c r="G153" s="120">
+      <c r="G153" s="119">
         <v>1.337962962962963E-2</v>
       </c>
-      <c r="H153" s="117" t="s">
+      <c r="H153" s="116" t="s">
         <v>17</v>
       </c>
-      <c r="I153" s="117" t="s">
+      <c r="I153" s="116" t="s">
         <v>846</v>
       </c>
-      <c r="J153" s="117" t="s">
+      <c r="J153" s="116" t="s">
         <v>705</v>
       </c>
-      <c r="K153" s="117" t="s">
+      <c r="K153" s="116" t="s">
         <v>538</v>
       </c>
-      <c r="L153" s="117" t="s">
+      <c r="L153" s="116" t="s">
         <v>847</v>
       </c>
-      <c r="M153" s="121" t="s">
+      <c r="M153" s="120" t="s">
         <v>848</v>
       </c>
-      <c r="N153" s="117" t="s">
+      <c r="N153" s="116" t="s">
         <v>849</v>
       </c>
     </row>
@@ -11732,37 +11996,39 @@
       <c r="A154" s="5">
         <v>153</v>
       </c>
-      <c r="B154" s="115"/>
-      <c r="C154" s="116"/>
-      <c r="D154" s="117"/>
-      <c r="E154" s="118">
+      <c r="B154" s="114"/>
+      <c r="C154" s="115"/>
+      <c r="D154" s="116" t="s">
+        <v>776</v>
+      </c>
+      <c r="E154" s="117">
         <v>18</v>
       </c>
-      <c r="F154" s="119" t="s">
+      <c r="F154" s="118" t="s">
         <v>850</v>
       </c>
-      <c r="G154" s="120">
+      <c r="G154" s="119">
         <v>4.0393518518518521E-3</v>
       </c>
-      <c r="H154" s="117" t="s">
+      <c r="H154" s="116" t="s">
         <v>251</v>
       </c>
-      <c r="I154" s="117" t="s">
+      <c r="I154" s="116" t="s">
         <v>252</v>
       </c>
-      <c r="J154" s="117" t="s">
+      <c r="J154" s="116" t="s">
         <v>705</v>
       </c>
-      <c r="K154" s="117" t="s">
+      <c r="K154" s="116" t="s">
         <v>538</v>
       </c>
-      <c r="L154" s="117" t="s">
+      <c r="L154" s="116" t="s">
         <v>851</v>
       </c>
-      <c r="M154" s="121" t="s">
+      <c r="M154" s="120" t="s">
         <v>852</v>
       </c>
-      <c r="N154" s="117" t="s">
+      <c r="N154" s="116" t="s">
         <v>853</v>
       </c>
     </row>
@@ -11770,37 +12036,39 @@
       <c r="A155" s="6">
         <v>154</v>
       </c>
-      <c r="B155" s="115"/>
-      <c r="C155" s="116"/>
-      <c r="D155" s="117"/>
-      <c r="E155" s="118">
+      <c r="B155" s="114"/>
+      <c r="C155" s="115"/>
+      <c r="D155" s="116" t="s">
+        <v>776</v>
+      </c>
+      <c r="E155" s="117">
         <v>19</v>
       </c>
-      <c r="F155" s="119" t="s">
+      <c r="F155" s="118" t="s">
         <v>854</v>
       </c>
-      <c r="G155" s="120">
+      <c r="G155" s="119">
         <v>5.138888888888889E-3</v>
       </c>
-      <c r="H155" s="117" t="s">
+      <c r="H155" s="116" t="s">
         <v>374</v>
       </c>
-      <c r="I155" s="117" t="s">
+      <c r="I155" s="116" t="s">
         <v>778</v>
       </c>
-      <c r="J155" s="117" t="s">
+      <c r="J155" s="116" t="s">
         <v>705</v>
       </c>
-      <c r="K155" s="117" t="s">
+      <c r="K155" s="116" t="s">
         <v>538</v>
       </c>
-      <c r="L155" s="117" t="s">
+      <c r="L155" s="116" t="s">
         <v>855</v>
       </c>
-      <c r="M155" s="121" t="s">
+      <c r="M155" s="120" t="s">
         <v>856</v>
       </c>
-      <c r="N155" s="117" t="s">
+      <c r="N155" s="116" t="s">
         <v>857</v>
       </c>
     </row>
@@ -11808,43 +12076,43 @@
       <c r="A156" s="5">
         <v>155</v>
       </c>
-      <c r="B156" s="122" t="s">
+      <c r="B156" s="121" t="s">
         <v>858</v>
       </c>
-      <c r="C156" s="123" t="s">
+      <c r="C156" s="122" t="s">
         <v>294</v>
       </c>
-      <c r="D156" s="124" t="s">
+      <c r="D156" s="123" t="s">
         <v>859</v>
       </c>
-      <c r="E156" s="125">
+      <c r="E156" s="124">
         <v>1</v>
       </c>
-      <c r="F156" s="126" t="s">
+      <c r="F156" s="125" t="s">
         <v>860</v>
       </c>
-      <c r="G156" s="127">
+      <c r="G156" s="126">
         <v>3.7499999999999999E-3</v>
       </c>
-      <c r="H156" s="124" t="s">
+      <c r="H156" s="123" t="s">
         <v>251</v>
       </c>
-      <c r="I156" s="124" t="s">
+      <c r="I156" s="123" t="s">
         <v>861</v>
       </c>
-      <c r="J156" s="124" t="s">
+      <c r="J156" s="123" t="s">
         <v>705</v>
       </c>
-      <c r="K156" s="124" t="s">
+      <c r="K156" s="123" t="s">
         <v>538</v>
       </c>
-      <c r="L156" s="124" t="s">
+      <c r="L156" s="123" t="s">
         <v>862</v>
       </c>
-      <c r="M156" s="128" t="s">
+      <c r="M156" s="127" t="s">
         <v>863</v>
       </c>
-      <c r="N156" s="124" t="s">
+      <c r="N156" s="123" t="s">
         <v>864</v>
       </c>
     </row>
@@ -11852,77 +12120,81 @@
       <c r="A157" s="6">
         <v>156</v>
       </c>
-      <c r="B157" s="122" t="s">
+      <c r="B157" s="121" t="s">
         <v>858</v>
       </c>
-      <c r="C157" s="123"/>
-      <c r="D157" s="124"/>
-      <c r="E157" s="125">
+      <c r="C157" s="122"/>
+      <c r="D157" s="123" t="s">
+        <v>859</v>
+      </c>
+      <c r="E157" s="124">
         <v>2</v>
       </c>
-      <c r="F157" s="126" t="s">
+      <c r="F157" s="125" t="s">
         <v>865</v>
       </c>
-      <c r="G157" s="127">
+      <c r="G157" s="126">
         <v>6.2847222222222219E-3</v>
       </c>
-      <c r="H157" s="124" t="s">
+      <c r="H157" s="123" t="s">
         <v>251</v>
       </c>
-      <c r="I157" s="124" t="s">
+      <c r="I157" s="123" t="s">
         <v>861</v>
       </c>
-      <c r="J157" s="124" t="s">
+      <c r="J157" s="123" t="s">
         <v>705</v>
       </c>
-      <c r="K157" s="124" t="s">
+      <c r="K157" s="123" t="s">
         <v>538</v>
       </c>
-      <c r="L157" s="124" t="s">
+      <c r="L157" s="123" t="s">
         <v>866</v>
       </c>
-      <c r="M157" s="128" t="s">
+      <c r="M157" s="127" t="s">
         <v>867</v>
       </c>
-      <c r="N157" s="124" t="s">
+      <c r="N157" s="123" t="s">
         <v>868</v>
       </c>
     </row>
-    <row r="158" spans="1:14" ht="198">
+    <row r="158" spans="1:14" ht="216">
       <c r="A158" s="5">
         <v>157</v>
       </c>
-      <c r="B158" s="122"/>
-      <c r="C158" s="123"/>
-      <c r="D158" s="124"/>
-      <c r="E158" s="125">
+      <c r="B158" s="121"/>
+      <c r="C158" s="122"/>
+      <c r="D158" s="123" t="s">
+        <v>859</v>
+      </c>
+      <c r="E158" s="124">
         <v>3</v>
       </c>
-      <c r="F158" s="129" t="s">
+      <c r="F158" s="128" t="s">
         <v>869</v>
       </c>
-      <c r="G158" s="127">
+      <c r="G158" s="126">
         <v>4.4675925925925924E-3</v>
       </c>
-      <c r="H158" s="124" t="s">
+      <c r="H158" s="123" t="s">
         <v>251</v>
       </c>
-      <c r="I158" s="124" t="s">
+      <c r="I158" s="123" t="s">
         <v>861</v>
       </c>
-      <c r="J158" s="124" t="s">
+      <c r="J158" s="123" t="s">
         <v>705</v>
       </c>
-      <c r="K158" s="124" t="s">
+      <c r="K158" s="123" t="s">
         <v>538</v>
       </c>
-      <c r="L158" s="124" t="s">
+      <c r="L158" s="123" t="s">
         <v>870</v>
       </c>
-      <c r="M158" s="128" t="s">
+      <c r="M158" s="127" t="s">
         <v>871</v>
       </c>
-      <c r="N158" s="124" t="s">
+      <c r="N158" s="123" t="s">
         <v>872</v>
       </c>
     </row>
@@ -11930,805 +12202,841 @@
       <c r="A159" s="6">
         <v>158</v>
       </c>
-      <c r="B159" s="122"/>
-      <c r="C159" s="123"/>
-      <c r="D159" s="124"/>
-      <c r="E159" s="125">
+      <c r="B159" s="121"/>
+      <c r="C159" s="122"/>
+      <c r="D159" s="123" t="s">
+        <v>859</v>
+      </c>
+      <c r="E159" s="124">
         <v>4</v>
       </c>
-      <c r="F159" s="129" t="s">
+      <c r="F159" s="128" t="s">
         <v>873</v>
       </c>
-      <c r="G159" s="127">
+      <c r="G159" s="126">
         <v>4.5601851851851853E-3</v>
       </c>
-      <c r="H159" s="124" t="s">
+      <c r="H159" s="123" t="s">
         <v>251</v>
       </c>
-      <c r="I159" s="124" t="s">
+      <c r="I159" s="123" t="s">
         <v>861</v>
       </c>
-      <c r="J159" s="124" t="s">
+      <c r="J159" s="123" t="s">
         <v>705</v>
       </c>
-      <c r="K159" s="124" t="s">
+      <c r="K159" s="123" t="s">
         <v>538</v>
       </c>
-      <c r="L159" s="124" t="s">
+      <c r="L159" s="123" t="s">
         <v>874</v>
       </c>
-      <c r="M159" s="128" t="s">
+      <c r="M159" s="127" t="s">
         <v>875</v>
       </c>
-      <c r="N159" s="124" t="s">
+      <c r="N159" s="123" t="s">
         <v>876</v>
       </c>
     </row>
-    <row r="160" spans="1:14" ht="400.8">
+    <row r="160" spans="1:14" ht="180">
       <c r="A160" s="5">
         <v>159</v>
       </c>
-      <c r="B160" s="130" t="s">
+      <c r="B160" s="129" t="s">
         <v>877</v>
       </c>
-      <c r="C160" s="131" t="s">
+      <c r="C160" s="130" t="s">
         <v>878</v>
       </c>
-      <c r="D160" s="132" t="s">
+      <c r="D160" s="131" t="s">
         <v>879</v>
       </c>
-      <c r="E160" s="133" t="s">
+      <c r="E160" s="132" t="s">
         <v>15</v>
       </c>
-      <c r="F160" s="132" t="s">
+      <c r="F160" s="131" t="s">
         <v>880</v>
       </c>
-      <c r="G160" s="134">
+      <c r="G160" s="133">
         <v>1.2824074074074075E-2</v>
       </c>
-      <c r="H160" s="132" t="s">
+      <c r="H160" s="131" t="s">
         <v>95</v>
       </c>
-      <c r="I160" s="132" t="s">
+      <c r="I160" s="131" t="s">
         <v>96</v>
       </c>
-      <c r="J160" s="132" t="s">
+      <c r="J160" s="131" t="s">
         <v>384</v>
       </c>
-      <c r="K160" s="132" t="s">
+      <c r="K160" s="131" t="s">
         <v>19</v>
       </c>
-      <c r="L160" s="132" t="s">
+      <c r="L160" s="131" t="s">
         <v>881</v>
       </c>
-      <c r="M160" s="135" t="s">
+      <c r="M160" s="134" t="s">
         <v>882</v>
       </c>
-      <c r="N160" s="132" t="s">
+      <c r="N160" s="131" t="s">
         <v>883</v>
       </c>
     </row>
-    <row r="161" spans="1:14" ht="409.6" thickBot="1">
+    <row r="161" spans="1:14" ht="227.4" thickBot="1">
       <c r="A161" s="6">
         <v>160</v>
       </c>
-      <c r="B161" s="130" t="s">
+      <c r="B161" s="129" t="s">
         <v>884</v>
       </c>
-      <c r="C161" s="131"/>
-      <c r="D161" s="132"/>
-      <c r="E161" s="133" t="s">
+      <c r="C161" s="130"/>
+      <c r="D161" s="131" t="s">
+        <v>879</v>
+      </c>
+      <c r="E161" s="132" t="s">
         <v>22</v>
       </c>
-      <c r="F161" s="132" t="s">
+      <c r="F161" s="131" t="s">
         <v>885</v>
       </c>
-      <c r="G161" s="134">
+      <c r="G161" s="133">
         <v>1.787037037037037E-2</v>
       </c>
-      <c r="H161" s="132" t="s">
+      <c r="H161" s="131" t="s">
         <v>95</v>
       </c>
-      <c r="I161" s="132" t="s">
+      <c r="I161" s="131" t="s">
         <v>96</v>
       </c>
-      <c r="J161" s="132" t="s">
+      <c r="J161" s="131" t="s">
         <v>384</v>
       </c>
-      <c r="K161" s="132" t="s">
+      <c r="K161" s="131" t="s">
         <v>19</v>
       </c>
-      <c r="L161" s="132" t="s">
+      <c r="L161" s="131" t="s">
         <v>886</v>
       </c>
-      <c r="M161" s="135" t="s">
+      <c r="M161" s="134" t="s">
         <v>887</v>
       </c>
-      <c r="N161" s="132" t="s">
+      <c r="N161" s="131" t="s">
         <v>888</v>
       </c>
     </row>
-    <row r="162" spans="1:14" ht="409.6">
+    <row r="162" spans="1:14" ht="244.2">
       <c r="A162" s="5">
         <v>161</v>
       </c>
-      <c r="B162" s="130" t="s">
+      <c r="B162" s="129" t="s">
         <v>889</v>
       </c>
-      <c r="C162" s="131"/>
-      <c r="D162" s="132"/>
-      <c r="E162" s="133" t="s">
+      <c r="C162" s="130"/>
+      <c r="D162" s="131" t="s">
+        <v>879</v>
+      </c>
+      <c r="E162" s="132" t="s">
         <v>27</v>
       </c>
-      <c r="F162" s="132" t="s">
+      <c r="F162" s="131" t="s">
         <v>890</v>
       </c>
-      <c r="G162" s="134">
+      <c r="G162" s="133">
         <v>1.9039351851851852E-2</v>
       </c>
-      <c r="H162" s="132" t="s">
+      <c r="H162" s="131" t="s">
         <v>236</v>
       </c>
-      <c r="I162" s="132" t="s">
+      <c r="I162" s="131" t="s">
         <v>891</v>
       </c>
-      <c r="J162" s="132" t="s">
+      <c r="J162" s="131" t="s">
         <v>384</v>
       </c>
-      <c r="K162" s="132" t="s">
+      <c r="K162" s="131" t="s">
         <v>19</v>
       </c>
-      <c r="L162" s="132" t="s">
+      <c r="L162" s="131" t="s">
         <v>892</v>
       </c>
-      <c r="M162" s="135" t="s">
+      <c r="M162" s="134" t="s">
         <v>893</v>
       </c>
-      <c r="N162" s="132" t="s">
+      <c r="N162" s="131" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="163" spans="1:14" ht="409.6" thickBot="1">
+    <row r="163" spans="1:14" ht="262.2" thickBot="1">
       <c r="A163" s="6">
         <v>162</v>
       </c>
-      <c r="B163" s="130" t="s">
+      <c r="B163" s="129" t="s">
         <v>895</v>
       </c>
-      <c r="C163" s="131"/>
-      <c r="D163" s="132"/>
-      <c r="E163" s="133" t="s">
+      <c r="C163" s="130"/>
+      <c r="D163" s="131" t="s">
+        <v>879</v>
+      </c>
+      <c r="E163" s="132" t="s">
         <v>31</v>
       </c>
-      <c r="F163" s="132" t="s">
+      <c r="F163" s="131" t="s">
         <v>896</v>
       </c>
-      <c r="G163" s="134">
+      <c r="G163" s="133">
         <v>1.5601851851851851E-2</v>
       </c>
-      <c r="H163" s="132" t="s">
+      <c r="H163" s="131" t="s">
         <v>95</v>
       </c>
-      <c r="I163" s="132" t="s">
+      <c r="I163" s="131" t="s">
         <v>96</v>
       </c>
-      <c r="J163" s="132" t="s">
+      <c r="J163" s="131" t="s">
         <v>384</v>
       </c>
-      <c r="K163" s="132" t="s">
+      <c r="K163" s="131" t="s">
         <v>19</v>
       </c>
-      <c r="L163" s="132" t="s">
+      <c r="L163" s="131" t="s">
         <v>897</v>
       </c>
-      <c r="M163" s="135" t="s">
+      <c r="M163" s="134" t="s">
         <v>898</v>
       </c>
-      <c r="N163" s="132" t="s">
+      <c r="N163" s="131" t="s">
         <v>899</v>
       </c>
     </row>
-    <row r="164" spans="1:14" ht="409.6">
+    <row r="164" spans="1:14" ht="261.60000000000002">
       <c r="A164" s="5">
         <v>163</v>
       </c>
-      <c r="B164" s="130" t="s">
+      <c r="B164" s="129" t="s">
         <v>900</v>
       </c>
-      <c r="C164" s="131"/>
-      <c r="D164" s="132"/>
-      <c r="E164" s="133" t="s">
+      <c r="C164" s="130"/>
+      <c r="D164" s="131" t="s">
+        <v>879</v>
+      </c>
+      <c r="E164" s="132" t="s">
         <v>35</v>
       </c>
-      <c r="F164" s="132" t="s">
+      <c r="F164" s="131" t="s">
         <v>901</v>
       </c>
-      <c r="G164" s="134">
+      <c r="G164" s="133">
         <v>1.4456018518518519E-2</v>
       </c>
-      <c r="H164" s="132" t="s">
+      <c r="H164" s="131" t="s">
         <v>17</v>
       </c>
-      <c r="I164" s="132" t="s">
+      <c r="I164" s="131" t="s">
         <v>115</v>
       </c>
-      <c r="J164" s="132" t="s">
+      <c r="J164" s="131" t="s">
         <v>384</v>
       </c>
-      <c r="K164" s="132" t="s">
+      <c r="K164" s="131" t="s">
         <v>19</v>
       </c>
-      <c r="L164" s="132" t="s">
+      <c r="L164" s="131" t="s">
         <v>902</v>
       </c>
-      <c r="M164" s="135" t="s">
+      <c r="M164" s="134" t="s">
         <v>903</v>
       </c>
-      <c r="N164" s="132" t="s">
+      <c r="N164" s="131" t="s">
         <v>904</v>
       </c>
     </row>
-    <row r="165" spans="1:14" ht="409.6" thickBot="1">
+    <row r="165" spans="1:14" ht="262.2" thickBot="1">
       <c r="A165" s="6">
         <v>164</v>
       </c>
-      <c r="B165" s="130" t="s">
+      <c r="B165" s="129" t="s">
         <v>905</v>
       </c>
-      <c r="C165" s="131"/>
-      <c r="D165" s="132"/>
-      <c r="E165" s="133" t="s">
+      <c r="C165" s="130"/>
+      <c r="D165" s="131" t="s">
+        <v>879</v>
+      </c>
+      <c r="E165" s="132" t="s">
         <v>39</v>
       </c>
-      <c r="F165" s="132" t="s">
+      <c r="F165" s="131" t="s">
         <v>906</v>
       </c>
-      <c r="G165" s="134">
+      <c r="G165" s="133">
         <v>1.2627314814814815E-2</v>
       </c>
-      <c r="H165" s="132" t="s">
+      <c r="H165" s="131" t="s">
         <v>236</v>
       </c>
-      <c r="I165" s="132" t="s">
+      <c r="I165" s="131" t="s">
         <v>891</v>
       </c>
-      <c r="J165" s="132" t="s">
+      <c r="J165" s="131" t="s">
         <v>384</v>
       </c>
-      <c r="K165" s="132" t="s">
+      <c r="K165" s="131" t="s">
         <v>19</v>
       </c>
-      <c r="L165" s="132" t="s">
+      <c r="L165" s="131" t="s">
         <v>907</v>
       </c>
-      <c r="M165" s="135" t="s">
+      <c r="M165" s="134" t="s">
         <v>903</v>
       </c>
-      <c r="N165" s="132" t="s">
+      <c r="N165" s="131" t="s">
         <v>908</v>
       </c>
     </row>
-    <row r="166" spans="1:14" ht="409.6">
+    <row r="166" spans="1:14" ht="216">
       <c r="A166" s="5">
         <v>165</v>
       </c>
-      <c r="B166" s="130" t="s">
+      <c r="B166" s="129" t="s">
         <v>909</v>
       </c>
-      <c r="C166" s="131"/>
-      <c r="D166" s="132"/>
-      <c r="E166" s="133" t="s">
+      <c r="C166" s="130"/>
+      <c r="D166" s="131" t="s">
+        <v>879</v>
+      </c>
+      <c r="E166" s="132" t="s">
         <v>43</v>
       </c>
-      <c r="F166" s="132" t="s">
+      <c r="F166" s="131" t="s">
         <v>910</v>
       </c>
-      <c r="G166" s="134">
+      <c r="G166" s="133">
         <v>1.2453703703703703E-2</v>
       </c>
-      <c r="H166" s="132" t="s">
+      <c r="H166" s="131" t="s">
         <v>107</v>
       </c>
-      <c r="I166" s="132" t="s">
+      <c r="I166" s="131" t="s">
         <v>108</v>
       </c>
-      <c r="J166" s="132" t="s">
+      <c r="J166" s="131" t="s">
         <v>384</v>
       </c>
-      <c r="K166" s="132" t="s">
+      <c r="K166" s="131" t="s">
         <v>19</v>
       </c>
-      <c r="L166" s="132" t="s">
+      <c r="L166" s="131" t="s">
         <v>911</v>
       </c>
-      <c r="M166" s="135" t="s">
+      <c r="M166" s="134" t="s">
         <v>912</v>
       </c>
-      <c r="N166" s="132" t="s">
+      <c r="N166" s="131" t="s">
         <v>913</v>
       </c>
     </row>
-    <row r="167" spans="1:14" ht="401.4" thickBot="1">
+    <row r="167" spans="1:14" ht="216.6" thickBot="1">
       <c r="A167" s="6">
         <v>166</v>
       </c>
-      <c r="B167" s="136" t="s">
+      <c r="B167" s="135" t="s">
         <v>13</v>
       </c>
-      <c r="C167" s="137" t="s">
+      <c r="C167" s="136" t="s">
         <v>914</v>
       </c>
-      <c r="D167" s="138" t="s">
+      <c r="D167" s="137" t="s">
         <v>14</v>
       </c>
-      <c r="E167" s="139" t="s">
+      <c r="E167" s="138" t="s">
         <v>15</v>
       </c>
-      <c r="F167" s="138" t="s">
+      <c r="F167" s="137" t="s">
         <v>16</v>
       </c>
-      <c r="G167" s="140">
+      <c r="G167" s="139">
         <v>3.982638888888889E-2</v>
       </c>
-      <c r="H167" s="138" t="s">
+      <c r="H167" s="137" t="s">
         <v>17</v>
       </c>
-      <c r="I167" s="138" t="s">
+      <c r="I167" s="137" t="s">
         <v>18</v>
       </c>
-      <c r="J167" s="138" t="s">
+      <c r="J167" s="137" t="s">
         <v>915</v>
       </c>
-      <c r="K167" s="138" t="s">
+      <c r="K167" s="137" t="s">
         <v>19</v>
       </c>
-      <c r="L167" s="138" t="s">
+      <c r="L167" s="137" t="s">
         <v>916</v>
       </c>
-      <c r="M167" s="141" t="s">
+      <c r="M167" s="140" t="s">
         <v>20</v>
       </c>
-      <c r="N167" s="138" t="s">
+      <c r="N167" s="137" t="s">
         <v>917</v>
       </c>
     </row>
-    <row r="168" spans="1:14" ht="313.8">
+    <row r="168" spans="1:14" ht="234">
       <c r="A168" s="5">
         <v>167</v>
       </c>
-      <c r="B168" s="136" t="s">
+      <c r="B168" s="135" t="s">
         <v>21</v>
       </c>
-      <c r="C168" s="137"/>
-      <c r="D168" s="138"/>
-      <c r="E168" s="139" t="s">
+      <c r="C168" s="136"/>
+      <c r="D168" s="137" t="s">
+        <v>14</v>
+      </c>
+      <c r="E168" s="138" t="s">
         <v>22</v>
       </c>
-      <c r="F168" s="138" t="s">
+      <c r="F168" s="137" t="s">
         <v>23</v>
       </c>
-      <c r="G168" s="140">
+      <c r="G168" s="139">
         <v>3.7326388888888888E-2</v>
       </c>
-      <c r="H168" s="138" t="s">
+      <c r="H168" s="137" t="s">
         <v>17</v>
       </c>
-      <c r="I168" s="138" t="s">
+      <c r="I168" s="137" t="s">
         <v>918</v>
       </c>
-      <c r="J168" s="138" t="s">
+      <c r="J168" s="137" t="s">
         <v>915</v>
       </c>
-      <c r="K168" s="138" t="s">
+      <c r="K168" s="137" t="s">
         <v>19</v>
       </c>
-      <c r="L168" s="138" t="s">
+      <c r="L168" s="137" t="s">
         <v>919</v>
       </c>
-      <c r="M168" s="141" t="s">
+      <c r="M168" s="140" t="s">
         <v>25</v>
       </c>
-      <c r="N168" s="138" t="s">
+      <c r="N168" s="137" t="s">
         <v>920</v>
       </c>
     </row>
-    <row r="169" spans="1:14" ht="349.2" thickBot="1">
+    <row r="169" spans="1:14" ht="180.6" thickBot="1">
       <c r="A169" s="6">
         <v>168</v>
       </c>
-      <c r="B169" s="136" t="s">
+      <c r="B169" s="135" t="s">
         <v>26</v>
       </c>
-      <c r="C169" s="137"/>
-      <c r="D169" s="138"/>
-      <c r="E169" s="139" t="s">
+      <c r="C169" s="136"/>
+      <c r="D169" s="137" t="s">
+        <v>14</v>
+      </c>
+      <c r="E169" s="138" t="s">
         <v>27</v>
       </c>
-      <c r="F169" s="138" t="s">
+      <c r="F169" s="137" t="s">
         <v>28</v>
       </c>
-      <c r="G169" s="140">
+      <c r="G169" s="139">
         <v>3.9155092592592596E-2</v>
       </c>
-      <c r="H169" s="138" t="s">
+      <c r="H169" s="137" t="s">
         <v>17</v>
       </c>
-      <c r="I169" s="138" t="s">
+      <c r="I169" s="137" t="s">
         <v>918</v>
       </c>
-      <c r="J169" s="138" t="s">
+      <c r="J169" s="137" t="s">
         <v>915</v>
       </c>
-      <c r="K169" s="138" t="s">
+      <c r="K169" s="137" t="s">
         <v>19</v>
       </c>
-      <c r="L169" s="138" t="s">
+      <c r="L169" s="137" t="s">
         <v>921</v>
       </c>
-      <c r="M169" s="141" t="s">
+      <c r="M169" s="140" t="s">
         <v>29</v>
       </c>
-      <c r="N169" s="138" t="s">
+      <c r="N169" s="137" t="s">
         <v>922</v>
       </c>
     </row>
-    <row r="170" spans="1:14" ht="366">
+    <row r="170" spans="1:14" ht="198">
       <c r="A170" s="5">
         <v>169</v>
       </c>
-      <c r="B170" s="136" t="s">
+      <c r="B170" s="135" t="s">
         <v>30</v>
       </c>
-      <c r="C170" s="137"/>
-      <c r="D170" s="138"/>
-      <c r="E170" s="139" t="s">
+      <c r="C170" s="136"/>
+      <c r="D170" s="137" t="s">
+        <v>14</v>
+      </c>
+      <c r="E170" s="138" t="s">
         <v>31</v>
       </c>
-      <c r="F170" s="138" t="s">
+      <c r="F170" s="137" t="s">
         <v>32</v>
       </c>
-      <c r="G170" s="140">
+      <c r="G170" s="139">
         <v>3.0601851851851852E-2</v>
       </c>
-      <c r="H170" s="138" t="s">
+      <c r="H170" s="137" t="s">
         <v>17</v>
       </c>
-      <c r="I170" s="138" t="s">
+      <c r="I170" s="137" t="s">
         <v>918</v>
       </c>
-      <c r="J170" s="138" t="s">
+      <c r="J170" s="137" t="s">
         <v>923</v>
       </c>
-      <c r="K170" s="138" t="s">
+      <c r="K170" s="137" t="s">
         <v>19</v>
       </c>
-      <c r="L170" s="138" t="s">
+      <c r="L170" s="137" t="s">
         <v>924</v>
       </c>
-      <c r="M170" s="141" t="s">
+      <c r="M170" s="140" t="s">
         <v>33</v>
       </c>
-      <c r="N170" s="138" t="s">
+      <c r="N170" s="137" t="s">
         <v>925</v>
       </c>
     </row>
-    <row r="171" spans="1:14" ht="244.8" thickBot="1">
+    <row r="171" spans="1:14" ht="216.6" thickBot="1">
       <c r="A171" s="6">
         <v>170</v>
       </c>
-      <c r="B171" s="136" t="s">
+      <c r="B171" s="135" t="s">
         <v>34</v>
       </c>
-      <c r="C171" s="137"/>
-      <c r="D171" s="138"/>
-      <c r="E171" s="139" t="s">
+      <c r="C171" s="136"/>
+      <c r="D171" s="137" t="s">
+        <v>14</v>
+      </c>
+      <c r="E171" s="138" t="s">
         <v>35</v>
       </c>
-      <c r="F171" s="138" t="s">
+      <c r="F171" s="137" t="s">
         <v>36</v>
       </c>
-      <c r="G171" s="140">
+      <c r="G171" s="139">
         <v>4.659722222222222E-2</v>
       </c>
-      <c r="H171" s="138" t="s">
+      <c r="H171" s="137" t="s">
         <v>17</v>
       </c>
-      <c r="I171" s="138" t="s">
+      <c r="I171" s="137" t="s">
         <v>918</v>
       </c>
-      <c r="J171" s="138" t="s">
+      <c r="J171" s="137" t="s">
         <v>116</v>
       </c>
-      <c r="K171" s="138" t="s">
+      <c r="K171" s="137" t="s">
         <v>19</v>
       </c>
-      <c r="L171" s="138" t="s">
+      <c r="L171" s="137" t="s">
         <v>926</v>
       </c>
-      <c r="M171" s="141" t="s">
+      <c r="M171" s="140" t="s">
         <v>37</v>
       </c>
-      <c r="N171" s="138" t="s">
+      <c r="N171" s="137" t="s">
         <v>927</v>
       </c>
     </row>
-    <row r="172" spans="1:14" ht="244.2">
+    <row r="172" spans="1:14" ht="198">
       <c r="A172" s="5">
         <v>171</v>
       </c>
-      <c r="B172" s="136" t="s">
+      <c r="B172" s="135" t="s">
         <v>38</v>
       </c>
-      <c r="C172" s="137"/>
-      <c r="D172" s="138"/>
-      <c r="E172" s="139" t="s">
+      <c r="C172" s="136"/>
+      <c r="D172" s="137" t="s">
+        <v>14</v>
+      </c>
+      <c r="E172" s="138" t="s">
         <v>39</v>
       </c>
-      <c r="F172" s="138" t="s">
+      <c r="F172" s="137" t="s">
         <v>40</v>
       </c>
-      <c r="G172" s="140">
+      <c r="G172" s="139">
         <v>1.9155092592592592E-2</v>
       </c>
-      <c r="H172" s="138" t="s">
+      <c r="H172" s="137" t="s">
         <v>17</v>
       </c>
-      <c r="I172" s="138" t="s">
+      <c r="I172" s="137" t="s">
         <v>918</v>
       </c>
-      <c r="J172" s="138" t="s">
+      <c r="J172" s="137" t="s">
         <v>116</v>
       </c>
-      <c r="K172" s="138" t="s">
+      <c r="K172" s="137" t="s">
         <v>19</v>
       </c>
-      <c r="L172" s="138" t="s">
+      <c r="L172" s="137" t="s">
         <v>928</v>
       </c>
-      <c r="M172" s="141" t="s">
+      <c r="M172" s="140" t="s">
         <v>41</v>
       </c>
-      <c r="N172" s="138" t="s">
+      <c r="N172" s="137" t="s">
         <v>929</v>
       </c>
     </row>
-    <row r="173" spans="1:14" ht="384" thickBot="1">
+    <row r="173" spans="1:14" ht="198.6" thickBot="1">
       <c r="A173" s="6">
         <v>172</v>
       </c>
-      <c r="B173" s="136" t="s">
+      <c r="B173" s="135" t="s">
         <v>42</v>
       </c>
-      <c r="C173" s="137"/>
-      <c r="D173" s="138"/>
-      <c r="E173" s="139" t="s">
+      <c r="C173" s="136"/>
+      <c r="D173" s="137" t="s">
+        <v>14</v>
+      </c>
+      <c r="E173" s="138" t="s">
         <v>43</v>
       </c>
-      <c r="F173" s="142" t="s">
+      <c r="F173" s="141" t="s">
         <v>44</v>
       </c>
-      <c r="G173" s="140">
+      <c r="G173" s="139">
         <v>2.5138888888888888E-2</v>
       </c>
-      <c r="H173" s="138" t="s">
+      <c r="H173" s="137" t="s">
         <v>17</v>
       </c>
-      <c r="I173" s="138" t="s">
+      <c r="I173" s="137" t="s">
         <v>45</v>
       </c>
-      <c r="J173" s="138" t="s">
+      <c r="J173" s="137" t="s">
         <v>930</v>
       </c>
-      <c r="K173" s="138" t="s">
+      <c r="K173" s="137" t="s">
         <v>19</v>
       </c>
-      <c r="L173" s="138" t="s">
+      <c r="L173" s="137" t="s">
         <v>931</v>
       </c>
-      <c r="M173" s="141" t="s">
+      <c r="M173" s="140" t="s">
         <v>46</v>
       </c>
-      <c r="N173" s="138" t="s">
+      <c r="N173" s="137" t="s">
         <v>932</v>
       </c>
     </row>
-    <row r="174" spans="1:14" ht="296.39999999999998">
+    <row r="174" spans="1:14" ht="198">
       <c r="A174" s="5">
         <v>173</v>
       </c>
-      <c r="B174" s="136" t="s">
+      <c r="B174" s="135" t="s">
         <v>47</v>
       </c>
-      <c r="C174" s="137"/>
-      <c r="D174" s="138"/>
-      <c r="E174" s="139" t="s">
+      <c r="C174" s="136"/>
+      <c r="D174" s="137" t="s">
+        <v>14</v>
+      </c>
+      <c r="E174" s="138" t="s">
         <v>48</v>
       </c>
-      <c r="F174" s="138" t="s">
+      <c r="F174" s="137" t="s">
         <v>49</v>
       </c>
-      <c r="G174" s="140">
+      <c r="G174" s="139">
         <v>1.9293981481481481E-2</v>
       </c>
-      <c r="H174" s="138" t="s">
+      <c r="H174" s="137" t="s">
         <v>17</v>
       </c>
-      <c r="I174" s="138" t="s">
+      <c r="I174" s="137" t="s">
         <v>45</v>
       </c>
-      <c r="J174" s="138" t="s">
+      <c r="J174" s="137" t="s">
         <v>930</v>
       </c>
-      <c r="K174" s="138" t="s">
+      <c r="K174" s="137" t="s">
         <v>19</v>
       </c>
-      <c r="L174" s="138" t="s">
+      <c r="L174" s="137" t="s">
         <v>933</v>
       </c>
-      <c r="M174" s="141" t="s">
+      <c r="M174" s="140" t="s">
         <v>50</v>
       </c>
-      <c r="N174" s="138" t="s">
+      <c r="N174" s="137" t="s">
         <v>934</v>
       </c>
     </row>
-    <row r="175" spans="1:14" ht="262.2" thickBot="1">
+    <row r="175" spans="1:14" ht="180.6" thickBot="1">
       <c r="A175" s="6">
         <v>174</v>
       </c>
-      <c r="B175" s="136" t="s">
+      <c r="B175" s="135" t="s">
         <v>51</v>
       </c>
-      <c r="C175" s="137"/>
-      <c r="D175" s="138"/>
-      <c r="E175" s="139" t="s">
+      <c r="C175" s="136"/>
+      <c r="D175" s="137" t="s">
+        <v>14</v>
+      </c>
+      <c r="E175" s="138" t="s">
         <v>52</v>
       </c>
-      <c r="F175" s="138" t="s">
+      <c r="F175" s="137" t="s">
         <v>53</v>
       </c>
-      <c r="G175" s="140">
+      <c r="G175" s="139">
         <v>3.2048611111111111E-2</v>
       </c>
-      <c r="H175" s="138" t="s">
+      <c r="H175" s="137" t="s">
         <v>17</v>
       </c>
-      <c r="I175" s="138" t="s">
+      <c r="I175" s="137" t="s">
         <v>45</v>
       </c>
-      <c r="J175" s="138" t="s">
+      <c r="J175" s="137" t="s">
         <v>935</v>
       </c>
-      <c r="K175" s="138" t="s">
+      <c r="K175" s="137" t="s">
         <v>19</v>
       </c>
-      <c r="L175" s="138" t="s">
+      <c r="L175" s="137" t="s">
         <v>936</v>
       </c>
-      <c r="M175" s="141" t="s">
+      <c r="M175" s="140" t="s">
         <v>54</v>
       </c>
-      <c r="N175" s="138" t="s">
+      <c r="N175" s="137" t="s">
         <v>937</v>
       </c>
     </row>
-    <row r="176" spans="1:14" ht="409.6">
+    <row r="176" spans="1:14" ht="198">
       <c r="A176" s="5">
         <v>175</v>
       </c>
-      <c r="B176" s="136" t="s">
+      <c r="B176" s="135" t="s">
         <v>55</v>
       </c>
-      <c r="C176" s="137"/>
-      <c r="D176" s="138"/>
-      <c r="E176" s="139" t="s">
+      <c r="C176" s="136"/>
+      <c r="D176" s="137" t="s">
+        <v>14</v>
+      </c>
+      <c r="E176" s="138" t="s">
         <v>56</v>
       </c>
-      <c r="F176" s="138" t="s">
+      <c r="F176" s="137" t="s">
         <v>57</v>
       </c>
-      <c r="G176" s="140">
+      <c r="G176" s="139">
         <v>4.7581018518518516E-2</v>
       </c>
-      <c r="H176" s="138" t="s">
+      <c r="H176" s="137" t="s">
         <v>17</v>
       </c>
-      <c r="I176" s="138" t="s">
+      <c r="I176" s="137" t="s">
         <v>58</v>
       </c>
-      <c r="J176" s="138" t="s">
+      <c r="J176" s="137" t="s">
         <v>935</v>
       </c>
-      <c r="K176" s="138" t="s">
+      <c r="K176" s="137" t="s">
         <v>19</v>
       </c>
-      <c r="L176" s="138" t="s">
+      <c r="L176" s="137" t="s">
         <v>938</v>
       </c>
-      <c r="M176" s="141" t="s">
+      <c r="M176" s="140" t="s">
         <v>59</v>
       </c>
-      <c r="N176" s="138" t="s">
+      <c r="N176" s="137" t="s">
         <v>939</v>
       </c>
     </row>
-    <row r="177" spans="1:14" ht="279.60000000000002" thickBot="1">
+    <row r="177" spans="1:14" ht="216.6" thickBot="1">
       <c r="A177" s="6">
         <v>176</v>
       </c>
-      <c r="B177" s="136" t="s">
+      <c r="B177" s="135" t="s">
         <v>60</v>
       </c>
-      <c r="C177" s="137"/>
-      <c r="D177" s="138"/>
-      <c r="E177" s="139" t="s">
+      <c r="C177" s="136"/>
+      <c r="D177" s="137" t="s">
+        <v>14</v>
+      </c>
+      <c r="E177" s="138" t="s">
         <v>61</v>
       </c>
-      <c r="F177" s="138" t="s">
+      <c r="F177" s="137" t="s">
         <v>62</v>
       </c>
-      <c r="G177" s="140">
+      <c r="G177" s="139">
         <v>3.951388888888889E-2</v>
       </c>
-      <c r="H177" s="138" t="s">
+      <c r="H177" s="137" t="s">
         <v>17</v>
       </c>
-      <c r="I177" s="138" t="s">
+      <c r="I177" s="137" t="s">
         <v>58</v>
       </c>
-      <c r="J177" s="138" t="s">
+      <c r="J177" s="137" t="s">
         <v>940</v>
       </c>
-      <c r="K177" s="138" t="s">
+      <c r="K177" s="137" t="s">
         <v>19</v>
       </c>
-      <c r="L177" s="138" t="s">
+      <c r="L177" s="137" t="s">
         <v>941</v>
       </c>
-      <c r="M177" s="141" t="s">
+      <c r="M177" s="140" t="s">
         <v>63</v>
       </c>
-      <c r="N177" s="138" t="s">
+      <c r="N177" s="137" t="s">
         <v>942</v>
       </c>
     </row>
-    <row r="178" spans="1:14" ht="279">
+    <row r="178" spans="1:14" ht="216">
       <c r="A178" s="5">
         <v>177</v>
       </c>
-      <c r="B178" s="136" t="s">
+      <c r="B178" s="135" t="s">
         <v>64</v>
       </c>
-      <c r="C178" s="137"/>
-      <c r="D178" s="138"/>
-      <c r="E178" s="139" t="s">
+      <c r="C178" s="136"/>
+      <c r="D178" s="137" t="s">
+        <v>14</v>
+      </c>
+      <c r="E178" s="138" t="s">
         <v>65</v>
       </c>
-      <c r="F178" s="138" t="s">
+      <c r="F178" s="137" t="s">
         <v>66</v>
       </c>
-      <c r="G178" s="140">
+      <c r="G178" s="139">
         <v>2.826388888888889E-2</v>
       </c>
-      <c r="H178" s="138" t="s">
+      <c r="H178" s="137" t="s">
         <v>17</v>
       </c>
-      <c r="I178" s="138" t="s">
+      <c r="I178" s="137" t="s">
         <v>58</v>
       </c>
-      <c r="J178" s="138" t="s">
+      <c r="J178" s="137" t="s">
         <v>940</v>
       </c>
-      <c r="K178" s="138" t="s">
+      <c r="K178" s="137" t="s">
         <v>19</v>
       </c>
-      <c r="L178" s="138" t="s">
+      <c r="L178" s="137" t="s">
         <v>943</v>
       </c>
-      <c r="M178" s="141" t="s">
+      <c r="M178" s="140" t="s">
         <v>67</v>
       </c>
-      <c r="N178" s="138" t="s">
+      <c r="N178" s="137" t="s">
         <v>944</v>
       </c>
     </row>
@@ -12736,43 +13044,43 @@
       <c r="A179" s="6">
         <v>178</v>
       </c>
-      <c r="B179" s="143" t="s">
+      <c r="B179" s="142" t="s">
         <v>945</v>
       </c>
-      <c r="C179" s="144" t="s">
+      <c r="C179" s="143" t="s">
         <v>946</v>
       </c>
-      <c r="D179" s="145" t="s">
+      <c r="D179" s="144" t="s">
         <v>947</v>
       </c>
-      <c r="E179" s="146" t="s">
+      <c r="E179" s="145" t="s">
         <v>15</v>
       </c>
-      <c r="F179" s="145" t="s">
+      <c r="F179" s="144" t="s">
         <v>948</v>
       </c>
-      <c r="G179" s="147">
+      <c r="G179" s="146">
         <v>1.3796296296296296E-2</v>
       </c>
-      <c r="H179" s="145" t="s">
+      <c r="H179" s="144" t="s">
         <v>17</v>
       </c>
-      <c r="I179" s="145" t="s">
+      <c r="I179" s="144" t="s">
         <v>18</v>
       </c>
-      <c r="J179" s="145" t="s">
+      <c r="J179" s="144" t="s">
         <v>949</v>
       </c>
-      <c r="K179" s="145" t="s">
+      <c r="K179" s="144" t="s">
         <v>19</v>
       </c>
-      <c r="L179" s="145" t="s">
+      <c r="L179" s="144" t="s">
         <v>950</v>
       </c>
-      <c r="M179" s="148" t="s">
+      <c r="M179" s="147" t="s">
         <v>951</v>
       </c>
-      <c r="N179" s="145" t="s">
+      <c r="N179" s="144" t="s">
         <v>952</v>
       </c>
     </row>
@@ -12780,39 +13088,41 @@
       <c r="A180" s="5">
         <v>179</v>
       </c>
-      <c r="B180" s="143" t="s">
+      <c r="B180" s="142" t="s">
         <v>953</v>
       </c>
-      <c r="C180" s="144"/>
-      <c r="D180" s="145"/>
-      <c r="E180" s="146" t="s">
+      <c r="C180" s="143"/>
+      <c r="D180" s="144" t="s">
+        <v>947</v>
+      </c>
+      <c r="E180" s="145" t="s">
         <v>22</v>
       </c>
-      <c r="F180" s="145" t="s">
+      <c r="F180" s="144" t="s">
         <v>954</v>
       </c>
-      <c r="G180" s="147">
+      <c r="G180" s="146">
         <v>8.0555555555555554E-3</v>
       </c>
-      <c r="H180" s="145" t="s">
+      <c r="H180" s="144" t="s">
         <v>244</v>
       </c>
-      <c r="I180" s="145" t="s">
+      <c r="I180" s="144" t="s">
         <v>341</v>
       </c>
-      <c r="J180" s="145" t="s">
+      <c r="J180" s="144" t="s">
         <v>384</v>
       </c>
-      <c r="K180" s="145" t="s">
+      <c r="K180" s="144" t="s">
         <v>19</v>
       </c>
-      <c r="L180" s="145" t="s">
+      <c r="L180" s="144" t="s">
         <v>955</v>
       </c>
-      <c r="M180" s="148" t="s">
+      <c r="M180" s="147" t="s">
         <v>956</v>
       </c>
-      <c r="N180" s="145" t="s">
+      <c r="N180" s="144" t="s">
         <v>957</v>
       </c>
     </row>
@@ -12820,79 +13130,83 @@
       <c r="A181" s="6">
         <v>180</v>
       </c>
-      <c r="B181" s="143" t="s">
+      <c r="B181" s="142" t="s">
         <v>958</v>
       </c>
-      <c r="C181" s="144"/>
-      <c r="D181" s="145"/>
-      <c r="E181" s="146" t="s">
+      <c r="C181" s="143"/>
+      <c r="D181" s="144" t="s">
+        <v>947</v>
+      </c>
+      <c r="E181" s="145" t="s">
         <v>27</v>
       </c>
-      <c r="F181" s="145" t="s">
+      <c r="F181" s="144" t="s">
         <v>959</v>
       </c>
-      <c r="G181" s="147">
+      <c r="G181" s="146">
         <v>1.5266203703703704E-2</v>
       </c>
-      <c r="H181" s="145" t="s">
+      <c r="H181" s="144" t="s">
         <v>17</v>
       </c>
-      <c r="I181" s="145" t="s">
+      <c r="I181" s="144" t="s">
         <v>18</v>
       </c>
-      <c r="J181" s="145" t="s">
+      <c r="J181" s="144" t="s">
         <v>949</v>
       </c>
-      <c r="K181" s="145" t="s">
+      <c r="K181" s="144" t="s">
         <v>19</v>
       </c>
-      <c r="L181" s="145" t="s">
+      <c r="L181" s="144" t="s">
         <v>960</v>
       </c>
-      <c r="M181" s="148" t="s">
+      <c r="M181" s="147" t="s">
         <v>961</v>
       </c>
-      <c r="N181" s="145" t="s">
+      <c r="N181" s="144" t="s">
         <v>962</v>
       </c>
     </row>
-    <row r="182" spans="1:14" ht="162">
+    <row r="182" spans="1:14" ht="180">
       <c r="A182" s="5">
         <v>181</v>
       </c>
-      <c r="B182" s="143" t="s">
+      <c r="B182" s="142" t="s">
         <v>963</v>
       </c>
-      <c r="C182" s="144"/>
-      <c r="D182" s="145"/>
-      <c r="E182" s="146" t="s">
+      <c r="C182" s="143"/>
+      <c r="D182" s="144" t="s">
+        <v>947</v>
+      </c>
+      <c r="E182" s="145" t="s">
         <v>31</v>
       </c>
-      <c r="F182" s="145" t="s">
+      <c r="F182" s="144" t="s">
         <v>964</v>
       </c>
-      <c r="G182" s="147">
+      <c r="G182" s="146">
         <v>1.1967592592592592E-2</v>
       </c>
-      <c r="H182" s="145" t="s">
+      <c r="H182" s="144" t="s">
         <v>236</v>
       </c>
-      <c r="I182" s="145" t="s">
+      <c r="I182" s="144" t="s">
         <v>891</v>
       </c>
-      <c r="J182" s="145" t="s">
+      <c r="J182" s="144" t="s">
         <v>965</v>
       </c>
-      <c r="K182" s="145" t="s">
+      <c r="K182" s="144" t="s">
         <v>19</v>
       </c>
-      <c r="L182" s="145" t="s">
+      <c r="L182" s="144" t="s">
         <v>966</v>
       </c>
-      <c r="M182" s="148" t="s">
+      <c r="M182" s="147" t="s">
         <v>967</v>
       </c>
-      <c r="N182" s="145" t="s">
+      <c r="N182" s="144" t="s">
         <v>968</v>
       </c>
     </row>
@@ -12900,39 +13214,41 @@
       <c r="A183" s="6">
         <v>182</v>
       </c>
-      <c r="B183" s="143" t="s">
+      <c r="B183" s="142" t="s">
         <v>969</v>
       </c>
-      <c r="C183" s="144"/>
-      <c r="D183" s="145"/>
-      <c r="E183" s="146" t="s">
+      <c r="C183" s="143"/>
+      <c r="D183" s="144" t="s">
+        <v>947</v>
+      </c>
+      <c r="E183" s="145" t="s">
         <v>35</v>
       </c>
-      <c r="F183" s="145" t="s">
+      <c r="F183" s="144" t="s">
         <v>970</v>
       </c>
-      <c r="G183" s="147">
+      <c r="G183" s="146">
         <v>1.2037037037037037E-2</v>
       </c>
-      <c r="H183" s="145" t="s">
+      <c r="H183" s="144" t="s">
         <v>236</v>
       </c>
-      <c r="I183" s="145" t="s">
+      <c r="I183" s="144" t="s">
         <v>891</v>
       </c>
-      <c r="J183" s="145" t="s">
+      <c r="J183" s="144" t="s">
         <v>965</v>
       </c>
-      <c r="K183" s="145" t="s">
+      <c r="K183" s="144" t="s">
         <v>19</v>
       </c>
-      <c r="L183" s="145" t="s">
+      <c r="L183" s="144" t="s">
         <v>971</v>
       </c>
-      <c r="M183" s="148" t="s">
+      <c r="M183" s="147" t="s">
         <v>972</v>
       </c>
-      <c r="N183" s="145" t="s">
+      <c r="N183" s="144" t="s">
         <v>973</v>
       </c>
     </row>
@@ -12940,39 +13256,41 @@
       <c r="A184" s="5">
         <v>183</v>
       </c>
-      <c r="B184" s="143" t="s">
+      <c r="B184" s="142" t="s">
         <v>974</v>
       </c>
-      <c r="C184" s="144"/>
-      <c r="D184" s="145"/>
-      <c r="E184" s="146" t="s">
+      <c r="C184" s="143"/>
+      <c r="D184" s="144" t="s">
+        <v>947</v>
+      </c>
+      <c r="E184" s="145" t="s">
         <v>39</v>
       </c>
-      <c r="F184" s="145" t="s">
+      <c r="F184" s="144" t="s">
         <v>975</v>
       </c>
-      <c r="G184" s="147">
+      <c r="G184" s="146">
         <v>1.3703703703703704E-2</v>
       </c>
-      <c r="H184" s="145" t="s">
+      <c r="H184" s="144" t="s">
         <v>17</v>
       </c>
-      <c r="I184" s="145" t="s">
+      <c r="I184" s="144" t="s">
         <v>918</v>
       </c>
-      <c r="J184" s="145" t="s">
+      <c r="J184" s="144" t="s">
         <v>949</v>
       </c>
-      <c r="K184" s="145" t="s">
+      <c r="K184" s="144" t="s">
         <v>19</v>
       </c>
-      <c r="L184" s="145" t="s">
+      <c r="L184" s="144" t="s">
         <v>976</v>
       </c>
-      <c r="M184" s="148" t="s">
+      <c r="M184" s="147" t="s">
         <v>977</v>
       </c>
-      <c r="N184" s="145" t="s">
+      <c r="N184" s="144" t="s">
         <v>978</v>
       </c>
     </row>
@@ -12980,39 +13298,41 @@
       <c r="A185" s="6">
         <v>184</v>
       </c>
-      <c r="B185" s="143" t="s">
+      <c r="B185" s="142" t="s">
         <v>979</v>
       </c>
-      <c r="C185" s="144"/>
-      <c r="D185" s="145"/>
-      <c r="E185" s="146" t="s">
+      <c r="C185" s="143"/>
+      <c r="D185" s="144" t="s">
+        <v>947</v>
+      </c>
+      <c r="E185" s="145" t="s">
         <v>43</v>
       </c>
-      <c r="F185" s="145" t="s">
+      <c r="F185" s="144" t="s">
         <v>980</v>
       </c>
-      <c r="G185" s="147">
+      <c r="G185" s="146">
         <v>5.9606481481481481E-3</v>
       </c>
-      <c r="H185" s="145" t="s">
+      <c r="H185" s="144" t="s">
         <v>17</v>
       </c>
-      <c r="I185" s="145" t="s">
+      <c r="I185" s="144" t="s">
         <v>354</v>
       </c>
-      <c r="J185" s="145" t="s">
+      <c r="J185" s="144" t="s">
         <v>384</v>
       </c>
-      <c r="K185" s="145" t="s">
+      <c r="K185" s="144" t="s">
         <v>19</v>
       </c>
-      <c r="L185" s="145" t="s">
+      <c r="L185" s="144" t="s">
         <v>981</v>
       </c>
-      <c r="M185" s="148" t="s">
+      <c r="M185" s="147" t="s">
         <v>982</v>
       </c>
-      <c r="N185" s="145" t="s">
+      <c r="N185" s="144" t="s">
         <v>983</v>
       </c>
     </row>
@@ -13020,39 +13340,41 @@
       <c r="A186" s="5">
         <v>185</v>
       </c>
-      <c r="B186" s="143" t="s">
+      <c r="B186" s="142" t="s">
         <v>984</v>
       </c>
-      <c r="C186" s="144"/>
-      <c r="D186" s="145"/>
-      <c r="E186" s="146" t="s">
+      <c r="C186" s="143"/>
+      <c r="D186" s="144" t="s">
+        <v>947</v>
+      </c>
+      <c r="E186" s="145" t="s">
         <v>48</v>
       </c>
-      <c r="F186" s="145" t="s">
+      <c r="F186" s="144" t="s">
         <v>985</v>
       </c>
-      <c r="G186" s="147">
+      <c r="G186" s="146">
         <v>7.037037037037037E-3</v>
       </c>
-      <c r="H186" s="145" t="s">
+      <c r="H186" s="144" t="s">
         <v>17</v>
       </c>
-      <c r="I186" s="145" t="s">
+      <c r="I186" s="144" t="s">
         <v>354</v>
       </c>
-      <c r="J186" s="145" t="s">
+      <c r="J186" s="144" t="s">
         <v>384</v>
       </c>
-      <c r="K186" s="145" t="s">
+      <c r="K186" s="144" t="s">
         <v>19</v>
       </c>
-      <c r="L186" s="145" t="s">
+      <c r="L186" s="144" t="s">
         <v>986</v>
       </c>
-      <c r="M186" s="148" t="s">
+      <c r="M186" s="147" t="s">
         <v>987</v>
       </c>
-      <c r="N186" s="145" t="s">
+      <c r="N186" s="144" t="s">
         <v>988</v>
       </c>
     </row>
@@ -13060,39 +13382,41 @@
       <c r="A187" s="6">
         <v>186</v>
       </c>
-      <c r="B187" s="143" t="s">
+      <c r="B187" s="142" t="s">
         <v>989</v>
       </c>
-      <c r="C187" s="144"/>
-      <c r="D187" s="145"/>
-      <c r="E187" s="146" t="s">
+      <c r="C187" s="143"/>
+      <c r="D187" s="144" t="s">
+        <v>947</v>
+      </c>
+      <c r="E187" s="145" t="s">
         <v>52</v>
       </c>
-      <c r="F187" s="145" t="s">
+      <c r="F187" s="144" t="s">
         <v>990</v>
       </c>
-      <c r="G187" s="147">
+      <c r="G187" s="146">
         <v>3.2986111111111111E-3</v>
       </c>
-      <c r="H187" s="145" t="s">
+      <c r="H187" s="144" t="s">
         <v>17</v>
       </c>
-      <c r="I187" s="145" t="s">
+      <c r="I187" s="144" t="s">
         <v>354</v>
       </c>
-      <c r="J187" s="145" t="s">
+      <c r="J187" s="144" t="s">
         <v>384</v>
       </c>
-      <c r="K187" s="145" t="s">
+      <c r="K187" s="144" t="s">
         <v>19</v>
       </c>
-      <c r="L187" s="145" t="s">
+      <c r="L187" s="144" t="s">
         <v>991</v>
       </c>
-      <c r="M187" s="148" t="s">
+      <c r="M187" s="147" t="s">
         <v>992</v>
       </c>
-      <c r="N187" s="145" t="s">
+      <c r="N187" s="144" t="s">
         <v>993</v>
       </c>
     </row>
@@ -13100,39 +13424,41 @@
       <c r="A188" s="5">
         <v>187</v>
       </c>
-      <c r="B188" s="143" t="s">
+      <c r="B188" s="142" t="s">
         <v>994</v>
       </c>
-      <c r="C188" s="144"/>
-      <c r="D188" s="145"/>
-      <c r="E188" s="146" t="s">
+      <c r="C188" s="143"/>
+      <c r="D188" s="144" t="s">
+        <v>947</v>
+      </c>
+      <c r="E188" s="145" t="s">
         <v>56</v>
       </c>
-      <c r="F188" s="145" t="s">
+      <c r="F188" s="144" t="s">
         <v>995</v>
       </c>
-      <c r="G188" s="147">
+      <c r="G188" s="146">
         <v>3.5185185185185185E-3</v>
       </c>
-      <c r="H188" s="145" t="s">
+      <c r="H188" s="144" t="s">
         <v>17</v>
       </c>
-      <c r="I188" s="145" t="s">
+      <c r="I188" s="144" t="s">
         <v>354</v>
       </c>
-      <c r="J188" s="145" t="s">
+      <c r="J188" s="144" t="s">
         <v>384</v>
       </c>
-      <c r="K188" s="145" t="s">
+      <c r="K188" s="144" t="s">
         <v>19</v>
       </c>
-      <c r="L188" s="145" t="s">
+      <c r="L188" s="144" t="s">
         <v>996</v>
       </c>
-      <c r="M188" s="148" t="s">
+      <c r="M188" s="147" t="s">
         <v>997</v>
       </c>
-      <c r="N188" s="145" t="s">
+      <c r="N188" s="144" t="s">
         <v>998</v>
       </c>
     </row>
@@ -13140,39 +13466,41 @@
       <c r="A189" s="6">
         <v>188</v>
       </c>
-      <c r="B189" s="143" t="s">
+      <c r="B189" s="142" t="s">
         <v>999</v>
       </c>
-      <c r="C189" s="144"/>
-      <c r="D189" s="145"/>
-      <c r="E189" s="146" t="s">
+      <c r="C189" s="143"/>
+      <c r="D189" s="144" t="s">
+        <v>947</v>
+      </c>
+      <c r="E189" s="145" t="s">
         <v>61</v>
       </c>
-      <c r="F189" s="145" t="s">
+      <c r="F189" s="144" t="s">
         <v>1000</v>
       </c>
-      <c r="G189" s="147">
+      <c r="G189" s="146">
         <v>4.6759259259259263E-3</v>
       </c>
-      <c r="H189" s="145" t="s">
+      <c r="H189" s="144" t="s">
         <v>17</v>
       </c>
-      <c r="I189" s="145" t="s">
+      <c r="I189" s="144" t="s">
         <v>354</v>
       </c>
-      <c r="J189" s="145" t="s">
+      <c r="J189" s="144" t="s">
         <v>384</v>
       </c>
-      <c r="K189" s="145" t="s">
+      <c r="K189" s="144" t="s">
         <v>19</v>
       </c>
-      <c r="L189" s="145" t="s">
+      <c r="L189" s="144" t="s">
         <v>1001</v>
       </c>
-      <c r="M189" s="148" t="s">
+      <c r="M189" s="147" t="s">
         <v>1002</v>
       </c>
-      <c r="N189" s="145" t="s">
+      <c r="N189" s="144" t="s">
         <v>1003</v>
       </c>
     </row>
@@ -13180,39 +13508,41 @@
       <c r="A190" s="5">
         <v>189</v>
       </c>
-      <c r="B190" s="143" t="s">
+      <c r="B190" s="142" t="s">
         <v>1004</v>
       </c>
-      <c r="C190" s="144"/>
-      <c r="D190" s="145"/>
-      <c r="E190" s="146" t="s">
+      <c r="C190" s="143"/>
+      <c r="D190" s="144" t="s">
+        <v>947</v>
+      </c>
+      <c r="E190" s="145" t="s">
         <v>65</v>
       </c>
-      <c r="F190" s="145" t="s">
+      <c r="F190" s="144" t="s">
         <v>1005</v>
       </c>
-      <c r="G190" s="147">
+      <c r="G190" s="146">
         <v>7.8935185185185185E-3</v>
       </c>
-      <c r="H190" s="145" t="s">
+      <c r="H190" s="144" t="s">
         <v>301</v>
       </c>
-      <c r="I190" s="145" t="s">
+      <c r="I190" s="144" t="s">
         <v>302</v>
       </c>
-      <c r="J190" s="145" t="s">
+      <c r="J190" s="144" t="s">
         <v>384</v>
       </c>
-      <c r="K190" s="145" t="s">
+      <c r="K190" s="144" t="s">
         <v>19</v>
       </c>
-      <c r="L190" s="145" t="s">
+      <c r="L190" s="144" t="s">
         <v>1006</v>
       </c>
-      <c r="M190" s="148" t="s">
+      <c r="M190" s="147" t="s">
         <v>1007</v>
       </c>
-      <c r="N190" s="145" t="s">
+      <c r="N190" s="144" t="s">
         <v>1008</v>
       </c>
     </row>
@@ -13220,39 +13550,41 @@
       <c r="A191" s="6">
         <v>190</v>
       </c>
-      <c r="B191" s="143" t="s">
+      <c r="B191" s="142" t="s">
         <v>1009</v>
       </c>
-      <c r="C191" s="144"/>
-      <c r="D191" s="145"/>
-      <c r="E191" s="146" t="s">
+      <c r="C191" s="143"/>
+      <c r="D191" s="144" t="s">
+        <v>947</v>
+      </c>
+      <c r="E191" s="145" t="s">
         <v>1010</v>
       </c>
-      <c r="F191" s="145" t="s">
+      <c r="F191" s="144" t="s">
         <v>1011</v>
       </c>
-      <c r="G191" s="147">
+      <c r="G191" s="146">
         <v>7.9745370370370369E-3</v>
       </c>
-      <c r="H191" s="145" t="s">
+      <c r="H191" s="144" t="s">
         <v>17</v>
       </c>
-      <c r="I191" s="145" t="s">
+      <c r="I191" s="144" t="s">
         <v>354</v>
       </c>
-      <c r="J191" s="145" t="s">
+      <c r="J191" s="144" t="s">
         <v>384</v>
       </c>
-      <c r="K191" s="145" t="s">
+      <c r="K191" s="144" t="s">
         <v>19</v>
       </c>
-      <c r="L191" s="145" t="s">
+      <c r="L191" s="144" t="s">
         <v>1012</v>
       </c>
-      <c r="M191" s="148" t="s">
+      <c r="M191" s="147" t="s">
         <v>1013</v>
       </c>
-      <c r="N191" s="145" t="s">
+      <c r="N191" s="144" t="s">
         <v>1014</v>
       </c>
     </row>
@@ -13260,79 +13592,83 @@
       <c r="A192" s="5">
         <v>191</v>
       </c>
-      <c r="B192" s="143" t="s">
+      <c r="B192" s="142" t="s">
         <v>1015</v>
       </c>
-      <c r="C192" s="144"/>
-      <c r="D192" s="145"/>
-      <c r="E192" s="146" t="s">
+      <c r="C192" s="143"/>
+      <c r="D192" s="144" t="s">
+        <v>947</v>
+      </c>
+      <c r="E192" s="145" t="s">
         <v>1016</v>
       </c>
-      <c r="F192" s="145" t="s">
+      <c r="F192" s="144" t="s">
         <v>1017</v>
       </c>
-      <c r="G192" s="147">
+      <c r="G192" s="146">
         <v>1.5694444444444445E-2</v>
       </c>
-      <c r="H192" s="145" t="s">
+      <c r="H192" s="144" t="s">
         <v>17</v>
       </c>
-      <c r="I192" s="145" t="s">
+      <c r="I192" s="144" t="s">
         <v>18</v>
       </c>
-      <c r="J192" s="145" t="s">
+      <c r="J192" s="144" t="s">
         <v>384</v>
       </c>
-      <c r="K192" s="145" t="s">
+      <c r="K192" s="144" t="s">
         <v>19</v>
       </c>
-      <c r="L192" s="145" t="s">
+      <c r="L192" s="144" t="s">
         <v>1018</v>
       </c>
-      <c r="M192" s="148" t="s">
+      <c r="M192" s="147" t="s">
         <v>1019</v>
       </c>
-      <c r="N192" s="145" t="s">
+      <c r="N192" s="144" t="s">
         <v>1020</v>
       </c>
     </row>
-    <row r="193" spans="1:14" ht="180.6" thickBot="1">
+    <row r="193" spans="1:14" ht="198.6" thickBot="1">
       <c r="A193" s="6">
         <v>192</v>
       </c>
-      <c r="B193" s="143" t="s">
+      <c r="B193" s="142" t="s">
         <v>1021</v>
       </c>
-      <c r="C193" s="144"/>
-      <c r="D193" s="145"/>
-      <c r="E193" s="146" t="s">
+      <c r="C193" s="143"/>
+      <c r="D193" s="144" t="s">
+        <v>947</v>
+      </c>
+      <c r="E193" s="145" t="s">
         <v>1022</v>
       </c>
-      <c r="F193" s="145" t="s">
+      <c r="F193" s="144" t="s">
         <v>1023</v>
       </c>
-      <c r="G193" s="147">
+      <c r="G193" s="146">
         <v>1.238425925925926E-2</v>
       </c>
-      <c r="H193" s="145" t="s">
+      <c r="H193" s="144" t="s">
         <v>17</v>
       </c>
-      <c r="I193" s="145" t="s">
+      <c r="I193" s="144" t="s">
         <v>18</v>
       </c>
-      <c r="J193" s="145" t="s">
+      <c r="J193" s="144" t="s">
         <v>384</v>
       </c>
-      <c r="K193" s="145" t="s">
+      <c r="K193" s="144" t="s">
         <v>19</v>
       </c>
-      <c r="L193" s="145" t="s">
+      <c r="L193" s="144" t="s">
         <v>1024</v>
       </c>
-      <c r="M193" s="148" t="s">
+      <c r="M193" s="147" t="s">
         <v>1025</v>
       </c>
-      <c r="N193" s="145" t="s">
+      <c r="N193" s="144" t="s">
         <v>1026</v>
       </c>
     </row>
@@ -13340,79 +13676,83 @@
       <c r="A194" s="5">
         <v>193</v>
       </c>
-      <c r="B194" s="143" t="s">
+      <c r="B194" s="142" t="s">
         <v>1027</v>
       </c>
-      <c r="C194" s="144"/>
-      <c r="D194" s="145"/>
-      <c r="E194" s="146" t="s">
+      <c r="C194" s="143"/>
+      <c r="D194" s="144" t="s">
+        <v>947</v>
+      </c>
+      <c r="E194" s="145" t="s">
         <v>1028</v>
       </c>
-      <c r="F194" s="145" t="s">
+      <c r="F194" s="144" t="s">
         <v>1029</v>
       </c>
-      <c r="G194" s="147">
+      <c r="G194" s="146">
         <v>1.0092592592592592E-2</v>
       </c>
-      <c r="H194" s="145" t="s">
+      <c r="H194" s="144" t="s">
         <v>17</v>
       </c>
-      <c r="I194" s="145" t="s">
+      <c r="I194" s="144" t="s">
         <v>18</v>
       </c>
-      <c r="J194" s="145" t="s">
+      <c r="J194" s="144" t="s">
         <v>384</v>
       </c>
-      <c r="K194" s="145" t="s">
+      <c r="K194" s="144" t="s">
         <v>19</v>
       </c>
-      <c r="L194" s="145" t="s">
+      <c r="L194" s="144" t="s">
         <v>1030</v>
       </c>
-      <c r="M194" s="148" t="s">
+      <c r="M194" s="147" t="s">
         <v>1031</v>
       </c>
-      <c r="N194" s="145" t="s">
+      <c r="N194" s="144" t="s">
         <v>1032</v>
       </c>
     </row>
-    <row r="195" spans="1:14" ht="198.6" thickBot="1">
+    <row r="195" spans="1:14" ht="216.6" thickBot="1">
       <c r="A195" s="6">
         <v>194</v>
       </c>
-      <c r="B195" s="143" t="s">
+      <c r="B195" s="142" t="s">
         <v>1033</v>
       </c>
-      <c r="C195" s="144"/>
-      <c r="D195" s="145"/>
-      <c r="E195" s="146" t="s">
+      <c r="C195" s="143"/>
+      <c r="D195" s="144" t="s">
+        <v>947</v>
+      </c>
+      <c r="E195" s="145" t="s">
         <v>1034</v>
       </c>
-      <c r="F195" s="145" t="s">
+      <c r="F195" s="144" t="s">
         <v>1035</v>
       </c>
-      <c r="G195" s="147">
+      <c r="G195" s="146">
         <v>1.9837962962962963E-2</v>
       </c>
-      <c r="H195" s="145" t="s">
+      <c r="H195" s="144" t="s">
         <v>17</v>
       </c>
-      <c r="I195" s="145" t="s">
+      <c r="I195" s="144" t="s">
         <v>395</v>
       </c>
-      <c r="J195" s="145" t="s">
+      <c r="J195" s="144" t="s">
         <v>384</v>
       </c>
-      <c r="K195" s="145" t="s">
+      <c r="K195" s="144" t="s">
         <v>19</v>
       </c>
-      <c r="L195" s="145" t="s">
+      <c r="L195" s="144" t="s">
         <v>1036</v>
       </c>
-      <c r="M195" s="148" t="s">
+      <c r="M195" s="147" t="s">
         <v>1037</v>
       </c>
-      <c r="N195" s="145" t="s">
+      <c r="N195" s="144" t="s">
         <v>1038</v>
       </c>
     </row>
@@ -13420,39 +13760,41 @@
       <c r="A196" s="5">
         <v>195</v>
       </c>
-      <c r="B196" s="143" t="s">
+      <c r="B196" s="142" t="s">
         <v>1039</v>
       </c>
-      <c r="C196" s="144"/>
-      <c r="D196" s="145"/>
-      <c r="E196" s="146" t="s">
+      <c r="C196" s="143"/>
+      <c r="D196" s="144" t="s">
+        <v>947</v>
+      </c>
+      <c r="E196" s="145" t="s">
         <v>1040</v>
       </c>
-      <c r="F196" s="145" t="s">
+      <c r="F196" s="144" t="s">
         <v>1041</v>
       </c>
-      <c r="G196" s="147">
+      <c r="G196" s="146">
         <v>1.375E-2</v>
       </c>
-      <c r="H196" s="145" t="s">
+      <c r="H196" s="144" t="s">
         <v>17</v>
       </c>
-      <c r="I196" s="145" t="s">
+      <c r="I196" s="144" t="s">
         <v>395</v>
       </c>
-      <c r="J196" s="145" t="s">
+      <c r="J196" s="144" t="s">
         <v>384</v>
       </c>
-      <c r="K196" s="145" t="s">
+      <c r="K196" s="144" t="s">
         <v>19</v>
       </c>
-      <c r="L196" s="145" t="s">
+      <c r="L196" s="144" t="s">
         <v>1042</v>
       </c>
-      <c r="M196" s="148" t="s">
+      <c r="M196" s="147" t="s">
         <v>1043</v>
       </c>
-      <c r="N196" s="145" t="s">
+      <c r="N196" s="144" t="s">
         <v>1044</v>
       </c>
     </row>
@@ -13460,41 +13802,41 @@
       <c r="A197" s="6">
         <v>196</v>
       </c>
-      <c r="B197" s="149" t="s">
+      <c r="B197" s="148" t="s">
         <v>1045</v>
       </c>
-      <c r="C197" s="150" t="s">
+      <c r="C197" s="149" t="s">
         <v>1046</v>
       </c>
-      <c r="D197" s="151" t="s">
+      <c r="D197" s="150" t="s">
         <v>1047</v>
       </c>
-      <c r="E197" s="152" t="s">
+      <c r="E197" s="151" t="s">
         <v>15</v>
       </c>
-      <c r="F197" s="151" t="s">
+      <c r="F197" s="150" t="s">
         <v>1048</v>
       </c>
-      <c r="G197" s="153">
+      <c r="G197" s="152">
         <v>1.4861111111111111E-2</v>
       </c>
-      <c r="H197" s="151" t="s">
+      <c r="H197" s="150" t="s">
         <v>17</v>
       </c>
-      <c r="I197" s="151" t="s">
+      <c r="I197" s="150" t="s">
         <v>918</v>
       </c>
-      <c r="J197" s="151"/>
-      <c r="K197" s="151" t="s">
+      <c r="J197" s="150"/>
+      <c r="K197" s="150" t="s">
         <v>19</v>
       </c>
-      <c r="L197" s="151" t="s">
+      <c r="L197" s="150" t="s">
         <v>1049</v>
       </c>
-      <c r="M197" s="154" t="s">
+      <c r="M197" s="153" t="s">
         <v>1050</v>
       </c>
-      <c r="N197" s="151" t="s">
+      <c r="N197" s="150" t="s">
         <v>1051</v>
       </c>
     </row>
@@ -13502,37 +13844,39 @@
       <c r="A198" s="5">
         <v>197</v>
       </c>
-      <c r="B198" s="149" t="s">
+      <c r="B198" s="148" t="s">
         <v>1052</v>
       </c>
-      <c r="C198" s="150"/>
-      <c r="D198" s="151"/>
-      <c r="E198" s="152" t="s">
+      <c r="C198" s="149"/>
+      <c r="D198" s="150" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E198" s="151" t="s">
         <v>22</v>
       </c>
-      <c r="F198" s="151" t="s">
+      <c r="F198" s="150" t="s">
         <v>1053</v>
       </c>
-      <c r="G198" s="153">
+      <c r="G198" s="152">
         <v>6.4004629629629628E-3</v>
       </c>
-      <c r="H198" s="151" t="s">
+      <c r="H198" s="150" t="s">
         <v>17</v>
       </c>
-      <c r="I198" s="151" t="s">
+      <c r="I198" s="150" t="s">
         <v>354</v>
       </c>
-      <c r="J198" s="151"/>
-      <c r="K198" s="151" t="s">
+      <c r="J198" s="150"/>
+      <c r="K198" s="150" t="s">
         <v>19</v>
       </c>
-      <c r="L198" s="151" t="s">
+      <c r="L198" s="150" t="s">
         <v>1054</v>
       </c>
-      <c r="M198" s="154" t="s">
+      <c r="M198" s="153" t="s">
         <v>1055</v>
       </c>
-      <c r="N198" s="151" t="s">
+      <c r="N198" s="150" t="s">
         <v>1056</v>
       </c>
     </row>
@@ -13540,37 +13884,39 @@
       <c r="A199" s="6">
         <v>198</v>
       </c>
-      <c r="B199" s="149" t="s">
+      <c r="B199" s="148" t="s">
         <v>1057</v>
       </c>
-      <c r="C199" s="150"/>
-      <c r="D199" s="151"/>
-      <c r="E199" s="152" t="s">
+      <c r="C199" s="149"/>
+      <c r="D199" s="150" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E199" s="151" t="s">
         <v>27</v>
       </c>
-      <c r="F199" s="151" t="s">
+      <c r="F199" s="150" t="s">
         <v>1058</v>
       </c>
-      <c r="G199" s="153">
+      <c r="G199" s="152">
         <v>1.2777777777777779E-2</v>
       </c>
-      <c r="H199" s="151" t="s">
+      <c r="H199" s="150" t="s">
         <v>17</v>
       </c>
-      <c r="I199" s="151" t="s">
+      <c r="I199" s="150" t="s">
         <v>1059</v>
       </c>
-      <c r="J199" s="151"/>
-      <c r="K199" s="151" t="s">
+      <c r="J199" s="150"/>
+      <c r="K199" s="150" t="s">
         <v>19</v>
       </c>
-      <c r="L199" s="151" t="s">
+      <c r="L199" s="150" t="s">
         <v>1060</v>
       </c>
-      <c r="M199" s="154" t="s">
+      <c r="M199" s="153" t="s">
         <v>1061</v>
       </c>
-      <c r="N199" s="151" t="s">
+      <c r="N199" s="150" t="s">
         <v>1062</v>
       </c>
     </row>
@@ -13578,37 +13924,39 @@
       <c r="A200" s="5">
         <v>199</v>
       </c>
-      <c r="B200" s="149" t="s">
+      <c r="B200" s="148" t="s">
         <v>1063</v>
       </c>
-      <c r="C200" s="150"/>
-      <c r="D200" s="151"/>
-      <c r="E200" s="152" t="s">
+      <c r="C200" s="149"/>
+      <c r="D200" s="150" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E200" s="151" t="s">
         <v>31</v>
       </c>
-      <c r="F200" s="151" t="s">
+      <c r="F200" s="150" t="s">
         <v>1064</v>
       </c>
-      <c r="G200" s="153">
+      <c r="G200" s="152">
         <v>1.3657407407407408E-2</v>
       </c>
-      <c r="H200" s="151" t="s">
+      <c r="H200" s="150" t="s">
         <v>17</v>
       </c>
-      <c r="I200" s="151" t="s">
+      <c r="I200" s="150" t="s">
         <v>918</v>
       </c>
-      <c r="J200" s="151"/>
-      <c r="K200" s="151" t="s">
+      <c r="J200" s="150"/>
+      <c r="K200" s="150" t="s">
         <v>19</v>
       </c>
-      <c r="L200" s="151" t="s">
+      <c r="L200" s="150" t="s">
         <v>1065</v>
       </c>
-      <c r="M200" s="154" t="s">
+      <c r="M200" s="153" t="s">
         <v>1066</v>
       </c>
-      <c r="N200" s="151" t="s">
+      <c r="N200" s="150" t="s">
         <v>1067</v>
       </c>
     </row>
@@ -13616,37 +13964,39 @@
       <c r="A201" s="6">
         <v>200</v>
       </c>
-      <c r="B201" s="149" t="s">
+      <c r="B201" s="148" t="s">
         <v>1068</v>
       </c>
-      <c r="C201" s="150"/>
-      <c r="D201" s="151"/>
-      <c r="E201" s="152" t="s">
+      <c r="C201" s="149"/>
+      <c r="D201" s="150" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E201" s="151" t="s">
         <v>35</v>
       </c>
-      <c r="F201" s="151" t="s">
+      <c r="F201" s="150" t="s">
         <v>1069</v>
       </c>
-      <c r="G201" s="153">
+      <c r="G201" s="152">
         <v>1.3275462962962963E-2</v>
       </c>
-      <c r="H201" s="151" t="s">
+      <c r="H201" s="150" t="s">
         <v>17</v>
       </c>
-      <c r="I201" s="151" t="s">
+      <c r="I201" s="150" t="s">
         <v>846</v>
       </c>
-      <c r="J201" s="151"/>
-      <c r="K201" s="151" t="s">
+      <c r="J201" s="150"/>
+      <c r="K201" s="150" t="s">
         <v>19</v>
       </c>
-      <c r="L201" s="151" t="s">
+      <c r="L201" s="150" t="s">
         <v>1070</v>
       </c>
-      <c r="M201" s="154" t="s">
+      <c r="M201" s="153" t="s">
         <v>1071</v>
       </c>
-      <c r="N201" s="151" t="s">
+      <c r="N201" s="150" t="s">
         <v>1072</v>
       </c>
     </row>
